--- a/test/TW2203-1_model_results.xlsx
+++ b/test/TW2203-1_model_results.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -514,88 +514,103 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Y_PS</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.542553191489362</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Product/Brix</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Initial OD</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>0.6</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>OD</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Initial Brix</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>10.9</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Brix</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Initial Product</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Final simulated OD</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>99.62755635091774</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B10" t="n">
+        <v>50.11381682604605</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>OD</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Final simulated Brix</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1.136184278018755e-05</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B11" t="n">
+        <v>2.853282601634079e-06</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Brix</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Final simulated Product</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>9.902755635091772</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="n">
+        <v>24.75690841302303</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
@@ -612,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,6 +693,11 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>mu_raw</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>mu_net_interval</t>
         </is>
       </c>
@@ -710,6 +730,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -751,6 +772,9 @@
       <c r="M3" t="n">
         <v>0.321704603556448</v>
       </c>
+      <c r="N3" t="n">
+        <v>0.321704603556448</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -792,6 +816,9 @@
       <c r="M4" t="n">
         <v>0.1932974720583704</v>
       </c>
+      <c r="N4" t="n">
+        <v>0.2575010378074092</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -833,6 +860,9 @@
       <c r="M5" t="n">
         <v>0.08081793886166637</v>
       </c>
+      <c r="N5" t="n">
+        <v>0.1986066714921616</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -874,6 +904,9 @@
       <c r="M6" t="n">
         <v>0.0119102065203302</v>
       </c>
+      <c r="N6" t="n">
+        <v>0.09534187248012234</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -915,6 +948,9 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
+      <c r="N7" t="n">
+        <v>0.03090938179399886</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -956,6 +992,9 @@
       <c r="M8" t="n">
         <v>0.003381273613429516</v>
       </c>
+      <c r="N8" t="n">
+        <v>0.005097160044586573</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -996,6 +1035,9 @@
       </c>
       <c r="M9" t="n">
         <v>0.0006880248234825715</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001356432812304029</v>
       </c>
     </row>
   </sheetData>
@@ -1053,13 +1095,13 @@
         <v>0.1201714540191494</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6136736543782694</v>
+        <v>0.6136732569064917</v>
       </c>
       <c r="C3" t="n">
-        <v>10.8984949373401</v>
+        <v>10.89698996217984</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001367365437826943</v>
+        <v>0.006836628453245805</v>
       </c>
     </row>
     <row r="4">
@@ -1067,13 +1109,13 @@
         <v>0.2403429080382988</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6276581022816864</v>
+        <v>0.6276564622361156</v>
       </c>
       <c r="C4" t="n">
-        <v>10.89695566555682</v>
+        <v>10.89391169215411</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002765810228168643</v>
+        <v>0.01382823111805781</v>
       </c>
     </row>
     <row r="5">
@@ -1081,13 +1123,13 @@
         <v>0.3605143620574482</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6419603644743377</v>
+        <v>0.6419566435897592</v>
       </c>
       <c r="C5" t="n">
-        <v>10.89538141187285</v>
+        <v>10.89076364286314</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004196036447433774</v>
+        <v>0.02097832179487965</v>
       </c>
     </row>
     <row r="6">
@@ -1095,13 +1137,13 @@
         <v>0.4806858160765976</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6565876232062731</v>
+        <v>0.6565810531624274</v>
       </c>
       <c r="C6" t="n">
-        <v>10.89377138573608</v>
+        <v>10.88754421780499</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005658762320627305</v>
+        <v>0.02829052658121375</v>
       </c>
     </row>
     <row r="7">
@@ -1109,13 +1151,13 @@
         <v>0.600857270095747</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6715472244152708</v>
+        <v>0.671536830575348</v>
       </c>
       <c r="C7" t="n">
-        <v>10.89212477857724</v>
+        <v>10.88425184525976</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007154722441527082</v>
+        <v>0.03576841528767401</v>
       </c>
     </row>
     <row r="8">
@@ -1123,13 +1165,13 @@
         <v>0.7210287241148964</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6868466777268383</v>
+        <v>0.686831290245061</v>
       </c>
       <c r="C8" t="n">
-        <v>10.89044076380993</v>
+        <v>10.88088491502802</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008684667772683834</v>
+        <v>0.04341564512253046</v>
       </c>
     </row>
     <row r="9">
@@ -1137,13 +1179,13 @@
         <v>0.8412001781340458</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7024939674511055</v>
+        <v>0.702471938185243</v>
       </c>
       <c r="C9" t="n">
-        <v>10.88871846259906</v>
+        <v>10.87744177473205</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01024939674511055</v>
+        <v>0.05123596909262149</v>
       </c>
     </row>
     <row r="10">
@@ -1151,13 +1193,13 @@
         <v>0.9613716321531952</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7184976081766027</v>
+        <v>0.7184664720067075</v>
       </c>
       <c r="C10" t="n">
-        <v>10.88695693774169</v>
+        <v>10.87392072981585</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01184976081766027</v>
+        <v>0.05923323600335381</v>
       </c>
     </row>
     <row r="11">
@@ -1165,13 +1207,13 @@
         <v>1.081543086172345</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7348652753757148</v>
+        <v>0.7348227809174049</v>
       </c>
       <c r="C11" t="n">
-        <v>10.88515534439659</v>
+        <v>10.87032004354511</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01348652753757149</v>
+        <v>0.06741139045870247</v>
       </c>
     </row>
     <row r="12">
@@ -1179,13 +1221,13 @@
         <v>1.201714540191494</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7516048272130114</v>
+        <v>0.7515489457224217</v>
       </c>
       <c r="C12" t="n">
-        <v>10.88331281761356</v>
+        <v>10.86663793700724</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01516048272130114</v>
+        <v>0.07577447286121085</v>
       </c>
     </row>
     <row r="13">
@@ -1193,13 +1235,13 @@
         <v>1.321885994210643</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7687243663774582</v>
+        <v>0.7686532388239813</v>
       </c>
       <c r="C13" t="n">
-        <v>10.88142846552754</v>
+        <v>10.86287258911135</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01687243663774583</v>
+        <v>0.08432661941199066</v>
       </c>
     </row>
     <row r="14">
@@ -1207,13 +1249,13 @@
         <v>1.442057448229793</v>
       </c>
       <c r="B14" t="n">
-        <v>0.786232240082418</v>
+        <v>0.7861441242214439</v>
       </c>
       <c r="C14" t="n">
-        <v>10.87950136935861</v>
+        <v>10.85902213658825</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0186232240082418</v>
+        <v>0.09307206211072194</v>
       </c>
     </row>
     <row r="15">
@@ -1221,13 +1263,13 @@
         <v>1.562228902248942</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8041370400656496</v>
+        <v>0.8040302575113062</v>
       </c>
       <c r="C15" t="n">
-        <v>10.87753058341198</v>
+        <v>10.85508467399048</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02041370400656497</v>
+        <v>0.1020151287556531</v>
       </c>
     </row>
     <row r="16">
@@ -1235,13 +1277,13 @@
         <v>1.682400356268092</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8224476025893089</v>
+        <v>0.8223204858872015</v>
       </c>
       <c r="C16" t="n">
-        <v>10.87551513507799</v>
+        <v>10.85105825369228</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0222447602589309</v>
+        <v>0.1111602429436008</v>
       </c>
     </row>
     <row r="17">
@@ -1249,13 +1291,13 @@
         <v>1.802571810287241</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8411730084399484</v>
+        <v>0.8410238481399002</v>
       </c>
       <c r="C17" t="n">
-        <v>10.87345402483214</v>
+        <v>10.84694088588958</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02411730084399483</v>
+        <v>0.1205119240699501</v>
       </c>
     </row>
     <row r="18">
@@ -1263,13 +1305,13 @@
         <v>1.92274326430639</v>
       </c>
       <c r="B18" t="n">
-        <v>0.8603225829285166</v>
+        <v>0.8601495746573089</v>
       </c>
       <c r="C18" t="n">
-        <v>10.87134622623504</v>
+        <v>10.84273053860003</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02603225829285166</v>
+        <v>0.1300747873286545</v>
       </c>
     </row>
     <row r="19">
@@ -1277,13 +1319,13 @@
         <v>2.04291471832554</v>
       </c>
       <c r="B19" t="n">
-        <v>0.8799058958903592</v>
+        <v>0.879707087424471</v>
       </c>
       <c r="C19" t="n">
-        <v>10.86919068593244</v>
+        <v>10.838425137663</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02799058958903592</v>
+        <v>0.1398535437122355</v>
       </c>
     </row>
     <row r="20">
@@ -1291,13 +1333,13 @@
         <v>2.163086172344689</v>
       </c>
       <c r="B20" t="n">
-        <v>0.8999327616852182</v>
+        <v>0.8997060000235667</v>
       </c>
       <c r="C20" t="n">
-        <v>10.86698632365526</v>
+        <v>10.83402256673954</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02999327616852182</v>
+        <v>0.1498530000117834</v>
       </c>
     </row>
     <row r="21">
@@ -1305,13 +1347,13 @@
         <v>2.283257626363838</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9204132391972325</v>
+        <v>0.9201561176339127</v>
       </c>
       <c r="C21" t="n">
-        <v>10.86473203221951</v>
+        <v>10.82952066731244</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03204132391972325</v>
+        <v>0.1600780588169564</v>
       </c>
     </row>
     <row r="22">
@@ -1319,13 +1361,13 @@
         <v>2.403429080382988</v>
       </c>
       <c r="B22" t="n">
-        <v>0.9413576318349371</v>
+        <v>0.9410674370319625</v>
       </c>
       <c r="C22" t="n">
-        <v>10.86242667752637</v>
+        <v>10.82491723868617</v>
       </c>
       <c r="D22" t="n">
-        <v>0.03413576318349372</v>
+        <v>0.1705337185159812</v>
       </c>
     </row>
     <row r="23">
@@ -1333,13 +1375,13 @@
         <v>2.523600534402137</v>
       </c>
       <c r="B23" t="n">
-        <v>0.962776487531264</v>
+        <v>0.9624501465913061</v>
       </c>
       <c r="C23" t="n">
-        <v>10.86006909856213</v>
+        <v>10.82021003798693</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0362776487531264</v>
+        <v>0.1812250732956531</v>
       </c>
     </row>
     <row r="24">
@@ -1347,13 +1389,13 @@
         <v>2.643771988421287</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9846805987435416</v>
+        <v>0.9843146262826703</v>
       </c>
       <c r="C24" t="n">
-        <v>10.85765810739825</v>
+        <v>10.8153967801626</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03846805987435416</v>
+        <v>0.1921573131413351</v>
       </c>
     </row>
     <row r="25">
@@ -1361,13 +1403,13 @@
         <v>2.763943442440436</v>
       </c>
       <c r="B25" t="n">
-        <v>1.007081002453495</v>
+        <v>1.006671447673918</v>
       </c>
       <c r="C25" t="n">
-        <v>10.8551924891913</v>
+        <v>10.81047513798279</v>
       </c>
       <c r="D25" t="n">
-        <v>0.04070810024534949</v>
+        <v>0.2033357238369593</v>
       </c>
     </row>
     <row r="26">
@@ -1375,13 +1417,13 @@
         <v>2.884114896459586</v>
       </c>
       <c r="B26" t="n">
-        <v>1.029988980167246</v>
+        <v>1.029532113105745</v>
       </c>
       <c r="C26" t="n">
-        <v>10.852671002183</v>
+        <v>10.8054425793163</v>
       </c>
       <c r="D26" t="n">
-        <v>0.04299889801672457</v>
+        <v>0.2147660565528723</v>
       </c>
     </row>
     <row r="27">
@@ -1389,13 +1431,13 @@
         <v>3.004286350478735</v>
       </c>
       <c r="B27" t="n">
-        <v>1.053416057915312</v>
+        <v>1.052908805545817</v>
       </c>
       <c r="C27" t="n">
-        <v>10.85009237770019</v>
+        <v>10.80029642219835</v>
       </c>
       <c r="D27" t="n">
-        <v>0.04534160579153119</v>
+        <v>0.2264544027729086</v>
       </c>
     </row>
     <row r="28">
@@ -1403,13 +1445,13 @@
         <v>3.124457804497884</v>
       </c>
       <c r="B28" t="n">
-        <v>1.077374006252609</v>
+        <v>1.076812265458251</v>
       </c>
       <c r="C28" t="n">
-        <v>10.84745532015487</v>
+        <v>10.79503430221762</v>
       </c>
       <c r="D28" t="n">
-        <v>0.04773740062526087</v>
+        <v>0.2384061327291255</v>
       </c>
     </row>
     <row r="29">
@@ -1417,13 +1459,13 @@
         <v>3.244629258517034</v>
       </c>
       <c r="B29" t="n">
-        <v>1.101874840258447</v>
+        <v>1.101253518156284</v>
       </c>
       <c r="C29" t="n">
-        <v>10.84475850704415</v>
+        <v>10.78965379225599</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05018748402584473</v>
+        <v>0.2506267590781419</v>
       </c>
     </row>
     <row r="30">
@@ -1431,13 +1473,13 @@
         <v>3.364800712536183</v>
       </c>
       <c r="B30" t="n">
-        <v>1.126930819536536</v>
+        <v>1.12624392419639</v>
       </c>
       <c r="C30" t="n">
-        <v>10.84200058895031</v>
+        <v>10.78415239139471</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05269308195365356</v>
+        <v>0.2631219620981948</v>
       </c>
     </row>
     <row r="31">
@@ -1445,13 +1487,13 @@
         <v>3.484972166555333</v>
       </c>
       <c r="B31" t="n">
-        <v>1.152554448214978</v>
+        <v>1.15179517937828</v>
       </c>
       <c r="C31" t="n">
-        <v>10.83918018954074</v>
+        <v>10.77852752491438</v>
       </c>
       <c r="D31" t="n">
-        <v>0.05525544482149784</v>
+        <v>0.2758975896891398</v>
       </c>
     </row>
     <row r="32">
@@ -1459,13 +1501,13 @@
         <v>3.605143620574482</v>
       </c>
       <c r="B32" t="n">
-        <v>1.178758474946277</v>
+        <v>1.177919314744901</v>
       </c>
       <c r="C32" t="n">
-        <v>10.83629590556798</v>
+        <v>10.77277654429503</v>
       </c>
       <c r="D32" t="n">
-        <v>0.05787584749462765</v>
+        <v>0.2889596573724507</v>
       </c>
     </row>
     <row r="33">
@@ -1473,13 +1515,13 @@
         <v>3.725315074593631</v>
       </c>
       <c r="B33" t="n">
-        <v>1.205555892907328</v>
+        <v>1.20462869658244</v>
       </c>
       <c r="C33" t="n">
-        <v>10.83334630686969</v>
+        <v>10.76689672721604</v>
       </c>
       <c r="D33" t="n">
-        <v>0.06055558929073282</v>
+        <v>0.3023143482912198</v>
       </c>
     </row>
     <row r="34">
@@ -1487,13 +1529,13 @@
         <v>3.845486528612781</v>
       </c>
       <c r="B34" t="n">
-        <v>1.232959939799428</v>
+        <v>1.231936026420316</v>
       </c>
       <c r="C34" t="n">
-        <v>10.83032993636868</v>
+        <v>10.76088527755618</v>
       </c>
       <c r="D34" t="n">
-        <v>0.06329599397994275</v>
+        <v>0.3159680132101579</v>
       </c>
     </row>
     <row r="35">
@@ -1501,13 +1543,13 @@
         <v>3.96565798263193</v>
       </c>
       <c r="B35" t="n">
-        <v>1.260984097848266</v>
+        <v>1.259854341031188</v>
       </c>
       <c r="C35" t="n">
-        <v>10.82724531007291</v>
+        <v>10.7547393253936</v>
       </c>
       <c r="D35" t="n">
-        <v>0.06609840978482655</v>
+        <v>0.3299271705155941</v>
       </c>
     </row>
     <row r="36">
@@ -1515,13 +1557,13 @@
         <v>4.085829436651079</v>
       </c>
       <c r="B36" t="n">
-        <v>1.289642093803929</v>
+        <v>1.288397012430951</v>
       </c>
       <c r="C36" t="n">
-        <v>10.82409091707545</v>
+        <v>10.74845592700583</v>
       </c>
       <c r="D36" t="n">
-        <v>0.06896420938039295</v>
+        <v>0.3441985062154758</v>
       </c>
     </row>
     <row r="37">
@@ -1529,13 +1571,13 @@
         <v>4.206000890670229</v>
       </c>
       <c r="B37" t="n">
-        <v>1.318947898940904</v>
+        <v>1.317577747878738</v>
       </c>
       <c r="C37" t="n">
-        <v>10.82086521955452</v>
+        <v>10.74203206486979</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0718947898940904</v>
+        <v>0.3587888739393689</v>
       </c>
     </row>
     <row r="38">
@@ -1543,13 +1585,13 @@
         <v>4.326172344689378</v>
       </c>
       <c r="B38" t="n">
-        <v>1.34891572905807</v>
+        <v>1.347410589876916</v>
       </c>
       <c r="C38" t="n">
-        <v>10.81756665277347</v>
+        <v>10.73546464766176</v>
       </c>
       <c r="D38" t="n">
-        <v>0.07489157290580696</v>
+        <v>0.3737052949384579</v>
       </c>
     </row>
     <row r="39">
@@ -1557,13 +1599,13 @@
         <v>4.446343798708527</v>
       </c>
       <c r="B39" t="n">
-        <v>1.379560044478704</v>
+        <v>1.377909916171091</v>
       </c>
       <c r="C39" t="n">
-        <v>10.8141936250808</v>
+        <v>10.72875051025742</v>
       </c>
       <c r="D39" t="n">
-        <v>0.07795600444787033</v>
+        <v>0.3889549580855454</v>
       </c>
     </row>
     <row r="40">
@@ -1571,13 +1613,13 @@
         <v>4.566515252727677</v>
       </c>
       <c r="B40" t="n">
-        <v>1.41089555005048</v>
+        <v>1.409090439750105</v>
       </c>
       <c r="C40" t="n">
-        <v>10.81074451791014</v>
+        <v>10.72188641373183</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08108955500504794</v>
+        <v>0.4045452198750523</v>
       </c>
     </row>
     <row r="41">
@@ -1585,13 +1627,13 @@
         <v>4.686686706746826</v>
       </c>
       <c r="B41" t="n">
-        <v>1.442937195145469</v>
+        <v>1.440967208846037</v>
       </c>
       <c r="C41" t="n">
-        <v>10.80721768578024</v>
+        <v>10.71486904535942</v>
       </c>
       <c r="D41" t="n">
-        <v>0.08429371951454685</v>
+        <v>0.4204836044230186</v>
       </c>
     </row>
     <row r="42">
@@ -1599,13 +1641,13 @@
         <v>4.806858160765976</v>
       </c>
       <c r="B42" t="n">
-        <v>1.475702758224823</v>
+        <v>1.473555606934204</v>
       </c>
       <c r="C42" t="n">
-        <v>10.80361117181132</v>
+        <v>10.70769501861402</v>
       </c>
       <c r="D42" t="n">
-        <v>0.08757027582248229</v>
+        <v>0.4367778034671018</v>
       </c>
     </row>
     <row r="43">
@@ -1613,13 +1655,13 @@
         <v>4.927029614785125</v>
       </c>
       <c r="B43" t="n">
-        <v>1.509211479560233</v>
+        <v>1.506871352733157</v>
       </c>
       <c r="C43" t="n">
-        <v>10.79992285822171</v>
+        <v>10.70036087316881</v>
       </c>
       <c r="D43" t="n">
-        <v>0.09092114795602328</v>
+        <v>0.4534356763665784</v>
       </c>
     </row>
     <row r="44">
@@ -1627,13 +1669,13 @@
         <v>5.047201068804275</v>
       </c>
       <c r="B44" t="n">
-        <v>1.543478361250916</v>
+        <v>1.540930500204686</v>
       </c>
       <c r="C44" t="n">
-        <v>10.79615109372648</v>
+        <v>10.69286307489639</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09434783612509158</v>
+        <v>0.4704652501023432</v>
       </c>
     </row>
     <row r="45">
@@ -1641,13 +1683,13 @@
         <v>5.167372522823424</v>
       </c>
       <c r="B45" t="n">
-        <v>1.578518871082042</v>
+        <v>1.575749438553818</v>
       </c>
       <c r="C45" t="n">
-        <v>10.79229417578254</v>
+        <v>10.68519801586872</v>
       </c>
       <c r="D45" t="n">
-        <v>0.09785188710820418</v>
+        <v>0.487874719276909</v>
       </c>
     </row>
     <row r="46">
@@ -1655,13 +1697,13 @@
         <v>5.287543976842573</v>
       </c>
       <c r="B46" t="n">
-        <v>1.614349015835013</v>
+        <v>1.611344892228815</v>
       </c>
       <c r="C46" t="n">
-        <v>10.78835034251933</v>
+        <v>10.67736201435712</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1014349015835013</v>
+        <v>0.5056724461144076</v>
       </c>
     </row>
     <row r="47">
@@ -1669,13 +1711,13 @@
         <v>5.407715430861723</v>
       </c>
       <c r="B47" t="n">
-        <v>1.650985341287463</v>
+        <v>1.647733920921178</v>
       </c>
       <c r="C47" t="n">
-        <v>10.78431777273885</v>
+        <v>10.66935131483234</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1050985341287463</v>
+        <v>0.523866960460589</v>
       </c>
     </row>
     <row r="48">
@@ -1683,13 +1725,13 @@
         <v>5.527886884880872</v>
       </c>
       <c r="B48" t="n">
-        <v>1.688444932213261</v>
+        <v>1.684933919565643</v>
       </c>
       <c r="C48" t="n">
-        <v>10.78019458591564</v>
+        <v>10.66116208796447</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1088444932213261</v>
+        <v>0.5424669597828213</v>
       </c>
     </row>
     <row r="49">
@@ -1697,13 +1739,13 @@
         <v>5.648058338900022</v>
       </c>
       <c r="B49" t="n">
-        <v>1.726745412382504</v>
+        <v>1.722962618340183</v>
       </c>
       <c r="C49" t="n">
-        <v>10.77597884219677</v>
+        <v>10.65279043062301</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1126745412382504</v>
+        <v>0.5614813091700914</v>
       </c>
     </row>
     <row r="50">
@@ -1711,13 +1753,13 @@
         <v>5.768229792919171</v>
       </c>
       <c r="B50" t="n">
-        <v>1.765904944561526</v>
+        <v>1.761838082666008</v>
       </c>
       <c r="C50" t="n">
-        <v>10.77166854240189</v>
+        <v>10.6442323658768</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1165904944561527</v>
+        <v>0.5809190413330041</v>
       </c>
     </row>
     <row r="51">
@@ -1725,13 +1767,13 @@
         <v>5.88840124693832</v>
       </c>
       <c r="B51" t="n">
-        <v>1.805942230512892</v>
+        <v>1.801578713207567</v>
       </c>
       <c r="C51" t="n">
-        <v>10.76726162802317</v>
+        <v>10.63548384299412</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1205942230512892</v>
+        <v>0.6007893566037834</v>
       </c>
     </row>
     <row r="52">
@@ -1739,13 +1781,13 @@
         <v>6.00857270095747</v>
       </c>
       <c r="B52" t="n">
-        <v>1.846876510995397</v>
+        <v>1.842203245872542</v>
       </c>
       <c r="C52" t="n">
-        <v>10.76275598122533</v>
+        <v>10.62654073744258</v>
       </c>
       <c r="D52" t="n">
-        <v>0.1246876510995397</v>
+        <v>0.6211016229362709</v>
       </c>
     </row>
     <row r="53">
@@ -1753,13 +1795,13 @@
         <v>6.128744154976619</v>
       </c>
       <c r="B53" t="n">
-        <v>1.888727565764072</v>
+        <v>1.883730751811854</v>
       </c>
       <c r="C53" t="n">
-        <v>10.75814942484564</v>
+        <v>10.6173988508892</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1288727565764072</v>
+        <v>0.6418653759059271</v>
       </c>
     </row>
     <row r="54">
@@ -1767,13 +1809,13 @@
         <v>6.248915608995769</v>
       </c>
       <c r="B54" t="n">
-        <v>1.931515713570179</v>
+        <v>1.926180637419661</v>
       </c>
       <c r="C54" t="n">
-        <v>10.75343972239392</v>
+        <v>10.60805391120036</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1331515713570179</v>
+        <v>0.6630903187098307</v>
       </c>
     </row>
     <row r="55">
@@ -1781,13 +1823,13 @@
         <v>6.369087063014918</v>
       </c>
       <c r="B55" t="n">
-        <v>1.975261812161213</v>
+        <v>1.969572644333358</v>
       </c>
       <c r="C55" t="n">
-        <v>10.74862457805251</v>
+        <v>10.59850157244184</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1375261812161213</v>
+        <v>0.6847863221666788</v>
       </c>
     </row>
     <row r="56">
@@ -1795,13 +1837,13 @@
         <v>6.489258517034068</v>
       </c>
       <c r="B56" t="n">
-        <v>2.0199872582809</v>
+        <v>2.013926849433574</v>
       </c>
       <c r="C56" t="n">
-        <v>10.74370163667634</v>
+        <v>10.58873741487879</v>
       </c>
       <c r="D56" t="n">
-        <v>0.14199872582809</v>
+        <v>0.7069634247167871</v>
       </c>
     </row>
     <row r="57">
@@ -1809,13 +1851,13 @@
         <v>6.609429971053217</v>
       </c>
       <c r="B57" t="n">
-        <v>2.065713987669201</v>
+        <v>2.059263664844178</v>
       </c>
       <c r="C57" t="n">
-        <v>10.73866848379285</v>
+        <v>10.57875694497575</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1465713987669201</v>
+        <v>0.7296318324220892</v>
       </c>
     </row>
     <row r="58">
@@ -1823,13 +1865,13 @@
         <v>6.729601425072366</v>
       </c>
       <c r="B58" t="n">
-        <v>2.112464475062307</v>
+        <v>2.105603837932275</v>
       </c>
       <c r="C58" t="n">
-        <v>10.73352264560204</v>
+        <v>10.56855559539664</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1512464475062307</v>
+        <v>0.7528019189661375</v>
       </c>
     </row>
     <row r="59">
@@ -1837,13 +1879,13 @@
         <v>6.849772879091516</v>
       </c>
       <c r="B59" t="n">
-        <v>2.160261734192643</v>
+        <v>2.152968451308206</v>
       </c>
       <c r="C59" t="n">
-        <v>10.72826158897645</v>
+        <v>10.55812872500475</v>
       </c>
       <c r="D59" t="n">
-        <v>0.1560261734192643</v>
+        <v>0.7764842256541031</v>
       </c>
     </row>
     <row r="60">
@@ -1851,13 +1893,13 @@
         <v>6.969944333110665</v>
       </c>
       <c r="B60" t="n">
-        <v>2.209129317788866</v>
+        <v>2.20137892282555</v>
       </c>
       <c r="C60" t="n">
-        <v>10.72288272146118</v>
+        <v>10.54747161886276</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1609129317788866</v>
+        <v>0.8006894614127749</v>
       </c>
     </row>
     <row r="61">
@@ -1865,13 +1907,13 @@
         <v>7.090115787129815</v>
       </c>
       <c r="B61" t="n">
-        <v>2.259091317575866</v>
+        <v>2.250857005581121</v>
       </c>
       <c r="C61" t="n">
-        <v>10.71738339127385</v>
+        <v>10.53657948823273</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1659091317575866</v>
+        <v>0.8254285027905606</v>
       </c>
     </row>
     <row r="62">
@@ -1879,13 +1921,13 @@
         <v>7.210287241148964</v>
       </c>
       <c r="B62" t="n">
-        <v>2.310172364274765</v>
+        <v>2.301424787914971</v>
       </c>
       <c r="C62" t="n">
-        <v>10.71176088730465</v>
+        <v>10.5254474705761</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1710172364274765</v>
+        <v>0.8507123939574859</v>
       </c>
     </row>
     <row r="63">
@@ -1893,13 +1935,13 @@
         <v>7.330458695168113</v>
       </c>
       <c r="B63" t="n">
-        <v>2.362397627602918</v>
+        <v>2.35310469341039</v>
       </c>
       <c r="C63" t="n">
-        <v>10.70601243911631</v>
+        <v>10.51407062955369</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1762397627602918</v>
+        <v>0.876552346705195</v>
       </c>
     </row>
     <row r="64">
@@ -1907,13 +1949,13 @@
         <v>7.450630149187263</v>
       </c>
       <c r="B64" t="n">
-        <v>2.415792816273911</v>
+        <v>2.405919480893902</v>
       </c>
       <c r="C64" t="n">
-        <v>10.70013521694409</v>
+        <v>10.5024439550257</v>
       </c>
       <c r="D64" t="n">
-        <v>0.1815792816273911</v>
+        <v>0.9029597404469512</v>
       </c>
     </row>
     <row r="65">
@@ -1921,13 +1963,13 @@
         <v>7.570801603206412</v>
       </c>
       <c r="B65" t="n">
-        <v>2.470384177997564</v>
+        <v>2.459892244435271</v>
       </c>
       <c r="C65" t="n">
-        <v>10.69412633169582</v>
+        <v>10.49056236305172</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1870384177997564</v>
+        <v>0.9299461222176355</v>
       </c>
     </row>
     <row r="66">
@@ -1935,13 +1977,13 @@
         <v>7.690973057225562</v>
       </c>
       <c r="B66" t="n">
-        <v>2.52619849947993</v>
+        <v>2.515046413347494</v>
       </c>
       <c r="C66" t="n">
-        <v>10.68798283495186</v>
+        <v>10.47842069589072</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1926198499479931</v>
+        <v>0.9575232066737471</v>
       </c>
     </row>
     <row r="67">
@@ -1949,13 +1991,13 @@
         <v>7.811144511244711</v>
       </c>
       <c r="B67" t="n">
-        <v>2.583263106423293</v>
+        <v>2.571405752186809</v>
       </c>
       <c r="C67" t="n">
-        <v>10.68170171896512</v>
+        <v>10.46601372200103</v>
       </c>
       <c r="D67" t="n">
-        <v>0.1983263106423294</v>
+        <v>0.9857028760934043</v>
       </c>
     </row>
     <row r="68">
@@ -1963,13 +2005,13 @@
         <v>7.931315965263861</v>
       </c>
       <c r="B68" t="n">
-        <v>2.641605863526171</v>
+        <v>2.628994360752686</v>
       </c>
       <c r="C68" t="n">
-        <v>10.67527991666105</v>
+        <v>10.45333613604039</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2041605863526171</v>
+        <v>1.014497180376343</v>
       </c>
     </row>
     <row r="69">
@@ -1977,13 +2019,13 @@
         <v>8.05148741928301</v>
       </c>
       <c r="B69" t="n">
-        <v>2.701255174483312</v>
+        <v>2.687836674087838</v>
       </c>
       <c r="C69" t="n">
-        <v>10.66871430163767</v>
+        <v>10.44038255886591</v>
       </c>
       <c r="D69" t="n">
-        <v>0.2101255174483312</v>
+        <v>1.043918337043919</v>
       </c>
     </row>
     <row r="70">
@@ -1991,13 +2033,13 @@
         <v>8.171658873302158</v>
       </c>
       <c r="B70" t="n">
-        <v>2.762239981985698</v>
+        <v>2.747950765859806</v>
       </c>
       <c r="C70" t="n">
-        <v>10.66200168816551</v>
+        <v>10.4271490117311</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2162239981985699</v>
+        <v>1.073975382929903</v>
       </c>
     </row>
     <row r="71">
@@ -2005,13 +2047,13 @@
         <v>8.291830327321309</v>
       </c>
       <c r="B71" t="n">
-        <v>2.824589767720546</v>
+        <v>2.809351199467555</v>
       </c>
       <c r="C71" t="n">
-        <v>10.65513883118767</v>
+        <v>10.4136322886418</v>
       </c>
       <c r="D71" t="n">
-        <v>0.2224589767720547</v>
+        <v>1.104675599733777</v>
       </c>
     </row>
     <row r="72">
@@ -2019,13 +2061,13 @@
         <v>8.412001781340457</v>
       </c>
       <c r="B72" t="n">
-        <v>2.888334552371301</v>
+        <v>2.872067860694693</v>
       </c>
       <c r="C72" t="n">
-        <v>10.64812242631979</v>
+        <v>10.39982581052623</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2288334552371302</v>
+        <v>1.136033930347347</v>
       </c>
     </row>
     <row r="73">
@@ -2033,13 +2075,13 @@
         <v>8.532173235359608</v>
       </c>
       <c r="B73" t="n">
-        <v>2.953504895617645</v>
+        <v>2.936131375063282</v>
       </c>
       <c r="C73" t="n">
-        <v>10.64094910985005</v>
+        <v>10.38572283546616</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2353504895617646</v>
+        <v>1.168065687531641</v>
       </c>
     </row>
     <row r="74">
@@ -2047,13 +2089,13 @@
         <v>8.652344689378756</v>
       </c>
       <c r="B74" t="n">
-        <v>3.020131896135487</v>
+        <v>3.001572729412429</v>
       </c>
       <c r="C74" t="n">
-        <v>10.63361545873919</v>
+        <v>10.37131654200289</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2420131896135488</v>
+        <v>1.200786364706214</v>
       </c>
     </row>
     <row r="75">
@@ -2061,13 +2103,13 @@
         <v>8.772516143397906</v>
       </c>
       <c r="B75" t="n">
-        <v>3.088247191596974</v>
+        <v>3.068423271898298</v>
       </c>
       <c r="C75" t="n">
-        <v>10.62611799062048</v>
+        <v>10.35660002913714</v>
       </c>
       <c r="D75" t="n">
-        <v>0.2488247191596975</v>
+        <v>1.234211635949149</v>
       </c>
     </row>
     <row r="76">
@@ -2075,13 +2117,13 @@
         <v>8.892687597417055</v>
       </c>
       <c r="B76" t="n">
-        <v>3.157882958670482</v>
+        <v>3.136714711994103</v>
       </c>
       <c r="C76" t="n">
-        <v>10.61845316379974</v>
+        <v>10.34156631632917</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2557882958670483</v>
+        <v>1.268357355997052</v>
       </c>
     </row>
     <row r="77">
@@ -2089,13 +2131,13 @@
         <v>9.012859051436205</v>
       </c>
       <c r="B77" t="n">
-        <v>3.229071913020621</v>
+        <v>3.206479120490112</v>
       </c>
       <c r="C77" t="n">
-        <v>10.61061737725534</v>
+        <v>10.32620834349867</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2629071913020622</v>
+        <v>1.303239560245056</v>
       </c>
     </row>
     <row r="78">
@@ -2103,13 +2145,13 @@
         <v>9.133030505455354</v>
       </c>
       <c r="B78" t="n">
-        <v>3.301847309308233</v>
+        <v>3.277748929493641</v>
       </c>
       <c r="C78" t="n">
-        <v>10.6026069706382</v>
+        <v>10.31051897102482</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2701847309308234</v>
+        <v>1.33887446474682</v>
       </c>
     </row>
     <row r="79">
@@ -2117,13 +2159,13 @@
         <v>9.253201959474504</v>
       </c>
       <c r="B79" t="n">
-        <v>3.376242941190394</v>
+        <v>3.350556932429062</v>
       </c>
       <c r="C79" t="n">
-        <v>10.59441822427178</v>
+        <v>10.2944909797463</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2776242941190394</v>
+        <v>1.375278466214531</v>
       </c>
     </row>
     <row r="80">
@@ -2131,13 +2173,13 @@
         <v>9.373373413493653</v>
       </c>
       <c r="B80" t="n">
-        <v>3.452293141320408</v>
+        <v>3.424936284037797</v>
       </c>
       <c r="C80" t="n">
-        <v>10.58604735915209</v>
+        <v>10.27811707096124</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2852293141320409</v>
+        <v>1.412468142018898</v>
       </c>
     </row>
     <row r="81">
@@ -2145,13 +2187,13 @@
         <v>9.493544867512803</v>
       </c>
       <c r="B81" t="n">
-        <v>3.530032781347817</v>
+        <v>3.500920500378322</v>
       </c>
       <c r="C81" t="n">
-        <v>10.57749053694767</v>
+        <v>10.26138986642726</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2930032781347819</v>
+        <v>1.450460250189161</v>
       </c>
     </row>
     <row r="82">
@@ -2159,13 +2201,13 @@
         <v>9.613716321531951</v>
       </c>
       <c r="B82" t="n">
-        <v>3.609497271918393</v>
+        <v>3.578543458826161</v>
       </c>
       <c r="C82" t="n">
-        <v>10.56874385999962</v>
+        <v>10.24430190836146</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3009497271918395</v>
+        <v>1.48927172941308</v>
       </c>
     </row>
     <row r="83">
@@ -2173,13 +2215,13 @@
         <v>9.733887775551102</v>
       </c>
       <c r="B83" t="n">
-        <v>3.690722562674142</v>
+        <v>3.657839398073895</v>
       </c>
       <c r="C83" t="n">
-        <v>10.55980337132158</v>
+        <v>10.22684565944041</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3090722562674144</v>
+        <v>1.528919699036948</v>
       </c>
     </row>
     <row r="84">
@@ -2187,13 +2229,13 @@
         <v>9.85405922957025</v>
       </c>
       <c r="B84" t="n">
-        <v>3.773745142253297</v>
+        <v>3.738842918131154</v>
       </c>
       <c r="C84" t="n">
-        <v>10.55066505459975</v>
+        <v>10.20901350280017</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3173745142253299</v>
+        <v>1.569421459065577</v>
       </c>
     </row>
     <row r="85">
@@ -2201,13 +2243,13 @@
         <v>9.974230683589401</v>
       </c>
       <c r="B85" t="n">
-        <v>3.858602038290333</v>
+        <v>3.821588980324621</v>
       </c>
       <c r="C85" t="n">
-        <v>10.54132483419287</v>
+        <v>10.19079774203627</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3258602038290334</v>
+        <v>1.610794490162311</v>
       </c>
     </row>
     <row r="86">
@@ -2215,13 +2257,13 @@
         <v>10.09440213760855</v>
       </c>
       <c r="B86" t="n">
-        <v>3.945330817415946</v>
+        <v>3.906112907298029</v>
       </c>
       <c r="C86" t="n">
-        <v>10.5317785751322</v>
+        <v>10.17219060120371</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3345330817415948</v>
+        <v>1.653056453649015</v>
       </c>
     </row>
     <row r="87">
@@ -2229,13 +2271,13 @@
         <v>10.2145735916277</v>
       </c>
       <c r="B87" t="n">
-        <v>4.033969585257077</v>
+        <v>3.992450383012168</v>
       </c>
       <c r="C87" t="n">
-        <v>10.52202208312159</v>
+        <v>10.15318422481699</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3433969585257078</v>
+        <v>1.696225191506084</v>
       </c>
     </row>
     <row r="88">
@@ -2243,13 +2285,13 @@
         <v>10.33474504564685</v>
       </c>
       <c r="B88" t="n">
-        <v>4.124556986436888</v>
+        <v>4.080637452744874</v>
       </c>
       <c r="C88" t="n">
-        <v>10.51205110453739</v>
+        <v>10.13377067785008</v>
       </c>
       <c r="D88" t="n">
-        <v>0.352455698643689</v>
+        <v>1.740318726372437</v>
       </c>
     </row>
     <row r="89">
@@ -2257,13 +2299,13 @@
         <v>10.454916499666</v>
       </c>
       <c r="B89" t="n">
-        <v>4.217132204574782</v>
+        <v>4.17071052309104</v>
       </c>
       <c r="C89" t="n">
-        <v>10.50186132642854</v>
+        <v>10.1139419457364</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3617132204574784</v>
+        <v>1.78535526154552</v>
       </c>
     </row>
     <row r="90">
@@ -2271,13 +2313,13 @@
         <v>10.57508795368515</v>
       </c>
       <c r="B90" t="n">
-        <v>4.311734962286391</v>
+        <v>4.262706361962605</v>
       </c>
       <c r="C90" t="n">
-        <v>10.49144837651649</v>
+        <v>10.09368993436889</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3711734962286392</v>
+        <v>1.831353180981303</v>
       </c>
     </row>
     <row r="91">
@@ -2285,13 +2327,13 @@
         <v>10.6952594077043</v>
       </c>
       <c r="B91" t="n">
-        <v>4.408405521183576</v>
+        <v>4.35666209858857</v>
       </c>
       <c r="C91" t="n">
-        <v>10.48080782319525</v>
+        <v>10.07300647009994</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3808405521183579</v>
+        <v>1.878331049294285</v>
       </c>
     </row>
     <row r="92">
@@ -2299,13 +2341,13 @@
         <v>10.81543086172345</v>
       </c>
       <c r="B92" t="n">
-        <v>4.507181902758877</v>
+        <v>4.452615223514976</v>
       </c>
       <c r="C92" t="n">
-        <v>10.46993548142935</v>
+        <v>10.05188329974144</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3907181902758877</v>
+        <v>1.926307611757488</v>
       </c>
     </row>
     <row r="93">
@@ -2313,13 +2355,13 @@
         <v>10.9356023157426</v>
       </c>
       <c r="B93" t="n">
-        <v>4.608090192635198</v>
+        <v>4.550603588604926</v>
       </c>
       <c r="C93" t="n">
-        <v>10.45882847996755</v>
+        <v>10.03031209056472</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4008090192635199</v>
+        <v>1.975301794302463</v>
       </c>
     </row>
     <row r="94">
@@ -2327,13 +2369,13 @@
         <v>11.05577376976174</v>
       </c>
       <c r="B94" t="n">
-        <v>4.711176177128282</v>
+        <v>4.650665407038568</v>
       </c>
       <c r="C94" t="n">
-        <v>10.44748177909829</v>
+        <v>10.00828443030064</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4111176177128283</v>
+        <v>2.025332703519284</v>
       </c>
     </row>
     <row r="95">
@@ -2341,13 +2383,13 @@
         <v>11.17594522378089</v>
       </c>
       <c r="B95" t="n">
-        <v>4.816489983497782</v>
+        <v>4.752839253313109</v>
       </c>
       <c r="C95" t="n">
-        <v>10.43588986130118</v>
+        <v>9.985791827139504</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4216489983497782</v>
+        <v>2.076419626656555</v>
       </c>
     </row>
     <row r="96">
@@ -2355,13 +2397,13 @@
         <v>11.29611667780004</v>
       </c>
       <c r="B96" t="n">
-        <v>4.924082553331365</v>
+        <v>4.857164063242799</v>
       </c>
       <c r="C96" t="n">
-        <v>10.42404711942254</v>
+        <v>9.962825709731094</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4324082553331365</v>
+        <v>2.128582031621399</v>
       </c>
     </row>
     <row r="97">
@@ -2369,13 +2411,13 @@
         <v>11.41628813181919</v>
       </c>
       <c r="B97" t="n">
-        <v>5.034005642544726</v>
+        <v>4.96367913395895</v>
       </c>
       <c r="C97" t="n">
-        <v>10.41194785667541</v>
+        <v>9.939377427184683</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4434005642544727</v>
+        <v>2.181839566979475</v>
       </c>
     </row>
     <row r="98">
@@ -2383,13 +2425,13 @@
         <v>11.53645958583834</v>
       </c>
       <c r="B98" t="n">
-        <v>5.146311821381573</v>
+        <v>5.072424123909917</v>
       </c>
       <c r="C98" t="n">
-        <v>10.3995862866395</v>
+        <v>9.915438249069012</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4546311821381573</v>
+        <v>2.236212061954958</v>
       </c>
     </row>
     <row r="99">
@@ -2397,13 +2439,13 @@
         <v>11.65663103985749</v>
       </c>
       <c r="B99" t="n">
-        <v>5.261054474413638</v>
+        <v>5.183439052861115</v>
       </c>
       <c r="C99" t="n">
-        <v>10.38695653326126</v>
+        <v>9.890999365412309</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4661054474413638</v>
+        <v>2.291719526430557</v>
       </c>
     </row>
     <row r="100">
@@ -2411,13 +2453,13 @@
         <v>11.77680249387664</v>
       </c>
       <c r="B100" t="n">
-        <v>5.378287800540667</v>
+        <v>5.296764301895002</v>
       </c>
       <c r="C100" t="n">
-        <v>10.37405263085384</v>
+        <v>9.866051886702273</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4778287800540668</v>
+        <v>2.348382150947501</v>
       </c>
     </row>
     <row r="101">
@@ -2425,13 +2467,13 @@
         <v>11.89697394789579</v>
       </c>
       <c r="B101" t="n">
-        <v>5.498066812990434</v>
+        <v>5.412440613411099</v>
       </c>
       <c r="C101" t="n">
-        <v>10.36086852409707</v>
+        <v>9.840586843886083</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4898066812990434</v>
+        <v>2.406220306705549</v>
       </c>
     </row>
     <row r="102">
@@ -2439,13 +2481,13 @@
         <v>12.01714540191494</v>
       </c>
       <c r="B102" t="n">
-        <v>5.62044733931872</v>
+        <v>5.530509091125969</v>
       </c>
       <c r="C102" t="n">
-        <v>10.34739806803752</v>
+        <v>9.814595188370397</v>
       </c>
       <c r="D102" t="n">
-        <v>0.5020447339318721</v>
+        <v>2.465254545562984</v>
       </c>
     </row>
     <row r="103">
@@ -2453,13 +2495,13 @@
         <v>12.13731685593409</v>
       </c>
       <c r="B103" t="n">
-        <v>5.74548602140934</v>
+        <v>5.651011200073234</v>
       </c>
       <c r="C103" t="n">
-        <v>10.33363502808843</v>
+        <v>9.78806779202135</v>
       </c>
       <c r="D103" t="n">
-        <v>0.514548602140934</v>
+        <v>2.525505600036617</v>
       </c>
     </row>
     <row r="104">
@@ -2467,13 +2509,13 @@
         <v>12.25748830995324</v>
       </c>
       <c r="B104" t="n">
-        <v>5.873240315474117</v>
+        <v>5.773988766603564</v>
       </c>
       <c r="C104" t="n">
-        <v>10.31957308002978</v>
+        <v>9.760995447164555</v>
       </c>
       <c r="D104" t="n">
-        <v>0.5273240315474117</v>
+        <v>2.586994383301782</v>
       </c>
     </row>
     <row r="105">
@@ -2481,13 +2523,13 @@
         <v>12.37765976397239</v>
       </c>
       <c r="B105" t="n">
-        <v>6.003768492052901</v>
+        <v>5.899483978384682</v>
       </c>
       <c r="C105" t="n">
-        <v>10.30520581000823</v>
+        <v>9.733368866585106</v>
       </c>
       <c r="D105" t="n">
-        <v>0.5403768492052901</v>
+        <v>2.649741989192341</v>
       </c>
     </row>
     <row r="106">
@@ -2495,13 +2537,13 @@
         <v>12.49783121799154</v>
       </c>
       <c r="B106" t="n">
-        <v>6.137129636013555</v>
+        <v>6.027539384401363</v>
       </c>
       <c r="C106" t="n">
-        <v>10.29052671453715</v>
+        <v>9.705178683527571</v>
       </c>
       <c r="D106" t="n">
-        <v>0.5537129636013555</v>
+        <v>2.713769692200681</v>
       </c>
     </row>
     <row r="107">
@@ -2509,13 +2551,13 @@
         <v>12.61800267201069</v>
       </c>
       <c r="B107" t="n">
-        <v>6.273383646551968</v>
+        <v>6.158197894955436</v>
       </c>
       <c r="C107" t="n">
-        <v>10.27552920049662</v>
+        <v>9.676415451695993</v>
       </c>
       <c r="D107" t="n">
-        <v>0.5673383646551968</v>
+        <v>2.779098947477718</v>
       </c>
     </row>
     <row r="108">
@@ -2523,13 +2565,13 @@
         <v>12.73817412602984</v>
       </c>
       <c r="B108" t="n">
-        <v>6.412591237192043</v>
+        <v>6.291502781665779</v>
       </c>
       <c r="C108" t="n">
-        <v>10.26020658513343</v>
+        <v>9.647069645253904</v>
       </c>
       <c r="D108" t="n">
-        <v>0.5812591237192042</v>
+        <v>2.84575139083289</v>
       </c>
     </row>
     <row r="109">
@@ -2537,13 +2579,13 @@
         <v>12.85834558004899</v>
       </c>
       <c r="B109" t="n">
-        <v>6.554813935785708</v>
+        <v>6.427497677468327</v>
       </c>
       <c r="C109" t="n">
-        <v>10.24455209606106</v>
+        <v>9.617131658824304</v>
       </c>
       <c r="D109" t="n">
-        <v>0.5954813935785708</v>
+        <v>2.913748838734163</v>
       </c>
     </row>
     <row r="110">
@@ -2551,13 +2593,13 @@
         <v>12.97851703406814</v>
       </c>
       <c r="B110" t="n">
-        <v>6.700114084512903</v>
+        <v>6.566226576616057</v>
       </c>
       <c r="C110" t="n">
-        <v>10.2285588712597</v>
+        <v>9.586591807489675</v>
       </c>
       <c r="D110" t="n">
-        <v>0.6100114084512902</v>
+        <v>2.983113288308028</v>
       </c>
     </row>
     <row r="111">
@@ -2565,13 +2607,13 @@
         <v>13.09868848808729</v>
       </c>
       <c r="B111" t="n">
-        <v>6.848554839881597</v>
+        <v>6.707733834679011</v>
       </c>
       <c r="C111" t="n">
-        <v>10.21221995907626</v>
+        <v>9.555440326791976</v>
       </c>
       <c r="D111" t="n">
-        <v>0.6248554839881597</v>
+        <v>3.053866917339505</v>
       </c>
     </row>
     <row r="112">
@@ -2579,13 +2621,13 @@
         <v>13.21885994210643</v>
       </c>
       <c r="B112" t="n">
-        <v>7.000200172727769</v>
+        <v>6.85206416854427</v>
       </c>
       <c r="C112" t="n">
-        <v>10.19552831822434</v>
+        <v>9.523667372732644</v>
       </c>
       <c r="D112" t="n">
-        <v>0.6400200172727768</v>
+        <v>3.126032084272135</v>
       </c>
     </row>
     <row r="113">
@@ -2593,13 +2635,13 @@
         <v>13.33903139612558</v>
       </c>
       <c r="B113" t="n">
-        <v>7.155114868215426</v>
+        <v>6.99926265641598</v>
       </c>
       <c r="C113" t="n">
-        <v>10.17847681778425</v>
+        <v>9.491263021772596</v>
       </c>
       <c r="D113" t="n">
-        <v>0.6555114868215425</v>
+        <v>3.19963132820799</v>
       </c>
     </row>
     <row r="114">
@@ -2607,13 +2649,13 @@
         <v>13.45920285014473</v>
       </c>
       <c r="B114" t="n">
-        <v>7.313364525836587</v>
+        <v>7.149374737815328</v>
       </c>
       <c r="C114" t="n">
-        <v>10.161058237203</v>
+        <v>9.458217270832224</v>
       </c>
       <c r="D114" t="n">
-        <v>0.6713364525836587</v>
+        <v>3.274687368907664</v>
       </c>
     </row>
     <row r="115">
@@ -2621,13 +2663,13 @@
         <v>13.57937430416388</v>
       </c>
       <c r="B115" t="n">
-        <v>7.475015559411297</v>
+        <v>7.302446213580561</v>
       </c>
       <c r="C115" t="n">
-        <v>10.14326526629431</v>
+        <v>9.4245200372914</v>
       </c>
       <c r="D115" t="n">
-        <v>0.6875015559411297</v>
+        <v>3.351223106790281</v>
       </c>
     </row>
     <row r="116">
@@ -2635,13 +2677,13 @@
         <v>13.69954575818303</v>
       </c>
       <c r="B116" t="n">
-        <v>7.640135197087615</v>
+        <v>7.458523245866972</v>
       </c>
       <c r="C116" t="n">
-        <v>10.1250905052386</v>
+        <v>9.390161158989473</v>
       </c>
       <c r="D116" t="n">
-        <v>0.7040135197087614</v>
+        <v>3.429261622933486</v>
       </c>
     </row>
     <row r="117">
@@ -2649,13 +2691,13 @@
         <v>13.81971721220218</v>
       </c>
       <c r="B117" t="n">
-        <v>7.808791481341625</v>
+        <v>7.61765235814691</v>
       </c>
       <c r="C117" t="n">
-        <v>10.10652646458301</v>
+        <v>9.355130394225272</v>
       </c>
       <c r="D117" t="n">
-        <v>0.7208791481341625</v>
+        <v>3.508826179073455</v>
       </c>
     </row>
     <row r="118">
@@ -2663,13 +2705,13 @@
         <v>13.93988866622133</v>
       </c>
       <c r="B118" t="n">
-        <v>7.981053268977424</v>
+        <v>7.779880435209774</v>
       </c>
       <c r="C118" t="n">
-        <v>10.08756556524136</v>
+        <v>9.3194174217571</v>
       </c>
       <c r="D118" t="n">
-        <v>0.7381053268977422</v>
+        <v>3.589940217604887</v>
       </c>
     </row>
     <row r="119">
@@ -2677,13 +2719,13 @@
         <v>14.06006012024048</v>
       </c>
       <c r="B119" t="n">
-        <v>8.156990231127136</v>
+        <v>7.945254723162019</v>
       </c>
       <c r="C119" t="n">
-        <v>10.0682001384942</v>
+        <v>9.283011840802741</v>
       </c>
       <c r="D119" t="n">
-        <v>0.7556990231127134</v>
+        <v>3.672627361581009</v>
       </c>
     </row>
     <row r="120">
@@ -2691,13 +2733,13 @@
         <v>14.18023157425963</v>
       </c>
       <c r="B120" t="n">
-        <v>8.336672853250896</v>
+        <v>8.113822829427141</v>
       </c>
       <c r="C120" t="n">
-        <v>10.04842242598878</v>
+        <v>9.24590317103946</v>
       </c>
       <c r="D120" t="n">
-        <v>0.7736672853250894</v>
+        <v>3.756911414713571</v>
       </c>
     </row>
     <row r="121">
@@ -2705,13 +2747,13 @@
         <v>14.30040302827878</v>
       </c>
       <c r="B121" t="n">
-        <v>8.520172435136869</v>
+        <v>8.285632722745705</v>
       </c>
       <c r="C121" t="n">
-        <v>10.02822457973903</v>
+        <v>9.208080852603992</v>
       </c>
       <c r="D121" t="n">
-        <v>0.7920172435136867</v>
+        <v>3.842816361372853</v>
       </c>
     </row>
     <row r="122">
@@ -2719,13 +2761,13 @@
         <v>14.42057448229793</v>
       </c>
       <c r="B122" t="n">
-        <v>8.707561090901226</v>
+        <v>8.460732733175313</v>
       </c>
       <c r="C122" t="n">
-        <v>10.00759866212563</v>
+        <v>9.169534246092557</v>
       </c>
       <c r="D122" t="n">
-        <v>0.8107561090901226</v>
+        <v>3.930366366587656</v>
       </c>
     </row>
     <row r="123">
@@ -2733,13 +2775,13 @@
         <v>14.54074593631708</v>
       </c>
       <c r="B123" t="n">
-        <v>8.898911748988176</v>
+        <v>8.639171552090627</v>
       </c>
       <c r="C123" t="n">
-        <v>9.986536645895915</v>
+        <v>9.130252632560847</v>
       </c>
       <c r="D123" t="n">
-        <v>0.8298911748988174</v>
+        <v>4.019585776045314</v>
       </c>
     </row>
     <row r="124">
@@ -2747,13 +2789,13 @@
         <v>14.66091739033623</v>
       </c>
       <c r="B124" t="n">
-        <v>9.094298152169923</v>
+        <v>8.820998232183356</v>
       </c>
       <c r="C124" t="n">
-        <v>9.965030414163968</v>
+        <v>9.09022521352404</v>
       </c>
       <c r="D124" t="n">
-        <v>0.8494298152169922</v>
+        <v>4.110499116091678</v>
       </c>
     </row>
     <row r="125">
@@ -2761,13 +2803,13 @@
         <v>14.78108884435538</v>
       </c>
       <c r="B125" t="n">
-        <v>9.293794857546716</v>
+        <v>9.006262187462269</v>
       </c>
       <c r="C125" t="n">
-        <v>9.94307176041055</v>
+        <v>9.049441110956785</v>
       </c>
       <c r="D125" t="n">
-        <v>0.8693794857546715</v>
+        <v>4.203131093731135</v>
       </c>
     </row>
     <row r="126">
@@ -2775,13 +2817,13 @@
         <v>14.90126029837453</v>
       </c>
       <c r="B126" t="n">
-        <v>9.497477236546805</v>
+        <v>9.195013193253178</v>
       </c>
       <c r="C126" t="n">
-        <v>9.920652388483139</v>
+        <v>9.007889367293213</v>
       </c>
       <c r="D126" t="n">
-        <v>0.8897477236546805</v>
+        <v>4.297506596626588</v>
       </c>
     </row>
     <row r="127">
@@ -2789,13 +2831,13 @@
         <v>15.02143175239368</v>
       </c>
       <c r="B127" t="n">
-        <v>9.705421474926471</v>
+        <v>9.387179326913413</v>
       </c>
       <c r="C127" t="n">
-        <v>9.897763912595916</v>
+        <v>8.965585815620935</v>
       </c>
       <c r="D127" t="n">
-        <v>0.9105421474926469</v>
+        <v>4.393589663456707</v>
       </c>
     </row>
     <row r="128">
@@ -2803,13 +2845,13 @@
         <v>15.14160320641282</v>
       </c>
       <c r="B128" t="n">
-        <v>9.917704572770003</v>
+        <v>9.58268245833062</v>
       </c>
       <c r="C128" t="n">
-        <v>9.874397857329766</v>
+        <v>8.922547655543143</v>
       </c>
       <c r="D128" t="n">
-        <v>0.931770457277</v>
+        <v>4.49134122916531</v>
       </c>
     </row>
     <row r="129">
@@ -2817,13 +2859,13 @@
         <v>15.26177466043197</v>
       </c>
       <c r="B129" t="n">
-        <v>10.13440434448972</v>
+        <v>9.781617999221385</v>
       </c>
       <c r="C129" t="n">
-        <v>9.85054565763228</v>
+        <v>8.878753883075387</v>
       </c>
       <c r="D129" t="n">
-        <v>0.953440434448972</v>
+        <v>4.590808999610693</v>
       </c>
     </row>
     <row r="130">
@@ -2831,13 +2873,13 @@
         <v>15.38194611445112</v>
       </c>
       <c r="B130" t="n">
-        <v>10.35559941882596</v>
+        <v>9.984077818179493</v>
       </c>
       <c r="C130" t="n">
-        <v>9.826198658817752</v>
+        <v>8.834184274218098</v>
       </c>
       <c r="D130" t="n">
-        <v>0.975559941882596</v>
+        <v>4.692038909089747</v>
       </c>
     </row>
     <row r="131">
@@ -2845,13 +2887,13 @@
         <v>15.50211756847027</v>
       </c>
       <c r="B131" t="n">
-        <v>10.58136923884707</v>
+        <v>10.19014953376624</v>
       </c>
       <c r="C131" t="n">
-        <v>9.801348116567185</v>
+        <v>8.78881954057605</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9981369238847069</v>
+        <v>4.795074766883122</v>
       </c>
     </row>
     <row r="132">
@@ -2859,13 +2901,13 @@
         <v>15.62228902248942</v>
       </c>
       <c r="B132" t="n">
-        <v>10.81179406194943</v>
+        <v>10.39991651451044</v>
       </c>
       <c r="C132" t="n">
-        <v>9.775985196928284</v>
+        <v>8.742641329358358</v>
       </c>
       <c r="D132" t="n">
-        <v>1.021179406194943</v>
+        <v>4.89995825725522</v>
       </c>
     </row>
     <row r="133">
@@ -2873,13 +2915,13 @@
         <v>15.74246047650857</v>
       </c>
       <c r="B133" t="n">
-        <v>11.04695495985744</v>
+        <v>10.61345787890838</v>
       </c>
       <c r="C133" t="n">
-        <v>9.750100976315458</v>
+        <v>8.695632223378484</v>
       </c>
       <c r="D133" t="n">
-        <v>1.044695495985743</v>
+        <v>5.006728939454192</v>
       </c>
     </row>
     <row r="134">
@@ -2887,13 +2929,13 @@
         <v>15.86263193052772</v>
       </c>
       <c r="B134" t="n">
-        <v>11.28693381862349</v>
+        <v>10.83084849542389</v>
       </c>
       <c r="C134" t="n">
-        <v>9.723686441509827</v>
+        <v>8.647775741054225</v>
       </c>
       <c r="D134" t="n">
-        <v>1.068693381862349</v>
+        <v>5.115424247711947</v>
       </c>
     </row>
     <row r="135">
@@ -2901,13 +2943,13 @@
         <v>15.98280338454687</v>
       </c>
       <c r="B135" t="n">
-        <v>11.53181333862804</v>
+        <v>11.05215898248829</v>
       </c>
       <c r="C135" t="n">
-        <v>9.69673248965921</v>
+        <v>8.599056336407731</v>
       </c>
       <c r="D135" t="n">
-        <v>1.093181333862803</v>
+        <v>5.226079491244144</v>
       </c>
     </row>
     <row r="136">
@@ -2915,13 +2957,13 @@
         <v>16.10297483856602</v>
       </c>
       <c r="B136" t="n">
-        <v>11.78167703457952</v>
+        <v>11.27745570850039</v>
       </c>
       <c r="C136" t="n">
-        <v>9.669229928278135</v>
+        <v>8.549459399065489</v>
       </c>
       <c r="D136" t="n">
-        <v>1.118167703457951</v>
+        <v>5.338727854250196</v>
       </c>
     </row>
     <row r="137">
@@ -2929,13 +2971,13 @@
         <v>16.22314629258517</v>
       </c>
       <c r="B137" t="n">
-        <v>12.03660923551441</v>
+        <v>11.50680079182654</v>
       </c>
       <c r="C137" t="n">
-        <v>9.64116947524783</v>
+        <v>8.498971254258327</v>
       </c>
       <c r="D137" t="n">
-        <v>1.143660923551441</v>
+        <v>5.45340039591327</v>
       </c>
     </row>
     <row r="138">
@@ -2943,13 +2985,13 @@
         <v>16.34331774660432</v>
       </c>
       <c r="B138" t="n">
-        <v>12.29669508479719</v>
+        <v>11.74025210080056</v>
       </c>
       <c r="C138" t="n">
-        <v>9.612541758816235</v>
+        <v>8.447579162821423</v>
       </c>
       <c r="D138" t="n">
-        <v>1.169669508479719</v>
+        <v>5.570126050400281</v>
       </c>
     </row>
     <row r="139">
@@ -2957,13 +2999,13 @@
         <v>16.46348920062347</v>
       </c>
       <c r="B139" t="n">
-        <v>12.5620205401204</v>
+        <v>11.97786325372381</v>
       </c>
       <c r="C139" t="n">
-        <v>9.583337317597991</v>
+        <v>8.39527132119429</v>
       </c>
       <c r="D139" t="n">
-        <v>1.196202054012039</v>
+        <v>5.688931626861908</v>
       </c>
     </row>
     <row r="140">
@@ -2971,13 +3013,13 @@
         <v>16.58366065464262</v>
       </c>
       <c r="B140" t="n">
-        <v>12.83267237350454</v>
+        <v>12.21968361886514</v>
       </c>
       <c r="C140" t="n">
-        <v>9.553546600574442</v>
+        <v>8.342036861420789</v>
       </c>
       <c r="D140" t="n">
-        <v>1.223267237350454</v>
+        <v>5.809841809432572</v>
       </c>
     </row>
     <row r="141">
@@ -2985,13 +3027,13 @@
         <v>16.70383210866177</v>
       </c>
       <c r="B141" t="n">
-        <v>13.10873817129818</v>
+        <v>12.4657583144609</v>
       </c>
       <c r="C141" t="n">
-        <v>9.523159967093644</v>
+        <v>8.287865851149123</v>
       </c>
       <c r="D141" t="n">
-        <v>1.250873817129817</v>
+        <v>5.932879157230452</v>
       </c>
     </row>
     <row r="142">
@@ -2999,13 +3041,13 @@
         <v>16.82400356268091</v>
       </c>
       <c r="B142" t="n">
-        <v>13.39030633417786</v>
+        <v>12.71612820871495</v>
       </c>
       <c r="C142" t="n">
-        <v>9.492167686870355</v>
+        <v>8.232749293631839</v>
       </c>
       <c r="D142" t="n">
-        <v>1.279030633417785</v>
+        <v>6.058064104357474</v>
       </c>
     </row>
     <row r="143">
@@ -3013,13 +3055,13 @@
         <v>16.94417501670006</v>
       </c>
       <c r="B143" t="n">
-        <v>13.6774660771482</v>
+        <v>12.97082991979866</v>
       </c>
       <c r="C143" t="n">
-        <v>9.46055993998603</v>
+        <v>8.176679127725821</v>
       </c>
       <c r="D143" t="n">
-        <v>1.307746607714819</v>
+        <v>6.185414959899332</v>
       </c>
     </row>
     <row r="144">
@@ -3027,13 +3069,13 @@
         <v>17.06434647071922</v>
       </c>
       <c r="B144" t="n">
-        <v>13.9703074295418</v>
+        <v>13.22989581585092</v>
       </c>
       <c r="C144" t="n">
-        <v>9.428326816888843</v>
+        <v>8.119648227892306</v>
       </c>
       <c r="D144" t="n">
-        <v>1.337030742954179</v>
+        <v>6.314947907925459</v>
       </c>
     </row>
     <row r="145">
@@ -3041,13 +3083,13 @@
         <v>17.18451792473837</v>
       </c>
       <c r="B145" t="n">
-        <v>14.26892123501927</v>
+        <v>13.49335401497809</v>
       </c>
       <c r="C145" t="n">
-        <v>9.395458318393665</v>
+        <v>8.061650404196863</v>
       </c>
       <c r="D145" t="n">
-        <v>1.366892123501926</v>
+        <v>6.446677007489043</v>
       </c>
     </row>
     <row r="146">
@@ -3055,13 +3097,13 @@
         <v>17.30468937875751</v>
       </c>
       <c r="B146" t="n">
-        <v>14.57339915156927</v>
+        <v>13.76122838525405</v>
       </c>
       <c r="C146" t="n">
-        <v>9.361944355682072</v>
+        <v>8.002680402309412</v>
       </c>
       <c r="D146" t="n">
-        <v>1.397339915156926</v>
+        <v>6.580614192627028</v>
       </c>
     </row>
     <row r="147">
@@ -3069,13 +3111,13 @@
         <v>17.42486083277666</v>
       </c>
       <c r="B147" t="n">
-        <v>14.88383365150848</v>
+        <v>14.03353854472023</v>
       </c>
       <c r="C147" t="n">
-        <v>9.327774750302348</v>
+        <v>7.942733903504212</v>
       </c>
       <c r="D147" t="n">
-        <v>1.428383365150847</v>
+        <v>6.716769272360113</v>
       </c>
     </row>
     <row r="148">
@@ -3083,13 +3125,13 @@
         <v>17.54503228679581</v>
       </c>
       <c r="B148" t="n">
-        <v>15.20031802148156</v>
+        <v>14.3102998613855</v>
       </c>
       <c r="C148" t="n">
-        <v>9.292939234169479</v>
+        <v>7.881807524659868</v>
       </c>
       <c r="D148" t="n">
-        <v>1.460031802148155</v>
+        <v>6.855149930692749</v>
       </c>
     </row>
     <row r="149">
@@ -3097,13 +3139,13 @@
         <v>17.66520374081496</v>
       </c>
       <c r="B149" t="n">
-        <v>15.52294636246124</v>
+        <v>14.59152345322627</v>
       </c>
       <c r="C149" t="n">
-        <v>9.257427449565158</v>
+        <v>7.819898818259324</v>
       </c>
       <c r="D149" t="n">
-        <v>1.492294636246122</v>
+        <v>6.995761726613134</v>
       </c>
     </row>
     <row r="150">
@@ -3111,13 +3153,13 @@
         <v>17.78537519483411</v>
       </c>
       <c r="B150" t="n">
-        <v>15.85181358974821</v>
+        <v>14.87721618818644</v>
       </c>
       <c r="C150" t="n">
-        <v>9.221228949137787</v>
+        <v>7.757006272389869</v>
       </c>
       <c r="D150" t="n">
-        <v>1.52518135897482</v>
+        <v>7.138608094093222</v>
       </c>
     </row>
     <row r="151">
@@ -3125,13 +3167,13 @@
         <v>17.90554664885326</v>
       </c>
       <c r="B151" t="n">
-        <v>16.18701543297125</v>
+        <v>15.16738068417746</v>
       </c>
       <c r="C151" t="n">
-        <v>9.184333195902465</v>
+        <v>7.693129310743136</v>
       </c>
       <c r="D151" t="n">
-        <v>1.558701543297124</v>
+        <v>7.28369034208873</v>
       </c>
     </row>
     <row r="152">
@@ -3139,13 +3181,13 @@
         <v>18.02571810287241</v>
       </c>
       <c r="B152" t="n">
-        <v>16.52856457895318</v>
+        <v>15.46201530907823</v>
       </c>
       <c r="C152" t="n">
-        <v>9.146738793417333</v>
+        <v>7.628268292615098</v>
       </c>
       <c r="D152" t="n">
-        <v>1.592856457895318</v>
+        <v>7.431007654539114</v>
       </c>
     </row>
     <row r="153">
@@ -3153,13 +3195,13 @@
         <v>18.14588955689156</v>
       </c>
       <c r="B153" t="n">
-        <v>16.8761345531445</v>
+        <v>15.76111418073518</v>
       </c>
       <c r="C153" t="n">
-        <v>9.10848167682016</v>
+        <v>7.562424512906073</v>
       </c>
       <c r="D153" t="n">
-        <v>1.62761345531445</v>
+        <v>7.58055709036759</v>
       </c>
     </row>
     <row r="154">
@@ -3167,13 +3209,13 @@
         <v>18.26606101091071</v>
       </c>
       <c r="B154" t="n">
-        <v>17.22984850870488</v>
+        <v>16.06466716696224</v>
       </c>
       <c r="C154" t="n">
-        <v>9.069548290610939</v>
+        <v>7.495600202120725</v>
       </c>
       <c r="D154" t="n">
-        <v>1.662984850870488</v>
+        <v>7.732333583481122</v>
       </c>
     </row>
     <row r="155">
@@ -3181,13 +3223,13 @@
         <v>18.38623246492986</v>
       </c>
       <c r="B155" t="n">
-        <v>17.58989768433633</v>
+        <v>16.37265988554087</v>
       </c>
       <c r="C155" t="n">
-        <v>9.02991758509647</v>
+        <v>7.427798526368051</v>
       </c>
       <c r="D155" t="n">
-        <v>1.698989768433633</v>
+        <v>7.886329942770438</v>
       </c>
     </row>
     <row r="156">
@@ -3195,13 +3237,13 @@
         <v>18.50640391894901</v>
       </c>
       <c r="B156" t="n">
-        <v>17.95646606809417</v>
+        <v>16.68507370422001</v>
       </c>
       <c r="C156" t="n">
-        <v>8.989569308664109</v>
+        <v>7.359023587361403</v>
       </c>
       <c r="D156" t="n">
-        <v>1.735646606809417</v>
+        <v>8.042536852110008</v>
       </c>
     </row>
     <row r="157">
@@ -3209,13 +3251,13 @@
         <v>18.62657537296816</v>
       </c>
       <c r="B157" t="n">
-        <v>18.32973039738713</v>
+        <v>17.00188574071612</v>
       </c>
       <c r="C157" t="n">
-        <v>8.948484007781744</v>
+        <v>7.289280422418466</v>
       </c>
       <c r="D157" t="n">
-        <v>1.772973039738714</v>
+        <v>8.200942870358059</v>
       </c>
     </row>
     <row r="158">
@@ -3223,13 +3265,13 @@
         <v>18.74674682698731</v>
       </c>
       <c r="B158" t="n">
-        <v>18.70986015897729</v>
+        <v>17.32306886271313</v>
       </c>
       <c r="C158" t="n">
-        <v>8.906643026997816</v>
+        <v>7.218575004461278</v>
       </c>
       <c r="D158" t="n">
-        <v>1.810986015897728</v>
+        <v>8.361534431356567</v>
       </c>
     </row>
     <row r="159">
@@ -3237,13 +3279,13 @@
         <v>18.86691828100646</v>
       </c>
       <c r="B159" t="n">
-        <v>19.09701758898009</v>
+        <v>17.64859168786255</v>
       </c>
       <c r="C159" t="n">
-        <v>8.864028508941303</v>
+        <v>7.146914242016208</v>
       </c>
       <c r="D159" t="n">
-        <v>1.849701758898009</v>
+        <v>8.524295843931274</v>
       </c>
     </row>
     <row r="160">
@@ -3251,13 +3293,13 @@
         <v>18.98708973502561</v>
       </c>
       <c r="B160" t="n">
-        <v>19.49135767286435</v>
+        <v>17.97841858378332</v>
       </c>
       <c r="C160" t="n">
-        <v>8.820623394321723</v>
+        <v>7.074305979213977</v>
       </c>
       <c r="D160" t="n">
-        <v>1.889135767286435</v>
+        <v>8.689209291891661</v>
       </c>
     </row>
     <row r="161">
@@ -3265,13 +3307,13 @@
         <v>19.10726118904476</v>
       </c>
       <c r="B161" t="n">
-        <v>19.89302814545225</v>
+        <v>18.31250966806194</v>
       </c>
       <c r="C161" t="n">
-        <v>8.776411421929144</v>
+        <v>7.000758995789645</v>
       </c>
       <c r="D161" t="n">
-        <v>1.929302814545225</v>
+        <v>8.856254834030967</v>
       </c>
     </row>
     <row r="162">
@@ -3279,13 +3321,13 @@
         <v>19.2274326430639</v>
       </c>
       <c r="B162" t="n">
-        <v>20.30216949091932</v>
+        <v>18.65082080825236</v>
       </c>
       <c r="C162" t="n">
-        <v>8.731377128634174</v>
+        <v>6.926283007082619</v>
       </c>
       <c r="D162" t="n">
-        <v>1.970216949091932</v>
+        <v>9.02541040412618</v>
       </c>
     </row>
     <row r="163">
@@ -3293,13 +3335,13 @@
         <v>19.34760409708305</v>
       </c>
       <c r="B163" t="n">
-        <v>20.71891494279449</v>
+        <v>18.99330362187611</v>
       </c>
       <c r="C163" t="n">
-        <v>8.68550584938796</v>
+        <v>6.850888664036642</v>
       </c>
       <c r="D163" t="n">
-        <v>2.011891494279449</v>
+        <v>9.196651810938054</v>
       </c>
     </row>
     <row r="164">
@@ -3307,13 +3349,13 @@
         <v>19.4677755511022</v>
       </c>
       <c r="B164" t="n">
-        <v>21.14339048396003</v>
+        <v>19.33990547642217</v>
       </c>
       <c r="C164" t="n">
-        <v>8.638783717222198</v>
+        <v>6.774587553199803</v>
       </c>
       <c r="D164" t="n">
-        <v>2.054339048396003</v>
+        <v>9.369952738211087</v>
       </c>
     </row>
     <row r="165">
@@ -3321,13 +3363,13 @@
         <v>19.58794700512135</v>
       </c>
       <c r="B165" t="n">
-        <v>21.57571484665158</v>
+        <v>19.69056948934705</v>
       </c>
       <c r="C165" t="n">
-        <v>8.591197663249124</v>
+        <v>6.697392196724538</v>
       </c>
       <c r="D165" t="n">
-        <v>2.097571484665158</v>
+        <v>9.545284744673523</v>
       </c>
     </row>
     <row r="166">
@@ -3335,13 +3377,13 @@
         <v>19.7081184591405</v>
       </c>
       <c r="B166" t="n">
-        <v>22.01599951245814</v>
+        <v>20.04523452807473</v>
       </c>
       <c r="C166" t="n">
-        <v>8.542735416661516</v>
+        <v>6.619316052367624</v>
       </c>
       <c r="D166" t="n">
-        <v>2.141599951245814</v>
+        <v>9.722617264037366</v>
       </c>
     </row>
     <row r="167">
@@ -3349,13 +3391,13 @@
         <v>19.82828991315965</v>
       </c>
       <c r="B167" t="n">
-        <v>22.46434871232211</v>
+        <v>20.40383520999676</v>
       </c>
       <c r="C167" t="n">
-        <v>8.493385504732696</v>
+        <v>6.540373513490174</v>
       </c>
       <c r="D167" t="n">
-        <v>2.186434871232211</v>
+        <v>9.901917604998381</v>
       </c>
     </row>
     <row r="168">
@@ -3363,13 +3405,13 @@
         <v>19.9484613671788</v>
       </c>
       <c r="B168" t="n">
-        <v>22.92085942653921</v>
+        <v>20.76630190247215</v>
       </c>
       <c r="C168" t="n">
-        <v>8.443137252816529</v>
+        <v>6.460579909057652</v>
       </c>
       <c r="D168" t="n">
-        <v>2.232085942653921</v>
+        <v>10.08315095123608</v>
       </c>
     </row>
     <row r="169">
@@ -3377,13 +3419,13 @@
         <v>20.06863282119795</v>
       </c>
       <c r="B169" t="n">
-        <v>23.38562138475855</v>
+        <v>21.13256072282743</v>
       </c>
       <c r="C169" t="n">
-        <v>8.391980784347419</v>
+        <v>6.379951503639864</v>
       </c>
       <c r="D169" t="n">
-        <v>2.278562138475855</v>
+        <v>10.26628036141372</v>
       </c>
     </row>
     <row r="170">
@@ -3391,13 +3433,13 @@
         <v>20.1888042752171</v>
       </c>
       <c r="B170" t="n">
-        <v>23.8587170659826</v>
+        <v>21.50253353835662</v>
       </c>
       <c r="C170" t="n">
-        <v>8.339907020840323</v>
+        <v>6.298505497410957</v>
       </c>
       <c r="D170" t="n">
-        <v>2.32587170659826</v>
+        <v>10.45126676917831</v>
       </c>
     </row>
     <row r="171">
@@ -3405,13 +3447,13 @@
         <v>20.30897572923625</v>
       </c>
       <c r="B171" t="n">
-        <v>24.34022169856721</v>
+        <v>21.87613796632126</v>
       </c>
       <c r="C171" t="n">
-        <v>8.28690768189073</v>
+        <v>6.216260026149419</v>
       </c>
       <c r="D171" t="n">
-        <v>2.374022169856721</v>
+        <v>10.63806898316063</v>
       </c>
     </row>
     <row r="172">
@@ -3419,13 +3461,13 @@
         <v>20.4291471832554</v>
       </c>
       <c r="B172" t="n">
-        <v>24.83020326022157</v>
+        <v>22.25328737395041</v>
       </c>
       <c r="C172" t="n">
-        <v>8.232975285174675</v>
+        <v>6.133234161238082</v>
       </c>
       <c r="D172" t="n">
-        <v>2.423020326022158</v>
+        <v>10.82664368697521</v>
       </c>
     </row>
     <row r="173">
@@ -3433,13 +3475,13 @@
         <v>20.54931863727455</v>
       </c>
       <c r="B173" t="n">
-        <v>25.32872247800827</v>
+        <v>22.63389087844062</v>
       </c>
       <c r="C173" t="n">
-        <v>8.178103146448739</v>
+        <v>6.049447909664126</v>
       </c>
       <c r="D173" t="n">
-        <v>2.472872247800828</v>
+        <v>11.01694543922031</v>
       </c>
     </row>
     <row r="174">
@@ -3447,13 +3489,13 @@
         <v>20.6694900912937</v>
       </c>
       <c r="B174" t="n">
-        <v>25.83583282834321</v>
+        <v>23.01785334695593</v>
       </c>
       <c r="C174" t="n">
-        <v>8.122285379550044</v>
+        <v>5.964922214019071</v>
       </c>
       <c r="D174" t="n">
-        <v>2.523583282834323</v>
+        <v>11.20892667347796</v>
       </c>
     </row>
     <row r="175">
@@ -3461,13 +3503,13 @@
         <v>20.78966154531285</v>
       </c>
       <c r="B175" t="n">
-        <v>26.35158053699575</v>
+        <v>23.40507539662792</v>
       </c>
       <c r="C175" t="n">
-        <v>8.065516896396254</v>
+        <v>5.879678952498772</v>
       </c>
       <c r="D175" t="n">
-        <v>2.575158053699576</v>
+        <v>11.40253769831396</v>
       </c>
     </row>
     <row r="176">
@@ -3475,13 +3517,13 @@
         <v>20.909832999332</v>
       </c>
       <c r="B176" t="n">
-        <v>26.87600457908852</v>
+        <v>23.79545339455565</v>
       </c>
       <c r="C176" t="n">
-        <v>8.007793406985574</v>
+        <v>5.79374093890344</v>
       </c>
       <c r="D176" t="n">
-        <v>2.627600457908851</v>
+        <v>11.59772669727783</v>
       </c>
     </row>
     <row r="177">
@@ -3489,13 +3531,13 @@
         <v>21.03000445335115</v>
       </c>
       <c r="B177" t="n">
-        <v>27.40913667909755</v>
+        <v>24.18887945780571</v>
       </c>
       <c r="C177" t="n">
-        <v>7.949111419396758</v>
+        <v>5.707131922637618</v>
       </c>
       <c r="D177" t="n">
-        <v>2.680913667909755</v>
+        <v>11.79443972890286</v>
       </c>
     </row>
     <row r="178">
@@ -3503,13 +3545,13 @@
         <v>21.15017590737029</v>
       </c>
       <c r="B178" t="n">
-        <v>27.95100131085225</v>
+        <v>24.58524145341216</v>
       </c>
       <c r="C178" t="n">
-        <v>7.889468239789098</v>
+        <v>5.619876588710205</v>
       </c>
       <c r="D178" t="n">
-        <v>2.735100131085225</v>
+        <v>11.99262072670608</v>
       </c>
     </row>
     <row r="179">
@@ -3517,13 +3559,13 @@
         <v>21.27034736138944</v>
       </c>
       <c r="B179" t="n">
-        <v>28.50161569753539</v>
+        <v>24.98442299837661</v>
       </c>
       <c r="C179" t="n">
-        <v>7.828861972402428</v>
+        <v>5.532000557734424</v>
       </c>
       <c r="D179" t="n">
-        <v>2.79016156975354</v>
+        <v>12.1922114991883</v>
       </c>
     </row>
     <row r="180">
@@ -3531,13 +3573,13 @@
         <v>21.39051881540859</v>
       </c>
       <c r="B180" t="n">
-        <v>29.06098981168311</v>
+        <v>25.38630345966814</v>
       </c>
       <c r="C180" t="n">
-        <v>7.76729151955713</v>
+        <v>5.443530385927858</v>
       </c>
       <c r="D180" t="n">
-        <v>2.846098981168312</v>
+        <v>12.39315172983407</v>
       </c>
     </row>
     <row r="181">
@@ -3545,13 +3587,13 @@
         <v>21.51069026942774</v>
       </c>
       <c r="B181" t="n">
-        <v>29.62912637518489</v>
+        <v>25.79075795422336</v>
       </c>
       <c r="C181" t="n">
-        <v>7.704756581654123</v>
+        <v>5.354493565112422</v>
       </c>
       <c r="D181" t="n">
-        <v>2.90291263751849</v>
+        <v>12.59537897711168</v>
       </c>
     </row>
     <row r="182">
@@ -3559,13 +3601,13 @@
         <v>21.63086172344689</v>
       </c>
       <c r="B182" t="n">
-        <v>30.20602085928359</v>
+        <v>26.19765734894636</v>
       </c>
       <c r="C182" t="n">
-        <v>7.641257657174874</v>
+        <v>5.264918522714385</v>
       </c>
       <c r="D182" t="n">
-        <v>2.96060208592836</v>
+        <v>12.79882867447318</v>
       </c>
     </row>
     <row r="183">
@@ -3573,13 +3615,13 @@
         <v>21.75103317746604</v>
       </c>
       <c r="B183" t="n">
-        <v>30.79166148457548</v>
+        <v>26.60693804439231</v>
       </c>
       <c r="C183" t="n">
-        <v>7.576796042681389</v>
+        <v>5.174819259548298</v>
       </c>
       <c r="D183" t="n">
-        <v>3.019166148457548</v>
+        <v>13.00346902219616</v>
       </c>
     </row>
     <row r="184">
@@ -3587,13 +3629,13 @@
         <v>21.87120463148519</v>
       </c>
       <c r="B184" t="n">
-        <v>31.38602922101013</v>
+        <v>27.0187848149515</v>
       </c>
       <c r="C184" t="n">
-        <v>7.511373832816217</v>
+        <v>5.084155099284682</v>
       </c>
       <c r="D184" t="n">
-        <v>3.078602922101013</v>
+        <v>13.20939240747575</v>
       </c>
     </row>
     <row r="185">
@@ -3601,13 +3643,13 @@
         <v>21.99137608550434</v>
       </c>
       <c r="B185" t="n">
-        <v>31.98909778789049</v>
+        <v>27.43293182397312</v>
       </c>
       <c r="C185" t="n">
-        <v>7.444993920302453</v>
+        <v>4.992984563340813</v>
       </c>
       <c r="D185" t="n">
-        <v>3.138909778789049</v>
+        <v>13.41646591198656</v>
       </c>
     </row>
     <row r="186">
@@ -3615,13 +3657,13 @@
         <v>22.11154753952349</v>
       </c>
       <c r="B186" t="n">
-        <v>32.60083365387288</v>
+        <v>27.8490473103177</v>
       </c>
       <c r="C186" t="n">
-        <v>7.377659995943735</v>
+        <v>4.901380685784861</v>
       </c>
       <c r="D186" t="n">
-        <v>3.200083365387289</v>
+        <v>13.62452365515885</v>
       </c>
     </row>
     <row r="187">
@@ -3629,13 +3671,13 @@
         <v>22.23171899354264</v>
       </c>
       <c r="B187" t="n">
-        <v>33.22119603696704</v>
+        <v>28.26680494989744</v>
       </c>
       <c r="C187" t="n">
-        <v>7.309376548624237</v>
+        <v>4.809415303769652</v>
       </c>
       <c r="D187" t="n">
-        <v>3.262119603696706</v>
+        <v>13.83340247494872</v>
       </c>
     </row>
     <row r="188">
@@ -3643,13 +3685,13 @@
         <v>22.35189044756179</v>
       </c>
       <c r="B188" t="n">
-        <v>33.85013690453602</v>
+        <v>28.68588385567605</v>
       </c>
       <c r="C188" t="n">
-        <v>7.240148865308683</v>
+        <v>4.717159057532673</v>
       </c>
       <c r="D188" t="n">
-        <v>3.325013690453603</v>
+        <v>14.04294192783803</v>
       </c>
     </row>
     <row r="189">
@@ -3657,13 +3699,13 @@
         <v>22.47206190158094</v>
       </c>
       <c r="B189" t="n">
-        <v>34.48760097329622</v>
+        <v>29.10596857766889</v>
       </c>
       <c r="C189" t="n">
-        <v>7.169983031042338</v>
+        <v>4.624681390396077</v>
       </c>
       <c r="D189" t="n">
-        <v>3.388760097329623</v>
+        <v>14.25298428883444</v>
       </c>
     </row>
     <row r="190">
@@ -3671,13 +3713,13 @@
         <v>22.59223335560009</v>
       </c>
       <c r="B190" t="n">
-        <v>35.13352570931742</v>
+        <v>29.52674910294288</v>
       </c>
       <c r="C190" t="n">
-        <v>7.09888592895101</v>
+        <v>4.532050548766675</v>
       </c>
       <c r="D190" t="n">
-        <v>3.453352570931743</v>
+        <v>14.46337455147144</v>
       </c>
     </row>
     <row r="191">
@@ -3685,13 +3727,13 @@
         <v>22.71240480961924</v>
       </c>
       <c r="B191" t="n">
-        <v>35.78784132802284</v>
+        <v>29.94792085561657</v>
       </c>
       <c r="C191" t="n">
-        <v>7.026865240241047</v>
+        <v>4.43933358213593</v>
       </c>
       <c r="D191" t="n">
-        <v>3.518784132802285</v>
+        <v>14.67396042780829</v>
       </c>
     </row>
     <row r="192">
@@ -3699,13 +3741,13 @@
         <v>22.83257626363839</v>
       </c>
       <c r="B192" t="n">
-        <v>36.45047079418895</v>
+        <v>30.3691846968601</v>
       </c>
       <c r="C192" t="n">
-        <v>6.953929444199344</v>
+        <v>4.346596343079978</v>
       </c>
       <c r="D192" t="n">
-        <v>3.585047079418897</v>
+        <v>14.88459234843005</v>
       </c>
     </row>
     <row r="193">
@@ -3713,13 +3755,13 @@
         <v>22.95274771765754</v>
       </c>
       <c r="B193" t="n">
-        <v>37.12132982194566</v>
+        <v>30.79024692489519</v>
       </c>
       <c r="C193" t="n">
-        <v>6.880087818193335</v>
+        <v>4.253903487259608</v>
       </c>
       <c r="D193" t="n">
-        <v>3.652132982194568</v>
+        <v>15.0951234624476</v>
       </c>
     </row>
     <row r="194">
@@ -3727,13 +3769,13 @@
         <v>23.07291917167668</v>
       </c>
       <c r="B194" t="n">
-        <v>37.80032687477622</v>
+        <v>31.21081927499514</v>
       </c>
       <c r="C194" t="n">
-        <v>6.805350437671003</v>
+        <v>4.161318473420274</v>
       </c>
       <c r="D194" t="n">
-        <v>3.720032687477624</v>
+        <v>15.30540963749757</v>
       </c>
     </row>
     <row r="195">
@@ -3741,13 +3783,13 @@
         <v>23.19309062569583</v>
       </c>
       <c r="B195" t="n">
-        <v>38.48736316551727</v>
+        <v>31.6306189194849</v>
       </c>
       <c r="C195" t="n">
-        <v>6.729728176160865</v>
+        <v>4.068903563392084</v>
       </c>
       <c r="D195" t="n">
-        <v>3.788736316551728</v>
+        <v>15.51530945974245</v>
       </c>
     </row>
     <row r="196">
@@ -3755,13 +3797,13 @@
         <v>23.31326207971498</v>
       </c>
       <c r="B196" t="n">
-        <v>39.18233265635877</v>
+        <v>32.04936846774096</v>
       </c>
       <c r="C196" t="n">
-        <v>6.653232705271988</v>
+        <v>3.976719822089811</v>
       </c>
       <c r="D196" t="n">
-        <v>3.858233265635879</v>
+        <v>15.72468423387048</v>
       </c>
     </row>
     <row r="197">
@@ -3769,13 +3811,13 @@
         <v>23.43343353373413</v>
       </c>
       <c r="B197" t="n">
-        <v>39.88512205884408</v>
+        <v>32.46679596619143</v>
       </c>
       <c r="C197" t="n">
-        <v>6.575876494693979</v>
+        <v>3.884827117512892</v>
       </c>
       <c r="D197" t="n">
-        <v>3.928512205884409</v>
+        <v>15.93339798309572</v>
       </c>
     </row>
     <row r="198">
@@ -3783,13 +3825,13 @@
         <v>23.55360498775328</v>
       </c>
       <c r="B198" t="n">
-        <v>40.59561083386995</v>
+        <v>32.88263489831605</v>
       </c>
       <c r="C198" t="n">
-        <v>6.497672812196987</v>
+        <v>3.793284120745414</v>
       </c>
       <c r="D198" t="n">
-        <v>3.999561083386997</v>
+        <v>16.14131744915802</v>
       </c>
     </row>
     <row r="199">
@@ -3797,13 +3839,13 @@
         <v>23.67377644177243</v>
       </c>
       <c r="B199" t="n">
-        <v>41.31367119168644</v>
+        <v>33.29662418464608</v>
       </c>
       <c r="C199" t="n">
-        <v>6.418635723631706</v>
+        <v>3.702148305956134</v>
       </c>
       <c r="D199" t="n">
-        <v>4.071367119168645</v>
+        <v>16.34831209232304</v>
       </c>
     </row>
     <row r="200">
@@ -3811,13 +3853,13 @@
         <v>23.79394789579158</v>
       </c>
       <c r="B200" t="n">
-        <v>42.03916809189701</v>
+        <v>33.70850818276443</v>
       </c>
       <c r="C200" t="n">
-        <v>6.338780092929371</v>
+        <v>3.611475950398463</v>
       </c>
       <c r="D200" t="n">
-        <v>4.143916809189703</v>
+        <v>16.55425409138222</v>
       </c>
     </row>
     <row r="201">
@@ -3825,13 +3867,13 @@
         <v>23.91411934981073</v>
       </c>
       <c r="B201" t="n">
-        <v>42.77195924345845</v>
+        <v>34.11803668730558</v>
       </c>
       <c r="C201" t="n">
-        <v>6.258121582101764</v>
+        <v>3.521322134410481</v>
       </c>
       <c r="D201" t="n">
-        <v>4.217195924345848</v>
+        <v>16.75901834365279</v>
       </c>
     </row>
     <row r="202">
@@ -3839,13 +3881,13 @@
         <v>24.03429080382988</v>
       </c>
       <c r="B202" t="n">
-        <v>43.511895104681</v>
+        <v>34.52496492995564</v>
       </c>
       <c r="C202" t="n">
-        <v>6.176676651241203</v>
+        <v>3.431740741414917</v>
       </c>
       <c r="D202" t="n">
-        <v>4.291189510468103</v>
+        <v>16.96248246497782</v>
       </c>
     </row>
     <row r="203">
@@ -3853,13 +3895,13 @@
         <v>24.15446225784903</v>
       </c>
       <c r="B203" t="n">
-        <v>44.25881888322818</v>
+        <v>34.92905357945229</v>
       </c>
       <c r="C203" t="n">
-        <v>6.094462558520553</v>
+        <v>3.34278445791917</v>
       </c>
       <c r="D203" t="n">
-        <v>4.365881888322821</v>
+        <v>17.16452678972614</v>
       </c>
     </row>
     <row r="204">
@@ -3867,13 +3909,13 @@
         <v>24.27463371186818</v>
       </c>
       <c r="B204" t="n">
-        <v>45.0125665361169</v>
+        <v>35.3300687415848</v>
       </c>
       <c r="C204" t="n">
-        <v>6.011497360193223</v>
+        <v>3.254504773515292</v>
       </c>
       <c r="D204" t="n">
-        <v>4.441256653611693</v>
+        <v>17.3650343707924</v>
       </c>
     </row>
     <row r="205">
@@ -3881,13 +3923,13 @@
         <v>24.39480516588733</v>
       </c>
       <c r="B205" t="n">
-        <v>45.77296676971744</v>
+        <v>35.72778195919402</v>
       </c>
       <c r="C205" t="n">
-        <v>5.927799910593166</v>
+        <v>3.166951980880004</v>
       </c>
       <c r="D205" t="n">
-        <v>4.517296676971746</v>
+        <v>17.56389097959701</v>
       </c>
     </row>
     <row r="206">
@@ -3895,13 +3937,13 @@
         <v>24.51497661990648</v>
       </c>
       <c r="B206" t="n">
-        <v>46.53984103975346</v>
+        <v>36.12197021217247</v>
       </c>
       <c r="C206" t="n">
-        <v>5.843389862134867</v>
+        <v>3.080175175774678</v>
       </c>
       <c r="D206" t="n">
-        <v>4.59398410397535</v>
+        <v>17.76098510608624</v>
       </c>
     </row>
     <row r="207">
@@ -3909,13 +3951,13 @@
         <v>24.63514807392563</v>
       </c>
       <c r="B207" t="n">
-        <v>47.31300355130199</v>
+        <v>36.5124159174642</v>
       </c>
       <c r="C207" t="n">
-        <v>5.758287665313366</v>
+        <v>2.994222257045352</v>
       </c>
       <c r="D207" t="n">
-        <v>4.671300355130201</v>
+        <v>17.9562079587321</v>
       </c>
     </row>
     <row r="208">
@@ -3923,13 +3965,13 @@
         <v>24.75531952794478</v>
       </c>
       <c r="B208" t="n">
-        <v>48.09226125879337</v>
+        <v>36.89890692906486</v>
       </c>
       <c r="C208" t="n">
-        <v>5.672514568704244</v>
+        <v>2.909139926622724</v>
       </c>
       <c r="D208" t="n">
-        <v>4.749226125879341</v>
+        <v>18.14945346453243</v>
       </c>
     </row>
     <row r="209">
@@ -3937,13 +3979,13 @@
         <v>24.87549098196392</v>
       </c>
       <c r="B209" t="n">
-        <v>48.87741386601136</v>
+        <v>37.2812365380217</v>
       </c>
       <c r="C209" t="n">
-        <v>5.586092618963623</v>
+        <v>2.824973689522154</v>
       </c>
       <c r="D209" t="n">
-        <v>4.82774138660114</v>
+        <v>18.34061826901085</v>
       </c>
     </row>
     <row r="210">
@@ -3951,13 +3993,13 @@
         <v>24.99566243598307</v>
       </c>
       <c r="B210" t="n">
-        <v>49.6682538260931</v>
+        <v>37.6592034724336</v>
       </c>
       <c r="C210" t="n">
-        <v>5.499044660828163</v>
+        <v>2.741767853843657</v>
       </c>
       <c r="D210" t="n">
-        <v>4.906825382609314</v>
+        <v>18.5296017362168</v>
       </c>
     </row>
     <row r="211">
@@ -3965,13 +4007,13 @@
         <v>25.11583389000223</v>
       </c>
       <c r="B211" t="n">
-        <v>50.46456634152904</v>
+        <v>38.032611897451</v>
       </c>
       <c r="C211" t="n">
-        <v>5.411394337115073</v>
+        <v>2.659565530771912</v>
       </c>
       <c r="D211" t="n">
-        <v>4.986456634152908</v>
+        <v>18.7163059487255</v>
       </c>
     </row>
     <row r="212">
@@ -3979,13 +4021,13 @@
         <v>25.23600534402138</v>
       </c>
       <c r="B212" t="n">
-        <v>51.26630854937486</v>
+        <v>38.40127141527594</v>
       </c>
       <c r="C212" t="n">
-        <v>5.323146365759675</v>
+        <v>2.578408634576258</v>
       </c>
       <c r="D212" t="n">
-        <v>5.066630854937486</v>
+        <v>18.90063570763797</v>
       </c>
     </row>
     <row r="213">
@@ -3993,13 +4035,13 @@
         <v>25.35617679804052</v>
       </c>
       <c r="B213" t="n">
-        <v>52.07401243286697</v>
+        <v>38.76499706516204</v>
       </c>
       <c r="C213" t="n">
-        <v>5.234242191230099</v>
+        <v>2.498337882610698</v>
       </c>
       <c r="D213" t="n">
-        <v>5.147401243286696</v>
+        <v>19.08249853258102</v>
       </c>
     </row>
     <row r="214">
@@ -4007,13 +4049,13 @@
         <v>25.47634825205967</v>
       </c>
       <c r="B214" t="n">
-        <v>52.8871672414064</v>
+        <v>39.12360932341458</v>
       </c>
       <c r="C214" t="n">
-        <v>5.144738031976344</v>
+        <v>2.419392795313887</v>
       </c>
       <c r="D214" t="n">
-        <v>5.228716724140639</v>
+        <v>19.26180466170729</v>
       </c>
     </row>
     <row r="215">
@@ -4021,13 +4063,13 @@
         <v>25.59651970607882</v>
       </c>
       <c r="B215" t="n">
-        <v>53.70512305828836</v>
+        <v>39.47693410339036</v>
       </c>
       <c r="C215" t="n">
-        <v>5.054705424497533</v>
+        <v>2.341611696209147</v>
       </c>
       <c r="D215" t="n">
-        <v>5.310512305828836</v>
+        <v>19.43846705169518</v>
       </c>
     </row>
     <row r="216">
@@ -4035,13 +4077,13 @@
         <v>25.71669116009797</v>
       </c>
       <c r="B216" t="n">
-        <v>54.52724014492038</v>
+        <v>39.82480275549782</v>
       </c>
       <c r="C216" t="n">
-        <v>4.964214784985344</v>
+        <v>2.26503171190446</v>
       </c>
       <c r="D216" t="n">
-        <v>5.392724014492038</v>
+        <v>19.61240137774891</v>
       </c>
     </row>
     <row r="217">
@@ -4049,13 +4091,13 @@
         <v>25.83686261411712</v>
       </c>
       <c r="B217" t="n">
-        <v>55.35288894082227</v>
+        <v>40.16705206719698</v>
       </c>
       <c r="C217" t="n">
-        <v>4.873335409324012</v>
+        <v>2.189688772092469</v>
       </c>
       <c r="D217" t="n">
-        <v>5.475288894082227</v>
+        <v>19.78352603359849</v>
       </c>
     </row>
     <row r="218">
@@ -4063,13 +4105,13 @@
         <v>25.95703406813627</v>
       </c>
       <c r="B218" t="n">
-        <v>56.18145006362621</v>
+        <v>40.50352426299945</v>
       </c>
       <c r="C218" t="n">
-        <v>4.782135473090323</v>
+        <v>2.115617609550472</v>
       </c>
       <c r="D218" t="n">
-        <v>5.55814500636262</v>
+        <v>19.95176213149973</v>
       </c>
     </row>
     <row r="219">
@@ -4077,13 +4119,13 @@
         <v>26.07720552215542</v>
       </c>
       <c r="B219" t="n">
-        <v>57.01231430907661</v>
+        <v>40.83406700446847</v>
       </c>
       <c r="C219" t="n">
-        <v>4.690682031553627</v>
+        <v>2.042851760140431</v>
       </c>
       <c r="D219" t="n">
-        <v>5.641231430907662</v>
+        <v>20.11703350223424</v>
       </c>
     </row>
     <row r="220">
@@ -4091,13 +4133,13 @@
         <v>26.19737697617457</v>
       </c>
       <c r="B220" t="n">
-        <v>57.84488265103025</v>
+        <v>41.15853339021883</v>
       </c>
       <c r="C220" t="n">
-        <v>4.599041019675827</v>
+        <v>1.97142356280897</v>
       </c>
       <c r="D220" t="n">
-        <v>5.724488265103025</v>
+        <v>20.27926669510941</v>
       </c>
     </row>
     <row r="221">
@@ -4105,13 +4147,13 @@
         <v>26.31754843019372</v>
       </c>
       <c r="B221" t="n">
-        <v>58.67856624145614</v>
+        <v>41.47678195591693</v>
       </c>
       <c r="C221" t="n">
-        <v>4.507277252111384</v>
+        <v>1.901364159587374</v>
       </c>
       <c r="D221" t="n">
-        <v>5.807856624145614</v>
+        <v>20.43839097795846</v>
       </c>
     </row>
     <row r="222">
@@ -4119,13 +4161,13 @@
         <v>26.43771988421287</v>
       </c>
       <c r="B222" t="n">
-        <v>59.51278641043569</v>
+        <v>41.78867667428079</v>
       </c>
       <c r="C222" t="n">
-        <v>4.415454423207312</v>
+        <v>1.832703495591582</v>
       </c>
       <c r="D222" t="n">
-        <v>5.891278641043569</v>
+        <v>20.5943383371404</v>
       </c>
     </row>
     <row r="223">
@@ -4133,13 +4175,13 @@
         <v>26.55789133823202</v>
       </c>
       <c r="B223" t="n">
-        <v>60.34697466616255</v>
+        <v>42.09408695508</v>
       </c>
       <c r="C223" t="n">
-        <v>4.323635107003184</v>
+        <v>1.7654703190222</v>
       </c>
       <c r="D223" t="n">
-        <v>5.974697466616256</v>
+        <v>20.74704347754</v>
       </c>
     </row>
     <row r="224">
@@ -4147,13 +4189,13 @@
         <v>26.67806279225117</v>
       </c>
       <c r="B224" t="n">
-        <v>61.1805726949427</v>
+        <v>42.39288764513576</v>
       </c>
       <c r="C224" t="n">
-        <v>4.231880757231131</v>
+        <v>1.699692181164493</v>
       </c>
       <c r="D224" t="n">
-        <v>6.05805726949427</v>
+        <v>20.89644382256788</v>
       </c>
     </row>
     <row r="225">
@@ -4161,13 +4203,13 @@
         <v>26.79823424627032</v>
       </c>
       <c r="B225" t="n">
-        <v>62.01303236119438</v>
+        <v>42.68495902832083</v>
       </c>
       <c r="C225" t="n">
-        <v>4.14025170731584</v>
+        <v>1.635395436388386</v>
       </c>
       <c r="D225" t="n">
-        <v>6.141303236119439</v>
+        <v>21.04247951416042</v>
       </c>
     </row>
     <row r="226">
@@ -4175,13 +4217,13 @@
         <v>26.91840570028947</v>
       </c>
       <c r="B226" t="n">
-        <v>62.84381570744824</v>
+        <v>42.97018682555965</v>
       </c>
       <c r="C226" t="n">
-        <v>4.048807170374548</v>
+        <v>1.572605242148461</v>
       </c>
       <c r="D226" t="n">
-        <v>6.224381570744825</v>
+        <v>21.18509341277982</v>
       </c>
     </row>
     <row r="227">
@@ -4189,13 +4231,13 @@
         <v>27.03857715430862</v>
       </c>
       <c r="B227" t="n">
-        <v>63.67239495434715</v>
+        <v>43.24846219482815</v>
       </c>
       <c r="C227" t="n">
-        <v>3.957605239217058</v>
+        <v>1.511345558983966</v>
       </c>
       <c r="D227" t="n">
-        <v>6.307239495434715</v>
+        <v>21.32423109741407</v>
       </c>
     </row>
     <row r="228">
@@ -4203,13 +4245,13 @@
         <v>27.15874860832777</v>
       </c>
       <c r="B228" t="n">
-        <v>64.49825250064629</v>
+        <v>43.51968173115393</v>
       </c>
       <c r="C228" t="n">
-        <v>3.866702886345724</v>
+        <v>1.451639150518806</v>
       </c>
       <c r="D228" t="n">
-        <v>6.389825250064629</v>
+        <v>21.45984086557696</v>
       </c>
     </row>
     <row r="229">
@@ -4217,13 +4259,13 @@
         <v>27.27892006234691</v>
       </c>
       <c r="B229" t="n">
-        <v>65.32088092321315</v>
+        <v>43.78374746661615</v>
       </c>
       <c r="C229" t="n">
-        <v>3.77615596395546</v>
+        <v>1.39350758346155</v>
       </c>
       <c r="D229" t="n">
-        <v>6.472088092321315</v>
+        <v>21.59187373330807</v>
       </c>
     </row>
     <row r="230">
@@ -4231,13 +4273,13 @@
         <v>27.39909151636606</v>
       </c>
       <c r="B230" t="n">
-        <v>66.13978297702759</v>
+        <v>44.04056687034559</v>
       </c>
       <c r="C230" t="n">
-        <v>3.686019203933731</v>
+        <v>1.33697122760542</v>
       </c>
       <c r="D230" t="n">
-        <v>6.553978297702759</v>
+        <v>21.72028343517279</v>
       </c>
     </row>
     <row r="231">
@@ -4245,13 +4287,13 @@
         <v>27.51926297038521</v>
       </c>
       <c r="B231" t="n">
-        <v>66.9544715951817</v>
+        <v>44.2900528485246</v>
       </c>
       <c r="C231" t="n">
-        <v>3.596346217860562</v>
+        <v>1.282049255828308</v>
       </c>
       <c r="D231" t="n">
-        <v>6.635447159518169</v>
+        <v>21.8450264242623</v>
       </c>
     </row>
     <row r="232">
@@ -4259,13 +4301,13 @@
         <v>27.63943442440436</v>
       </c>
       <c r="B232" t="n">
-        <v>67.76446988887989</v>
+        <v>44.53212374438715</v>
       </c>
       <c r="C232" t="n">
-        <v>3.507189497008536</v>
+        <v>1.228759644092758</v>
       </c>
       <c r="D232" t="n">
-        <v>6.71644698888799</v>
+        <v>21.96606187219357</v>
       </c>
     </row>
     <row r="233">
@@ -4273,13 +4315,13 @@
         <v>27.75960587842351</v>
       </c>
       <c r="B233" t="n">
-        <v>68.56931114743888</v>
+        <v>44.76670333821878</v>
       </c>
       <c r="C233" t="n">
-        <v>3.418600412342792</v>
+        <v>1.177119171445981</v>
       </c>
       <c r="D233" t="n">
-        <v>6.796931114743889</v>
+        <v>22.08335166910939</v>
       </c>
     </row>
     <row r="234">
@@ -4287,13 +4329,13 @@
         <v>27.87977733244266</v>
       </c>
       <c r="B234" t="n">
-        <v>69.36853883828776</v>
+        <v>44.99372084735666</v>
       </c>
       <c r="C234" t="n">
-        <v>3.330629214521019</v>
+        <v>1.127143420019844</v>
       </c>
       <c r="D234" t="n">
-        <v>6.876853883828776</v>
+        <v>22.19686042367833</v>
       </c>
     </row>
     <row r="235">
@@ -4301,13 +4343,13 @@
         <v>27.99994878646181</v>
       </c>
       <c r="B235" t="n">
-        <v>70.16170660696781</v>
+        <v>45.21311092618953</v>
       </c>
       <c r="C235" t="n">
-        <v>3.243325033893472</v>
+        <v>1.078846775030874</v>
       </c>
       <c r="D235" t="n">
-        <v>6.956170660696782</v>
+        <v>22.30655546309477</v>
       </c>
     </row>
     <row r="236">
@@ -4315,13 +4357,13 @@
         <v>28.12012024048096</v>
       </c>
       <c r="B236" t="n">
-        <v>70.94837827713272</v>
+        <v>45.42481366615773</v>
       </c>
       <c r="C236" t="n">
-        <v>3.156735880502956</v>
+        <v>1.032242424780264</v>
       </c>
       <c r="D236" t="n">
-        <v>7.034837827713272</v>
+        <v>22.41240683307887</v>
       </c>
     </row>
     <row r="237">
@@ -4329,13 +4371,13 @@
         <v>28.24029169450011</v>
       </c>
       <c r="B237" t="n">
-        <v>71.72812785054838</v>
+        <v>45.62877459575319</v>
       </c>
       <c r="C237" t="n">
-        <v>3.070908644084838</v>
+        <v>0.9873423606538632</v>
       </c>
       <c r="D237" t="n">
-        <v>7.112812785054838</v>
+        <v>22.5143872978766</v>
       </c>
     </row>
     <row r="238">
@@ -4343,13 +4385,13 @@
         <v>28.36046314851926</v>
       </c>
       <c r="B238" t="n">
-        <v>72.50053950709311</v>
+        <v>45.82494468051945</v>
       </c>
       <c r="C238" t="n">
-        <v>2.985889094067034</v>
+        <v>0.9441573771221794</v>
       </c>
       <c r="D238" t="n">
-        <v>7.190053950709311</v>
+        <v>22.61247234025973</v>
       </c>
     </row>
     <row r="239">
@@ -4357,13 +4399,13 @@
         <v>28.48063460253841</v>
       </c>
       <c r="B239" t="n">
-        <v>73.26520760475745</v>
+        <v>46.01328561691926</v>
       </c>
       <c r="C239" t="n">
-        <v>2.901721879570023</v>
+        <v>0.9026959063456446</v>
       </c>
       <c r="D239" t="n">
-        <v>7.266520760475745</v>
+        <v>22.70664280845963</v>
       </c>
     </row>
     <row r="240">
@@ -4371,13 +4413,13 @@
         <v>28.60080605655756</v>
       </c>
       <c r="B240" t="n">
-        <v>74.02173667964426</v>
+        <v>46.19449846002296</v>
       </c>
       <c r="C240" t="n">
-        <v>2.818450529406836</v>
+        <v>0.8628036176998664</v>
       </c>
       <c r="D240" t="n">
-        <v>7.342173667964428</v>
+        <v>22.79724923001148</v>
       </c>
     </row>
     <row r="241">
@@ -4385,13 +4427,13 @@
         <v>28.72097751057671</v>
       </c>
       <c r="B241" t="n">
-        <v>74.76974144596872</v>
+        <v>46.36917960120523</v>
       </c>
       <c r="C241" t="n">
-        <v>2.736117452083068</v>
+        <v>0.8243492212803477</v>
       </c>
       <c r="D241" t="n">
-        <v>7.416974144596872</v>
+        <v>22.88458980060262</v>
       </c>
     </row>
     <row r="242">
@@ -4399,13 +4441,13 @@
         <v>28.84114896459586</v>
       </c>
       <c r="B242" t="n">
-        <v>75.50884679605832</v>
+        <v>46.53745155989431</v>
       </c>
       <c r="C242" t="n">
-        <v>2.654763935796859</v>
+        <v>0.7873057455970371</v>
       </c>
       <c r="D242" t="n">
-        <v>7.490884679605832</v>
+        <v>22.96872577994716</v>
       </c>
     </row>
     <row r="243">
@@ -4413,13 +4455,13 @@
         <v>28.96132041861501</v>
       </c>
       <c r="B243" t="n">
-        <v>76.23868780035285</v>
+        <v>46.6994399618799</v>
       </c>
       <c r="C243" t="n">
-        <v>2.574430148438914</v>
+        <v>0.7516455353238655</v>
       </c>
       <c r="D243" t="n">
-        <v>7.563868780035286</v>
+        <v>23.04971998093995</v>
       </c>
     </row>
     <row r="244">
@@ -4427,13 +4469,13 @@
         <v>29.08149187263416</v>
       </c>
       <c r="B244" t="n">
-        <v>76.95890970740439</v>
+        <v>46.85527353931317</v>
       </c>
       <c r="C244" t="n">
-        <v>2.495155137592491</v>
+        <v>0.7173402512987413</v>
       </c>
       <c r="D244" t="n">
-        <v>7.635890970740439</v>
+        <v>23.12763676965659</v>
       </c>
     </row>
     <row r="245">
@@ -4441,13 +4483,13 @@
         <v>29.2016633266533</v>
       </c>
       <c r="B245" t="n">
-        <v>77.66916794387733</v>
+        <v>47.00508413070684</v>
       </c>
       <c r="C245" t="n">
-        <v>2.41697683053341</v>
+        <v>0.6843608705235534</v>
       </c>
       <c r="D245" t="n">
-        <v>7.706916794387732</v>
+        <v>23.20254206535342</v>
       </c>
     </row>
     <row r="246">
@@ -4455,13 +4497,13 @@
         <v>29.32183478067245</v>
       </c>
       <c r="B246" t="n">
-        <v>78.3691281145484</v>
+        <v>47.14900668093512</v>
       </c>
       <c r="C246" t="n">
-        <v>2.339932034230036</v>
+        <v>0.6526776861641668</v>
       </c>
       <c r="D246" t="n">
-        <v>7.77691281145484</v>
+        <v>23.27450334046756</v>
       </c>
     </row>
     <row r="247">
@@ -4469,13 +4511,13 @@
         <v>29.4420062346916</v>
       </c>
       <c r="B247" t="n">
-        <v>79.05846600230659</v>
+        <v>47.2871792412337</v>
       </c>
       <c r="C247" t="n">
-        <v>2.264056435343302</v>
+        <v>0.6222603075504282</v>
       </c>
       <c r="D247" t="n">
-        <v>7.84584660023066</v>
+        <v>23.34358962061685</v>
       </c>
     </row>
     <row r="248">
@@ -4483,13 +4525,13 @@
         <v>29.56217768871075</v>
       </c>
       <c r="B248" t="n">
-        <v>79.73686756815323</v>
+        <v>47.41974296919978</v>
       </c>
       <c r="C248" t="n">
-        <v>2.189384600226693</v>
+        <v>0.5930776601761626</v>
       </c>
       <c r="D248" t="n">
-        <v>7.913686756815324</v>
+        <v>23.40987148459989</v>
       </c>
     </row>
     <row r="249">
@@ -4497,13 +4539,13 @@
         <v>29.6823491427299</v>
       </c>
       <c r="B249" t="n">
-        <v>80.40402895120192</v>
+        <v>47.54684212879205</v>
       </c>
       <c r="C249" t="n">
-        <v>2.115949974926252</v>
+        <v>0.5650979856991751</v>
       </c>
       <c r="D249" t="n">
-        <v>7.980402895120193</v>
+        <v>23.47342106439602</v>
       </c>
     </row>
     <row r="250">
@@ -4511,13 +4553,13 @@
         <v>29.80252059674905</v>
       </c>
       <c r="B250" t="n">
-        <v>81.05965646867864</v>
+        <v>47.66862409033072</v>
       </c>
       <c r="C250" t="n">
-        <v>2.043784885180572</v>
+        <v>0.5382888419412468</v>
       </c>
       <c r="D250" t="n">
-        <v>8.045965646867863</v>
+        <v>23.53431204516536</v>
       </c>
     </row>
     <row r="251">
@@ -4525,13 +4567,13 @@
         <v>29.9226920507682</v>
       </c>
       <c r="B251" t="n">
-        <v>81.70346661592157</v>
+        <v>47.7852393304975</v>
       </c>
       <c r="C251" t="n">
-        <v>1.97292053642081</v>
+        <v>0.5126171028881408</v>
       </c>
       <c r="D251" t="n">
-        <v>8.110346661592157</v>
+        <v>23.59261966524875</v>
       </c>
     </row>
     <row r="252">
@@ -4539,13 +4581,13 @@
         <v>30.04286350478735</v>
       </c>
       <c r="B252" t="n">
-        <v>82.33518606638128</v>
+        <v>47.89684143233556</v>
       </c>
       <c r="C252" t="n">
-        <v>1.903387013770678</v>
+        <v>0.4880489586895986</v>
       </c>
       <c r="D252" t="n">
-        <v>8.17351860663813</v>
+        <v>23.64842071616778</v>
       </c>
     </row>
     <row r="253">
@@ -4553,13 +4595,13 @@
         <v>30.1630349588065</v>
       </c>
       <c r="B253" t="n">
-        <v>82.95455167162058</v>
+        <v>48.0035870852496</v>
       </c>
       <c r="C253" t="n">
-        <v>1.835213282046445</v>
+        <v>0.4645499156593406</v>
       </c>
       <c r="D253" t="n">
-        <v>8.23545516716206</v>
+        <v>23.7017935426248</v>
       </c>
     </row>
     <row r="254">
@@ -4567,13 +4609,13 @@
         <v>30.28320641282565</v>
       </c>
       <c r="B254" t="n">
-        <v>83.56131046131469</v>
+        <v>48.10563608500583</v>
       </c>
       <c r="C254" t="n">
-        <v>1.768427185756932</v>
+        <v>0.4420847962750652</v>
       </c>
       <c r="D254" t="n">
-        <v>8.296131046131469</v>
+        <v>23.75281804250291</v>
       </c>
     </row>
     <row r="255">
@@ -4581,13 +4623,13 @@
         <v>30.4033778668448</v>
       </c>
       <c r="B255" t="n">
-        <v>84.155219643251</v>
+        <v>48.20315133373194</v>
       </c>
       <c r="C255" t="n">
-        <v>1.703055449103519</v>
+        <v>0.4206177391784515</v>
       </c>
       <c r="D255" t="n">
-        <v>8.355521964325101</v>
+        <v>23.80157566686597</v>
       </c>
     </row>
     <row r="256">
@@ -4595,13 +4637,13 @@
         <v>30.52354932086395</v>
       </c>
       <c r="B256" t="n">
-        <v>84.73604660332933</v>
+        <v>48.29629883991711</v>
       </c>
       <c r="C256" t="n">
-        <v>1.639123675980144</v>
+        <v>0.4001121991751565</v>
       </c>
       <c r="D256" t="n">
-        <v>8.413604660332933</v>
+        <v>23.84814941995856</v>
       </c>
     </row>
     <row r="257">
@@ -4609,13 +4651,13 @@
         <v>30.6437207748831</v>
       </c>
       <c r="B257" t="n">
-        <v>85.30356890556169</v>
+        <v>48.38524771841206</v>
       </c>
       <c r="C257" t="n">
-        <v>1.576656349973304</v>
+        <v>0.3805309472348178</v>
       </c>
       <c r="D257" t="n">
-        <v>8.47035689055617</v>
+        <v>23.89262385920603</v>
       </c>
     </row>
     <row r="258">
@@ -4623,13 +4665,13 @@
         <v>30.76389222890225</v>
       </c>
       <c r="B258" t="n">
-        <v>85.85757429207251</v>
+        <v>48.47017019042897</v>
       </c>
       <c r="C258" t="n">
-        <v>1.515676834362043</v>
+        <v>0.3618360704910496</v>
       </c>
       <c r="D258" t="n">
-        <v>8.525757429207252</v>
+        <v>23.93508509521448</v>
       </c>
     </row>
     <row r="259">
@@ -4637,13 +4679,13 @@
         <v>30.8840636829214</v>
       </c>
       <c r="B259" t="n">
-        <v>86.39786068309844</v>
+        <v>48.55124158354152</v>
       </c>
       <c r="C259" t="n">
-        <v>1.456207372117971</v>
+        <v>0.3439889722414471</v>
       </c>
       <c r="D259" t="n">
-        <v>8.579786068309845</v>
+        <v>23.97562079177076</v>
       </c>
     </row>
     <row r="260">
@@ -4651,13 +4693,13 @@
         <v>31.00423513694054</v>
       </c>
       <c r="B260" t="n">
-        <v>86.92423617698847</v>
+        <v>48.62864033168492</v>
       </c>
       <c r="C260" t="n">
-        <v>1.39826908590525</v>
+        <v>0.3269503719475845</v>
       </c>
       <c r="D260" t="n">
-        <v>8.632423617698848</v>
+        <v>24.01432016584246</v>
       </c>
     </row>
     <row r="261">
@@ -4665,13 +4707,13 @@
         <v>31.12440659095969</v>
       </c>
       <c r="B261" t="n">
-        <v>87.43651905020391</v>
+        <v>48.70242322408347</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3418819780806</v>
+        <v>0.3107077680003603</v>
       </c>
       <c r="D261" t="n">
-        <v>8.683651905020394</v>
+        <v>24.05121161204174</v>
       </c>
     </row>
     <row r="262">
@@ -4679,13 +4721,13 @@
         <v>31.24457804497884</v>
       </c>
       <c r="B262" t="n">
-        <v>87.93453775731837</v>
+        <v>48.77261196710335</v>
       </c>
       <c r="C262" t="n">
-        <v>1.287064930693294</v>
+        <v>0.2952563819491463</v>
       </c>
       <c r="D262" t="n">
-        <v>8.733453775731837</v>
+        <v>24.08630598355168</v>
       </c>
     </row>
     <row r="263">
@@ -4693,13 +4735,13 @@
         <v>31.36474949899799</v>
       </c>
       <c r="B263" t="n">
-        <v>88.41813093101773</v>
+        <v>48.83941592157502</v>
       </c>
       <c r="C263" t="n">
-        <v>1.233835705485169</v>
+        <v>0.2805501249928536</v>
       </c>
       <c r="D263" t="n">
-        <v>8.781813093101773</v>
+        <v>24.11970796078751</v>
       </c>
     </row>
     <row r="264">
@@ -4707,13 +4749,13 @@
         <v>31.48492095301714</v>
       </c>
       <c r="B264" t="n">
-        <v>88.8871473821002</v>
+        <v>48.90303315019776</v>
       </c>
       <c r="C264" t="n">
-        <v>1.182210943890612</v>
+        <v>0.2665453955068188</v>
       </c>
       <c r="D264" t="n">
-        <v>8.828714738210019</v>
+        <v>24.15151657509888</v>
       </c>
     </row>
     <row r="265">
@@ -4721,13 +4763,13 @@
         <v>31.60509240703629</v>
       </c>
       <c r="B265" t="n">
-        <v>89.3414460994763</v>
+        <v>48.96364869771428</v>
       </c>
       <c r="C265" t="n">
-        <v>1.132206167036567</v>
+        <v>0.2532014576460373</v>
       </c>
       <c r="D265" t="n">
-        <v>8.874144609947631</v>
+        <v>24.18182434885714</v>
       </c>
     </row>
     <row r="266">
@@ -4735,13 +4777,13 @@
         <v>31.72526386105544</v>
       </c>
       <c r="B266" t="n">
-        <v>89.78089625016887</v>
+        <v>49.0214345909108</v>
       </c>
       <c r="C266" t="n">
-        <v>1.083835775742537</v>
+        <v>0.2404804413451656</v>
       </c>
       <c r="D266" t="n">
-        <v>8.918089625016888</v>
+        <v>24.2107172954554</v>
       </c>
     </row>
     <row r="267">
@@ -4749,13 +4791,13 @@
         <v>31.84543531507459</v>
       </c>
       <c r="B267" t="n">
-        <v>90.20537717931302</v>
+        <v>49.07654983861694</v>
       </c>
       <c r="C267" t="n">
-        <v>1.03711305052058</v>
+        <v>0.2283473423185198</v>
       </c>
       <c r="D267" t="n">
-        <v>8.960537717931304</v>
+        <v>24.23827491930847</v>
       </c>
     </row>
     <row r="268">
@@ -4763,13 +4805,13 @@
         <v>31.96560676909374</v>
       </c>
       <c r="B268" t="n">
-        <v>90.61477841015621</v>
+        <v>49.12914043170583</v>
       </c>
       <c r="C268" t="n">
-        <v>0.9920501515753131</v>
+        <v>0.2167700220600763</v>
       </c>
       <c r="D268" t="n">
-        <v>9.001477841015621</v>
+        <v>24.26457021585291</v>
       </c>
     </row>
     <row r="269">
@@ -4777,13 +4819,13 @@
         <v>32.08577822311289</v>
       </c>
       <c r="B269" t="n">
-        <v>91.00899964405815</v>
+        <v>49.17933934309403</v>
       </c>
       <c r="C269" t="n">
-        <v>0.9486581188039045</v>
+        <v>0.2057192078434707</v>
       </c>
       <c r="D269" t="n">
-        <v>9.040899964405817</v>
+        <v>24.28966967154701</v>
       </c>
     </row>
     <row r="270">
@@ -4791,13 +4833,13 @@
         <v>32.20594967713204</v>
       </c>
       <c r="B270" t="n">
-        <v>91.38795076049092</v>
+        <v>49.22726652774156</v>
       </c>
       <c r="C270" t="n">
-        <v>0.906946871796082</v>
+        <v>0.1951684927219992</v>
       </c>
       <c r="D270" t="n">
-        <v>9.078795076049094</v>
+        <v>24.31363326387078</v>
       </c>
     </row>
     <row r="271">
@@ -4805,13 +4847,13 @@
         <v>32.32612113115119</v>
       </c>
       <c r="B271" t="n">
-        <v>91.75155181703886</v>
+        <v>49.27302892265192</v>
       </c>
       <c r="C271" t="n">
-        <v>0.8669252098341307</v>
+        <v>0.1850943355286179</v>
       </c>
       <c r="D271" t="n">
-        <v>9.115155181703887</v>
+        <v>24.33651446132596</v>
       </c>
     </row>
     <row r="272">
@@ -4819,13 +4861,13 @@
         <v>32.44629258517034</v>
       </c>
       <c r="B272" t="n">
-        <v>92.10014062848099</v>
+        <v>49.31672044687205</v>
       </c>
       <c r="C272" t="n">
-        <v>0.8285559495582994</v>
+        <v>0.1754760608759427</v>
       </c>
       <c r="D272" t="n">
-        <v>9.150014062848097</v>
+        <v>24.35836022343603</v>
       </c>
     </row>
     <row r="273">
@@ -4833,13 +4875,13 @@
         <v>32.56646403918949</v>
       </c>
       <c r="B273" t="n">
-        <v>92.43577374860946</v>
+        <v>49.35842200149236</v>
       </c>
       <c r="C273" t="n">
-        <v>0.7916127255628926</v>
+        <v>0.1662958591562496</v>
       </c>
       <c r="D273" t="n">
-        <v>9.183577374860945</v>
+        <v>24.37921100074618</v>
       </c>
     </row>
     <row r="274">
@@ -4847,13 +4889,13 @@
         <v>32.68663549320863</v>
       </c>
       <c r="B274" t="n">
-        <v>92.75896252483538</v>
+        <v>49.39820146964671</v>
       </c>
       <c r="C274" t="n">
-        <v>0.7560392537066445</v>
+        <v>0.1575387865414751</v>
       </c>
       <c r="D274" t="n">
-        <v>9.215896252483537</v>
+        <v>24.39910073482335</v>
       </c>
     </row>
     <row r="275">
@@ -4861,13 +4903,13 @@
         <v>32.80680694722778</v>
       </c>
       <c r="B275" t="n">
-        <v>93.06996713570564</v>
+        <v>49.43611371651243</v>
       </c>
       <c r="C275" t="n">
-        <v>0.721806896069872</v>
+        <v>0.1491927649832139</v>
       </c>
       <c r="D275" t="n">
-        <v>9.246996713570562</v>
+        <v>24.41805685825621</v>
       </c>
     </row>
     <row r="276">
@@ -4875,13 +4917,13 @@
         <v>32.92697840124693</v>
       </c>
       <c r="B276" t="n">
-        <v>93.36905286185704</v>
+        <v>49.4722005893103</v>
       </c>
       <c r="C276" t="n">
-        <v>0.6888864531445409</v>
+        <v>0.1412485822127226</v>
       </c>
       <c r="D276" t="n">
-        <v>9.276905286185702</v>
+        <v>24.43610029465515</v>
       </c>
     </row>
     <row r="277">
@@ -4889,13 +4931,13 @@
         <v>33.04714985526608</v>
       </c>
       <c r="B277" t="n">
-        <v>93.65649008601643</v>
+        <v>49.50649091730457</v>
       </c>
       <c r="C277" t="n">
-        <v>0.6572481638342573</v>
+        <v>0.1336998917409169</v>
       </c>
       <c r="D277" t="n">
-        <v>9.305649008601641</v>
+        <v>24.45324545865228</v>
       </c>
     </row>
     <row r="278">
@@ -4903,13 +4945,13 @@
         <v>33.16732130928524</v>
       </c>
       <c r="B278" t="n">
-        <v>93.93255429300058</v>
+        <v>49.53900051180293</v>
       </c>
       <c r="C278" t="n">
-        <v>0.6268617054542696</v>
+        <v>0.1265432128583726</v>
       </c>
       <c r="D278" t="n">
-        <v>9.333255429300056</v>
+        <v>24.46950025590147</v>
       </c>
     </row>
     <row r="279">
@@ -4917,13 +4959,13 @@
         <v>33.28749276330439</v>
       </c>
       <c r="B279" t="n">
-        <v>94.19752606971623</v>
+        <v>49.56973216615656</v>
       </c>
       <c r="C279" t="n">
-        <v>0.5976961937314682</v>
+        <v>0.1197779306353257</v>
       </c>
       <c r="D279" t="n">
-        <v>9.359752606971622</v>
+        <v>24.48486608307828</v>
       </c>
     </row>
     <row r="280">
@@ -4931,13 +4973,13 @@
         <v>33.40766421732354</v>
       </c>
       <c r="B280" t="n">
-        <v>94.45169110516015</v>
+        <v>49.59867565576008</v>
       </c>
       <c r="C280" t="n">
-        <v>0.5697201828043869</v>
+        <v>0.1134062959216717</v>
       </c>
       <c r="D280" t="n">
-        <v>9.385169110516014</v>
+        <v>24.49933782788004</v>
       </c>
     </row>
     <row r="281">
@@ -4945,13 +4987,13 @@
         <v>33.52783567134269</v>
       </c>
       <c r="B281" t="n">
-        <v>94.695340190419</v>
+        <v>49.62580773805156</v>
       </c>
       <c r="C281" t="n">
-        <v>0.5429016652232006</v>
+        <v>0.1074334253469663</v>
       </c>
       <c r="D281" t="n">
-        <v>9.409534019041899</v>
+        <v>24.51290386902578</v>
       </c>
     </row>
     <row r="282">
@@ -4959,13 +5001,13 @@
         <v>33.64800712536183</v>
       </c>
       <c r="B282" t="n">
-        <v>94.92876921866949</v>
+        <v>49.651231092316</v>
       </c>
       <c r="C282" t="n">
-        <v>0.5172080719497292</v>
+        <v>0.1018367150405075</v>
       </c>
       <c r="D282" t="n">
-        <v>9.432876921866947</v>
+        <v>24.525615546158</v>
       </c>
     </row>
     <row r="283">
@@ -4973,13 +5015,13 @@
         <v>33.76817857938098</v>
       </c>
       <c r="B283" t="n">
-        <v>95.15227918517824</v>
+        <v>49.67535171208458</v>
       </c>
       <c r="C283" t="n">
-        <v>0.4926062723574295</v>
+        <v>0.09652678937716797</v>
       </c>
       <c r="D283" t="n">
-        <v>9.455227918517823</v>
+        <v>24.53767585604229</v>
       </c>
     </row>
     <row r="284">
@@ -4987,13 +5029,13 @@
         <v>33.88835003340013</v>
       </c>
       <c r="B284" t="n">
-        <v>95.3661761873019</v>
+        <v>49.69824896651849</v>
       </c>
       <c r="C284" t="n">
-        <v>0.4690625742314061</v>
+        <v>0.09148617598890565</v>
       </c>
       <c r="D284" t="n">
-        <v>9.47661761873019</v>
+        <v>24.54912448325925</v>
       </c>
     </row>
     <row r="285">
@@ -5001,13 +5043,13 @@
         <v>34.00852148741928</v>
       </c>
       <c r="B285" t="n">
-        <v>95.57077142448705</v>
+        <v>49.71997712776106</v>
       </c>
       <c r="C285" t="n">
-        <v>0.4465427237684039</v>
+        <v>0.08670292737813033</v>
       </c>
       <c r="D285" t="n">
-        <v>9.497077142448704</v>
+        <v>24.55998856388053</v>
       </c>
     </row>
     <row r="286">
@@ -5015,13 +5057,13 @@
         <v>34.12869294143843</v>
       </c>
       <c r="B286" t="n">
-        <v>95.76638119827025</v>
+        <v>49.74058918532142</v>
       </c>
       <c r="C286" t="n">
-        <v>0.4250119055768102</v>
+        <v>0.08216537840699562</v>
       </c>
       <c r="D286" t="n">
-        <v>9.516638119827023</v>
+        <v>24.57029459266071</v>
       </c>
     </row>
     <row r="287">
@@ -5029,13 +5071,13 @@
         <v>34.24886439545758</v>
       </c>
       <c r="B287" t="n">
-        <v>95.95332691227804</v>
+        <v>49.76013684607459</v>
       </c>
       <c r="C287" t="n">
-        <v>0.4044347426766551</v>
+        <v>0.07786214629739897</v>
       </c>
       <c r="D287" t="n">
-        <v>9.535332691227802</v>
+        <v>24.58006842303729</v>
       </c>
     </row>
     <row r="288">
@@ -5043,13 +5085,13 @@
         <v>34.36903584947673</v>
       </c>
       <c r="B288" t="n">
-        <v>96.13193507222694</v>
+        <v>49.7786705342614</v>
       </c>
       <c r="C288" t="n">
-        <v>0.3847752964996106</v>
+        <v>0.07378213063098166</v>
       </c>
       <c r="D288" t="n">
-        <v>9.553193507222693</v>
+        <v>24.5893352671307</v>
       </c>
     </row>
     <row r="289">
@@ -5057,13 +5099,13 @@
         <v>34.48920730349588</v>
       </c>
       <c r="B289" t="n">
-        <v>96.30253728592342</v>
+        <v>49.79623939148854</v>
       </c>
       <c r="C289" t="n">
-        <v>0.3659970668889914</v>
+        <v>0.06991451334912879</v>
       </c>
       <c r="D289" t="n">
-        <v>9.570253728592339</v>
+        <v>24.59811969574427</v>
       </c>
     </row>
     <row r="290">
@@ -5071,13 +5113,13 @@
         <v>34.60937875751502</v>
       </c>
       <c r="B290" t="n">
-        <v>96.46547026326392</v>
+        <v>49.81289127672854</v>
       </c>
       <c r="C290" t="n">
-        <v>0.3480629920997551</v>
+        <v>0.06624875875296954</v>
       </c>
       <c r="D290" t="n">
-        <v>9.586547026326391</v>
+        <v>24.60644563836427</v>
       </c>
     </row>
     <row r="291">
@@ -5085,13 +5127,13 @@
         <v>34.72955021153417</v>
       </c>
       <c r="B291" t="n">
-        <v>96.62107578559298</v>
+        <v>49.82867276631978</v>
       </c>
       <c r="C291" t="n">
-        <v>0.3309354521712642</v>
+        <v>0.06277461350337624</v>
       </c>
       <c r="D291" t="n">
-        <v>9.602107578559297</v>
+        <v>24.61433638315989</v>
       </c>
     </row>
     <row r="292">
@@ -5099,13 +5141,13 @@
         <v>34.84972166555333</v>
       </c>
       <c r="B292" t="n">
-        <v>96.76967376175048</v>
+        <v>49.84362915396647</v>
       </c>
       <c r="C292" t="n">
-        <v>0.3145792346550988</v>
+        <v>0.05948210662096576</v>
       </c>
       <c r="D292" t="n">
-        <v>9.616967376175047</v>
+        <v>24.62181457698323</v>
       </c>
     </row>
     <row r="293">
@@ -5113,13 +5155,13 @@
         <v>34.96989311957248</v>
       </c>
       <c r="B293" t="n">
-        <v>96.91151314526925</v>
+        <v>49.85780445073868</v>
       </c>
       <c r="C293" t="n">
-        <v>0.2989669371717674</v>
+        <v>0.05636154948609855</v>
       </c>
       <c r="D293" t="n">
-        <v>9.631151314526925</v>
+        <v>24.62890222536934</v>
       </c>
     </row>
     <row r="294">
@@ -5127,13 +5169,13 @@
         <v>35.09006457359163</v>
       </c>
       <c r="B294" t="n">
-        <v>97.04682867641306</v>
+        <v>49.87124138507233</v>
       </c>
       <c r="C294" t="n">
-        <v>0.2840727217999676</v>
+        <v>0.05340353583887889</v>
       </c>
       <c r="D294" t="n">
-        <v>9.644682867641304</v>
+        <v>24.63562069253616</v>
       </c>
     </row>
     <row r="295">
@@ -5141,13 +5183,13 @@
         <v>35.21023602761078</v>
       </c>
       <c r="B295" t="n">
-        <v>97.17585255513961</v>
+        <v>49.88398140276917</v>
       </c>
       <c r="C295" t="n">
-        <v>0.2698710302305348</v>
+        <v>0.05059894177915493</v>
       </c>
       <c r="D295" t="n">
-        <v>9.657585255513959</v>
+        <v>24.64199070138458</v>
       </c>
     </row>
     <row r="296">
@@ -5155,13 +5197,13 @@
         <v>35.33040748162993</v>
       </c>
       <c r="B296" t="n">
-        <v>97.29881444110062</v>
+        <v>49.89606466699678</v>
       </c>
       <c r="C296" t="n">
-        <v>0.2563365837664418</v>
+        <v>0.04793892576651861</v>
       </c>
       <c r="D296" t="n">
-        <v>9.669881444110061</v>
+        <v>24.64803233349839</v>
       </c>
     </row>
     <row r="297">
@@ -5169,13 +5211,13 @@
         <v>35.45057893564908</v>
       </c>
       <c r="B297" t="n">
-        <v>97.41594145364181</v>
+        <v>49.9075300574429</v>
       </c>
       <c r="C297" t="n">
-        <v>0.2434443833227992</v>
+        <v>0.04541492880648201</v>
       </c>
       <c r="D297" t="n">
-        <v>9.68159414536418</v>
+        <v>24.65376502872145</v>
       </c>
     </row>
     <row r="298">
@@ -5183,13 +5225,13 @@
         <v>35.57075038966822</v>
       </c>
       <c r="B298" t="n">
-        <v>97.52745817180282</v>
+        <v>49.91840937996808</v>
       </c>
       <c r="C298" t="n">
-        <v>0.2311697094268555</v>
+        <v>0.04301994914051634</v>
       </c>
       <c r="D298" t="n">
-        <v>9.692745817180281</v>
+        <v>24.65920468998404</v>
       </c>
     </row>
     <row r="299">
@@ -5197,13 +5239,13 @@
         <v>35.69092184368737</v>
       </c>
       <c r="B299" t="n">
-        <v>97.63358663431737</v>
+        <v>49.92872670005313</v>
       </c>
       <c r="C299" t="n">
-        <v>0.2194881222179949</v>
+        <v>0.04074868898127895</v>
       </c>
       <c r="D299" t="n">
-        <v>9.703358663431736</v>
+        <v>24.66436335002657</v>
       </c>
     </row>
     <row r="300">
@@ -5211,13 +5253,13 @@
         <v>35.81109329770652</v>
       </c>
       <c r="B300" t="n">
-        <v>97.73454633961308</v>
+        <v>49.93850751297705</v>
       </c>
       <c r="C300" t="n">
-        <v>0.2083754614477412</v>
+        <v>0.03859553578491378</v>
       </c>
       <c r="D300" t="n">
-        <v>9.713454633961307</v>
+        <v>24.66925375648852</v>
       </c>
     </row>
     <row r="301">
@@ -5225,13 +5267,13 @@
         <v>35.93126475172567</v>
       </c>
       <c r="B301" t="n">
-        <v>97.83055424581158</v>
+        <v>49.94777668634752</v>
       </c>
       <c r="C301" t="n">
-        <v>0.1978078464797551</v>
+        <v>0.03655501518345244</v>
       </c>
       <c r="D301" t="n">
-        <v>9.723055424581158</v>
+        <v>24.67388834317376</v>
       </c>
     </row>
     <row r="302">
@@ -5239,13 +5281,13 @@
         <v>36.05143620574482</v>
       </c>
       <c r="B302" t="n">
-        <v>97.92182477072852</v>
+        <v>49.9565584601009</v>
       </c>
       <c r="C302" t="n">
-        <v>0.1877616762898348</v>
+        <v>0.0346217909848143</v>
       </c>
       <c r="D302" t="n">
-        <v>9.73218247707285</v>
+        <v>24.67827923005045</v>
       </c>
     </row>
     <row r="303">
@@ -5253,13 +5295,13 @@
         <v>36.17160765976397</v>
       </c>
       <c r="B303" t="n">
-        <v>98.00856979187348</v>
+        <v>49.96487644650226</v>
       </c>
       <c r="C303" t="n">
-        <v>0.1782136294659162</v>
+        <v>0.03279066517280652</v>
       </c>
       <c r="D303" t="n">
-        <v>9.740856979187347</v>
+        <v>24.68243822325113</v>
       </c>
     </row>
     <row r="304">
@@ -5267,13 +5309,13 @@
         <v>36.29177911378312</v>
       </c>
       <c r="B304" t="n">
-        <v>98.09099864645006</v>
+        <v>49.97275363014531</v>
       </c>
       <c r="C304" t="n">
-        <v>0.1691406642080724</v>
+        <v>0.03105657790712402</v>
       </c>
       <c r="D304" t="n">
-        <v>9.749099864645006</v>
+        <v>24.68637681507265</v>
       </c>
     </row>
     <row r="305">
@@ -5281,13 +5323,13 @@
         <v>36.41195056780227</v>
       </c>
       <c r="B305" t="n">
-        <v>98.16931813135584</v>
+        <v>49.98021236795245</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1605200183285146</v>
+        <v>0.02941460752334953</v>
       </c>
       <c r="D305" t="n">
-        <v>9.756931813135582</v>
+        <v>24.69010618397622</v>
       </c>
     </row>
     <row r="306">
@@ -5295,13 +5337,13 @@
         <v>36.53212202182142</v>
       </c>
       <c r="B306" t="n">
-        <v>98.24373250318234</v>
+        <v>49.98727438917478</v>
       </c>
       <c r="C306" t="n">
-        <v>0.1523292092515914</v>
+        <v>0.02785997053295361</v>
       </c>
       <c r="D306" t="n">
-        <v>9.764373250318235</v>
+        <v>24.69363719458739</v>
       </c>
     </row>
     <row r="307">
@@ -5309,13 +5351,13 @@
         <v>36.65229347584057</v>
       </c>
       <c r="B307" t="n">
-        <v>98.31444347821515</v>
+        <v>49.99396079539206</v>
       </c>
       <c r="C307" t="n">
-        <v>0.1445460340137882</v>
+        <v>0.02638802162329434</v>
       </c>
       <c r="D307" t="n">
-        <v>9.771444347821514</v>
+        <v>24.69698039769603</v>
       </c>
     </row>
     <row r="308">
@@ -5323,13 +5365,13 @@
         <v>36.77246492985972</v>
       </c>
       <c r="B308" t="n">
-        <v>98.38165023243378</v>
+        <v>50.00029206051274</v>
       </c>
       <c r="C308" t="n">
-        <v>0.1371485692637288</v>
+        <v>0.02499425365761787</v>
       </c>
       <c r="D308" t="n">
-        <v>9.778165023243377</v>
+        <v>24.70014603025637</v>
       </c>
     </row>
     <row r="309">
@@ -5337,13 +5379,13 @@
         <v>36.89263638387887</v>
       </c>
       <c r="B309" t="n">
-        <v>98.44554940151173</v>
+        <v>50.00628803077394</v>
       </c>
       <c r="C309" t="n">
-        <v>0.1301151712621744</v>
+        <v>0.02367429767505801</v>
       </c>
       <c r="D309" t="n">
-        <v>9.784554940151173</v>
+        <v>24.70314401538697</v>
       </c>
     </row>
     <row r="310">
@@ -5351,13 +5393,13 @@
         <v>37.01280783789802</v>
       </c>
       <c r="B310" t="n">
-        <v>98.5063350808165</v>
+        <v>50.01196792474148</v>
       </c>
       <c r="C310" t="n">
-        <v>0.1234244758820239</v>
+        <v>0.02242392289063638</v>
       </c>
       <c r="D310" t="n">
-        <v>9.790633508081649</v>
+        <v>24.70598396237074</v>
       </c>
     </row>
     <row r="311">
@@ -5365,13 +5407,13 @@
         <v>37.13297929191717</v>
       </c>
       <c r="B311" t="n">
-        <v>98.56417914070234</v>
+        <v>50.01735033330982</v>
       </c>
       <c r="C311" t="n">
-        <v>0.117057565309111</v>
+        <v>0.02123903669526232</v>
       </c>
       <c r="D311" t="n">
-        <v>9.796417914070231</v>
+        <v>24.70867516665491</v>
       </c>
     </row>
     <row r="312">
@@ -5379,13 +5421,13 @@
         <v>37.25315074593632</v>
       </c>
       <c r="B312" t="n">
-        <v>98.61918751806792</v>
+        <v>50.02245321970216</v>
       </c>
       <c r="C312" t="n">
-        <v>0.1110027790417056</v>
+        <v>0.02011568465573301</v>
       </c>
       <c r="D312" t="n">
-        <v>9.801918751806788</v>
+        <v>24.71122660985108</v>
       </c>
     </row>
     <row r="313">
@@ -5393,13 +5435,13 @@
         <v>37.37332219995547</v>
       </c>
       <c r="B313" t="n">
-        <v>98.67146946902152</v>
+        <v>50.02729384311586</v>
       </c>
       <c r="C313" t="n">
-        <v>0.1052480912318245</v>
+        <v>0.01905006732344277</v>
       </c>
       <c r="D313" t="n">
-        <v>9.807146946902149</v>
+        <v>24.71364692155793</v>
       </c>
     </row>
     <row r="314">
@@ -5407,13 +5449,13 @@
         <v>37.49349365397461</v>
       </c>
       <c r="B314" t="n">
-        <v>98.72113353768668</v>
+        <v>50.0318861683398</v>
       </c>
       <c r="C314" t="n">
-        <v>0.09978155439982725</v>
+        <v>0.01803911048257411</v>
       </c>
       <c r="D314" t="n">
-        <v>9.812113353768666</v>
+        <v>24.7159430841699</v>
       </c>
     </row>
     <row r="315">
@@ -5421,13 +5463,13 @@
         <v>37.61366510799376</v>
       </c>
       <c r="B315" t="n">
-        <v>98.76828674491765</v>
+        <v>50.0362407370903</v>
       </c>
       <c r="C315" t="n">
-        <v>0.09459138873271919</v>
+        <v>0.01708049347426653</v>
       </c>
       <c r="D315" t="n">
-        <v>9.816828674491761</v>
+        <v>24.71812036854515</v>
       </c>
     </row>
     <row r="316">
@@ -5435,13 +5477,13 @@
         <v>37.73383656201291</v>
       </c>
       <c r="B316" t="n">
-        <v>98.81303458829929</v>
+        <v>50.04036777181483</v>
       </c>
       <c r="C316" t="n">
-        <v>0.08966598208415374</v>
+        <v>0.01617196592366795</v>
       </c>
       <c r="D316" t="n">
-        <v>9.821303458829927</v>
+        <v>24.72018388590741</v>
       </c>
     </row>
     <row r="317">
@@ -5449,13 +5491,13 @@
         <v>37.85400801603206</v>
       </c>
       <c r="B317" t="n">
-        <v>98.85548104214719</v>
+        <v>50.04427731464399</v>
       </c>
       <c r="C317" t="n">
-        <v>0.08499388997443086</v>
+        <v>0.01531131715097187</v>
       </c>
       <c r="D317" t="n">
-        <v>9.825548104214716</v>
+        <v>24.722138657322</v>
       </c>
     </row>
     <row r="318">
@@ -5463,13 +5505,13 @@
         <v>37.97417947005121</v>
       </c>
       <c r="B318" t="n">
-        <v>98.89572855750761</v>
+        <v>50.04797922739154</v>
       </c>
       <c r="C318" t="n">
-        <v>0.08056383559049742</v>
+        <v>0.0144963761714174</v>
       </c>
       <c r="D318" t="n">
-        <v>9.829572855750758</v>
+        <v>24.72398961369577</v>
       </c>
     </row>
     <row r="319">
@@ -5477,13 +5519,13 @@
         <v>38.09435092407036</v>
       </c>
       <c r="B319" t="n">
-        <v>98.93387806215746</v>
+        <v>50.05148319155438</v>
       </c>
       <c r="C319" t="n">
-        <v>0.07636470978594714</v>
+        <v>0.01372501169528933</v>
       </c>
       <c r="D319" t="n">
-        <v>9.833387806215743</v>
+        <v>24.72574159577719</v>
       </c>
     </row>
     <row r="320">
@@ -5491,13 +5533,13 @@
         <v>38.21452237808951</v>
       </c>
       <c r="B320" t="n">
-        <v>98.97002896060435</v>
+        <v>50.05479870831255</v>
       </c>
       <c r="C320" t="n">
-        <v>0.07238557108102073</v>
+        <v>0.01299513212791808</v>
       </c>
       <c r="D320" t="n">
-        <v>9.837002896060433</v>
+        <v>24.72739935415627</v>
       </c>
     </row>
     <row r="321">
@@ -5505,13 +5547,13 @@
         <v>38.33469383210866</v>
       </c>
       <c r="B321" t="n">
-        <v>99.00427913408654</v>
+        <v>50.05793509852923</v>
       </c>
       <c r="C321" t="n">
-        <v>0.06861564566260578</v>
+        <v>0.0123046855696797</v>
       </c>
       <c r="D321" t="n">
-        <v>9.840427913408652</v>
+        <v>24.72896754926461</v>
       </c>
     </row>
     <row r="322">
@@ -5519,13 +5561,13 @@
         <v>38.45486528612781</v>
       </c>
       <c r="B322" t="n">
-        <v>99.036724940573</v>
+        <v>50.06090150275075</v>
       </c>
       <c r="C322" t="n">
-        <v>0.06504432738423702</v>
+        <v>0.01165165981599594</v>
       </c>
       <c r="D322" t="n">
-        <v>9.843672494057298</v>
+        <v>24.73045075137537</v>
       </c>
     </row>
     <row r="323">
@@ -5533,13 +5575,13 @@
         <v>38.57503674014696</v>
       </c>
       <c r="B323" t="n">
-        <v>99.06746121476336</v>
+        <v>50.06370688120658</v>
       </c>
       <c r="C323" t="n">
-        <v>0.06166117776609538</v>
+        <v>0.01103408235733407</v>
       </c>
       <c r="D323" t="n">
-        <v>9.846746121476333</v>
+        <v>24.73185344060329</v>
       </c>
     </row>
     <row r="324">
@@ -5547,13 +5589,13 @@
         <v>38.69520819416611</v>
       </c>
       <c r="B324" t="n">
-        <v>99.0965812680879</v>
+        <v>50.06636001380935</v>
       </c>
       <c r="C324" t="n">
-        <v>0.05845592599500947</v>
+        <v>0.01045002037920713</v>
       </c>
       <c r="D324" t="n">
-        <v>9.849658126808787</v>
+        <v>24.73318000690467</v>
       </c>
     </row>
     <row r="325">
@@ -5561,13 +5603,13 @@
         <v>38.81537964818526</v>
       </c>
       <c r="B325" t="n">
-        <v>99.12417688870762</v>
+        <v>50.06886950015481</v>
       </c>
       <c r="C325" t="n">
-        <v>0.05541846892445448</v>
+        <v>0.009897580762173737</v>
       </c>
       <c r="D325" t="n">
-        <v>9.85241768887076</v>
+        <v>24.7344347500774</v>
       </c>
     </row>
     <row r="326">
@@ -5575,13 +5617,13 @@
         <v>38.93555110220441</v>
       </c>
       <c r="B326" t="n">
-        <v>99.15033834151417</v>
+        <v>50.07124375952187</v>
       </c>
       <c r="C326" t="n">
-        <v>0.0525388710745526</v>
+        <v>0.009374910081838177</v>
       </c>
       <c r="D326" t="n">
-        <v>9.855033834151415</v>
+        <v>24.73562187976093</v>
       </c>
     </row>
     <row r="327">
@@ -5589,13 +5631,13 @@
         <v>39.05572255622356</v>
       </c>
       <c r="B327" t="n">
-        <v>99.1751543681299</v>
+        <v>50.07349103087257</v>
       </c>
       <c r="C327" t="n">
-        <v>0.04980736463207286</v>
+        <v>0.008880194608850369</v>
       </c>
       <c r="D327" t="n">
-        <v>9.857515436812987</v>
+        <v>24.73674551543628</v>
       </c>
     </row>
     <row r="328">
@@ -5603,13 +5645,13 @@
         <v>39.17589401024271</v>
       </c>
       <c r="B328" t="n">
-        <v>99.19871218690778</v>
+        <v>50.0756193728521</v>
       </c>
       <c r="C328" t="n">
-        <v>0.04721434945043122</v>
+        <v>0.008411660308905874</v>
       </c>
       <c r="D328" t="n">
-        <v>9.859871218690776</v>
+        <v>24.73780968642605</v>
       </c>
     </row>
     <row r="329">
@@ -5617,13 +5659,13 @@
         <v>39.29606546426185</v>
       </c>
       <c r="B329" t="n">
-        <v>99.22109749293153</v>
+        <v>50.07763666378881</v>
       </c>
       <c r="C329" t="n">
-        <v>0.04475039304969075</v>
+        <v>0.007967572842745926</v>
       </c>
       <c r="D329" t="n">
-        <v>9.86210974929315</v>
+        <v>24.7388183318944</v>
       </c>
     </row>
     <row r="330">
@@ -5631,13 +5673,13 @@
         <v>39.416236918281</v>
       </c>
       <c r="B330" t="n">
-        <v>99.24239062766179</v>
+        <v>50.07955060169417</v>
       </c>
       <c r="C330" t="n">
-        <v>0.04240665222458122</v>
+        <v>0.007546237566157325</v>
       </c>
       <c r="D330" t="n">
-        <v>9.864239062766178</v>
+        <v>24.73977530084708</v>
       </c>
     </row>
     <row r="331">
@@ -5645,13 +5687,13 @@
         <v>39.53640837230015</v>
       </c>
       <c r="B331" t="n">
-        <v>99.26261772389789</v>
+        <v>50.08136869564748</v>
       </c>
       <c r="C331" t="n">
-        <v>0.04018025053114554</v>
+        <v>0.007146001426551817</v>
       </c>
       <c r="D331" t="n">
-        <v>9.866261772389787</v>
+        <v>24.74068434782374</v>
       </c>
     </row>
     <row r="332">
@@ -5659,13 +5701,13 @@
         <v>39.6565798263193</v>
       </c>
       <c r="B332" t="n">
-        <v>99.2818127069382</v>
+        <v>50.08309491996072</v>
       </c>
       <c r="C332" t="n">
-        <v>0.0380674538030556</v>
+        <v>0.0067659895168438</v>
       </c>
       <c r="D332" t="n">
-        <v>9.868181270693819</v>
+        <v>24.74154745998036</v>
       </c>
     </row>
     <row r="333">
@@ -5673,13 +5715,13 @@
         <v>39.77675128033845</v>
       </c>
       <c r="B333" t="n">
-        <v>99.30001920237196</v>
+        <v>50.0847315101017</v>
       </c>
       <c r="C333" t="n">
-        <v>0.03606346016046373</v>
+        <v>0.006405709719999252</v>
       </c>
       <c r="D333" t="n">
-        <v>9.870001920237195</v>
+        <v>24.74236575505085</v>
       </c>
     </row>
     <row r="334">
@@ -5687,13 +5729,13 @@
         <v>39.8969227343576</v>
       </c>
       <c r="B334" t="n">
-        <v>99.31728007668043</v>
+        <v>50.0862823427581</v>
       </c>
       <c r="C334" t="n">
-        <v>0.03416355127873472</v>
+        <v>0.006064308619996213</v>
       </c>
       <c r="D334" t="n">
-        <v>9.871728007668041</v>
+        <v>24.74314117137905</v>
       </c>
     </row>
     <row r="335">
@@ -5701,13 +5743,13 @@
         <v>40.01709418837675</v>
       </c>
       <c r="B335" t="n">
-        <v>99.33363743723689</v>
+        <v>50.08775122372721</v>
       </c>
       <c r="C335" t="n">
-        <v>0.03236309238844574</v>
+        <v>0.005740948406657329</v>
       </c>
       <c r="D335" t="n">
-        <v>9.873363743723687</v>
+        <v>24.7438756118636</v>
       </c>
     </row>
     <row r="336">
@@ -5715,13 +5757,13 @@
         <v>40.1372656423959</v>
       </c>
       <c r="B336" t="n">
-        <v>99.34913263230661</v>
+        <v>50.08914188791594</v>
       </c>
       <c r="C336" t="n">
-        <v>0.03065753227538645</v>
+        <v>0.005434806875649841</v>
       </c>
       <c r="D336" t="n">
-        <v>9.874913263230658</v>
+        <v>24.74457094395797</v>
       </c>
     </row>
     <row r="337">
@@ -5729,13 +5771,13 @@
         <v>40.25743709641505</v>
       </c>
       <c r="B337" t="n">
-        <v>99.36380625104684</v>
+        <v>50.09045799934082</v>
       </c>
       <c r="C337" t="n">
-        <v>0.02904240328055901</v>
+        <v>0.005145077428485616</v>
       </c>
       <c r="D337" t="n">
-        <v>9.876380625104682</v>
+        <v>24.74522899967041</v>
       </c>
     </row>
     <row r="338">
@@ -5743,13 +5785,13 @@
         <v>40.3776085504342</v>
       </c>
       <c r="B338" t="n">
-        <v>99.3776981235069</v>
+        <v>50.09170315112802</v>
       </c>
       <c r="C338" t="n">
-        <v>0.02751332130017774</v>
+        <v>0.00487096907252107</v>
       </c>
       <c r="D338" t="n">
-        <v>9.877769812350689</v>
+        <v>24.74585157556401</v>
       </c>
     </row>
     <row r="339">
@@ -5757,13 +5799,13 @@
         <v>40.49778000445335</v>
       </c>
       <c r="B339" t="n">
-        <v>99.39084732062807</v>
+        <v>50.09288086551332</v>
       </c>
       <c r="C339" t="n">
-        <v>0.02606598578566969</v>
+        <v>0.004611706420957274</v>
       </c>
       <c r="D339" t="n">
-        <v>9.879084732062806</v>
+        <v>24.74644043275666</v>
       </c>
     </row>
     <row r="340">
@@ -5771,13 +5813,13 @@
         <v>40.6179514584725</v>
       </c>
       <c r="B340" t="n">
-        <v>99.40329215424364</v>
+        <v>50.0939945938421</v>
       </c>
       <c r="C340" t="n">
-        <v>0.02469617974367423</v>
+        <v>0.00436652969283988</v>
       </c>
       <c r="D340" t="n">
-        <v>9.880329215424362</v>
+        <v>24.74699729692105</v>
       </c>
     </row>
     <row r="341">
@@ -5785,13 +5827,13 @@
         <v>40.73812291249165</v>
       </c>
       <c r="B341" t="n">
-        <v>99.41507017707893</v>
+        <v>50.0950477165694</v>
       </c>
       <c r="C341" t="n">
-        <v>0.02339976973604318</v>
+        <v>0.004134694713059148</v>
       </c>
       <c r="D341" t="n">
-        <v>9.881507017707891</v>
+        <v>24.7475238582847</v>
       </c>
     </row>
     <row r="342">
@@ -5799,13 +5841,13 @@
         <v>40.8582943665108</v>
       </c>
       <c r="B342" t="n">
-        <v>99.42621818275124</v>
+        <v>50.09604354325986</v>
       </c>
       <c r="C342" t="n">
-        <v>0.0221727058798408</v>
+        <v>0.003915472912349937</v>
       </c>
       <c r="D342" t="n">
-        <v>9.882621818275123</v>
+        <v>24.74802177162993</v>
       </c>
     </row>
     <row r="343">
@@ -5813,13 +5855,13 @@
         <v>40.97846582052995</v>
       </c>
       <c r="B343" t="n">
-        <v>99.43677220576988</v>
+        <v>50.09698531258773</v>
       </c>
       <c r="C343" t="n">
-        <v>0.02101102184734375</v>
+        <v>0.003708151327291707</v>
       </c>
       <c r="D343" t="n">
-        <v>9.883677220576986</v>
+        <v>24.74849265629386</v>
       </c>
     </row>
     <row r="344">
@@ -5827,13 +5869,13 @@
         <v>41.0986372745491</v>
       </c>
       <c r="B344" t="n">
-        <v>99.44676752153619</v>
+        <v>50.0978761923369</v>
       </c>
       <c r="C344" t="n">
-        <v>0.01991083486604117</v>
+        <v>0.003512032600308525</v>
       </c>
       <c r="D344" t="n">
-        <v>9.884676752153617</v>
+        <v>24.74893809616845</v>
       </c>
     </row>
     <row r="345">
@@ -5841,13 +5883,13 @@
         <v>41.21880872856824</v>
       </c>
       <c r="B345" t="n">
-        <v>99.45623864634348</v>
+        <v>50.09871927940087</v>
       </c>
       <c r="C345" t="n">
-        <v>0.01886834571863467</v>
+        <v>0.003326434979669066</v>
       </c>
       <c r="D345" t="n">
-        <v>9.885623864634345</v>
+        <v>24.74935963970043</v>
       </c>
     </row>
     <row r="346">
@@ -5855,13 +5897,13 @@
         <v>41.33898018258739</v>
       </c>
       <c r="B346" t="n">
-        <v>99.46521933737708</v>
+        <v>50.09951759978276</v>
       </c>
       <c r="C346" t="n">
-        <v>0.01787983874303813</v>
+        <v>0.00315069231948658</v>
       </c>
       <c r="D346" t="n">
-        <v>9.886521933737706</v>
+        <v>24.74975879989138</v>
       </c>
     </row>
     <row r="347">
@@ -5869,13 +5911,13 @@
         <v>41.45915163660654</v>
       </c>
       <c r="B347" t="n">
-        <v>99.47374259271436</v>
+        <v>50.10027410859532</v>
       </c>
       <c r="C347" t="n">
-        <v>0.01694168183237802</v>
+        <v>0.002984154079718949</v>
       </c>
       <c r="D347" t="n">
-        <v>9.887374259271434</v>
+        <v>24.75013705429766</v>
       </c>
     </row>
     <row r="348">
@@ -5883,13 +5925,13 @@
         <v>41.57932309062569</v>
       </c>
       <c r="B348" t="n">
-        <v>99.48184065132465</v>
+        <v>50.10099169006092</v>
       </c>
       <c r="C348" t="n">
-        <v>0.01605032643499322</v>
+        <v>0.002826185326168643</v>
       </c>
       <c r="D348" t="n">
-        <v>9.888184065132462</v>
+        <v>24.75049584503046</v>
       </c>
     </row>
     <row r="349">
@@ -5897,13 +5939,13 @@
         <v>41.69949454464484</v>
       </c>
       <c r="B349" t="n">
-        <v>99.48953419749463</v>
+        <v>50.10167315750821</v>
       </c>
       <c r="C349" t="n">
-        <v>0.01520349582611957</v>
+        <v>0.002676166731214162</v>
       </c>
       <c r="D349" t="n">
-        <v>9.888953419749459</v>
+        <v>24.7508365787541</v>
       </c>
     </row>
     <row r="350">
@@ -5911,13 +5953,13 @@
         <v>41.81966599866399</v>
       </c>
       <c r="B350" t="n">
-        <v>99.49683233690958</v>
+        <v>50.1023202034469</v>
       </c>
       <c r="C350" t="n">
-        <v>0.01440018774063352</v>
+        <v>0.002533725704898535</v>
       </c>
       <c r="D350" t="n">
-        <v>9.889683233690954</v>
+        <v>24.75116010172345</v>
       </c>
     </row>
     <row r="351">
@@ -5925,13 +5967,13 @@
         <v>41.93983745268314</v>
       </c>
       <c r="B351" t="n">
-        <v>99.50375192531921</v>
+        <v>50.10293365975556</v>
       </c>
       <c r="C351" t="n">
-        <v>0.01363854686182202</v>
+        <v>0.002398679117044396</v>
       </c>
       <c r="D351" t="n">
-        <v>9.890375192531918</v>
+        <v>24.75146682987778</v>
       </c>
     </row>
     <row r="352">
@@ -5939,13 +5981,13 @@
         <v>42.06000890670229</v>
       </c>
       <c r="B352" t="n">
-        <v>99.51030953785981</v>
+        <v>50.1035149668031</v>
       </c>
       <c r="C352" t="n">
-        <v>0.01291674876016291</v>
+        <v>0.002270709884094966</v>
       </c>
       <c r="D352" t="n">
-        <v>9.891030953785979</v>
+        <v>24.75175748340155</v>
       </c>
     </row>
     <row r="353">
@@ -5953,13 +5995,13 @@
         <v>42.18018036072144</v>
       </c>
       <c r="B353" t="n">
-        <v>99.51652144436521</v>
+        <v>50.10406553986443</v>
       </c>
       <c r="C353" t="n">
-        <v>0.01223300261085641</v>
+        <v>0.002149506446707897</v>
       </c>
       <c r="D353" t="n">
-        <v>9.891652144436518</v>
+        <v>24.75203276993221</v>
       </c>
     </row>
     <row r="354">
@@ -5967,13 +6009,13 @@
         <v>42.30035181474059</v>
       </c>
       <c r="B354" t="n">
-        <v>99.52240360936675</v>
+        <v>50.10458676912037</v>
       </c>
       <c r="C354" t="n">
-        <v>0.01158555119382496</v>
+        <v>0.002034762769755242</v>
       </c>
       <c r="D354" t="n">
-        <v>9.892240360936672</v>
+        <v>24.75229338456019</v>
       </c>
     </row>
     <row r="355">
@@ -5981,13 +6023,13 @@
         <v>42.42052326875974</v>
       </c>
       <c r="B355" t="n">
-        <v>99.5279716920933</v>
+        <v>50.10508001965775</v>
       </c>
       <c r="C355" t="n">
-        <v>0.01097267089371343</v>
+        <v>0.001926178342323503</v>
       </c>
       <c r="D355" t="n">
-        <v>9.892797169209327</v>
+        <v>24.75254000982887</v>
       </c>
     </row>
     <row r="356">
@@ -5995,13 +6037,13 @@
         <v>42.54069472277889</v>
       </c>
       <c r="B356" t="n">
-        <v>99.53324104647123</v>
+        <v>50.10554663146932</v>
       </c>
       <c r="C356" t="n">
-        <v>0.010392671699889</v>
+        <v>0.001823458177713596</v>
       </c>
       <c r="D356" t="n">
-        <v>9.893324104647121</v>
+        <v>24.75277331573466</v>
       </c>
     </row>
     <row r="357">
@@ -6009,13 +6051,13 @@
         <v>42.66086617679804</v>
       </c>
       <c r="B357" t="n">
-        <v>99.53822672112447</v>
+        <v>50.10598791945385</v>
       </c>
       <c r="C357" t="n">
-        <v>0.009843897206441164</v>
+        <v>0.001726312813440862</v>
       </c>
       <c r="D357" t="n">
-        <v>9.893822672112444</v>
+        <v>24.75299395972692</v>
       </c>
     </row>
     <row r="358">
@@ -6023,13 +6065,13 @@
         <v>42.78103763081719</v>
       </c>
       <c r="B358" t="n">
-        <v>99.54294345937444</v>
+        <v>50.10640517341599</v>
       </c>
       <c r="C358" t="n">
-        <v>0.009324724612181739</v>
+        <v>0.001634458311235066</v>
       </c>
       <c r="D358" t="n">
-        <v>9.894294345937443</v>
+        <v>24.75320258670799</v>
       </c>
     </row>
     <row r="359">
@@ -6037,13 +6079,13 @@
         <v>42.90120908483634</v>
       </c>
       <c r="B359" t="n">
-        <v>99.54740569924012</v>
+        <v>50.10679965806643</v>
       </c>
       <c r="C359" t="n">
-        <v>0.008833564720644893</v>
+        <v>0.001547616257040398</v>
       </c>
       <c r="D359" t="n">
-        <v>9.894740569924009</v>
+        <v>24.75339982903321</v>
       </c>
     </row>
     <row r="360">
@@ -6051,13 +6093,13 @@
         <v>43.02138053885549</v>
       </c>
       <c r="B360" t="n">
-        <v>99.55162757343794</v>
+        <v>50.10717261302177</v>
       </c>
       <c r="C360" t="n">
-        <v>0.008368861940087107</v>
+        <v>0.001465513761015469</v>
       </c>
       <c r="D360" t="n">
-        <v>9.895162757343792</v>
+        <v>24.75358630651089</v>
       </c>
     </row>
     <row r="361">
@@ -6065,13 +6107,13 @@
         <v>43.14155199287463</v>
       </c>
       <c r="B361" t="n">
-        <v>99.55562290938195</v>
+        <v>50.10752525280461</v>
       </c>
       <c r="C361" t="n">
-        <v>0.007929094283487219</v>
+        <v>0.001387883457533322</v>
       </c>
       <c r="D361" t="n">
-        <v>9.895562290938193</v>
+        <v>24.75376262640231</v>
       </c>
     </row>
     <row r="362">
@@ -6079,13 +6121,13 @@
         <v>43.26172344689378</v>
       </c>
       <c r="B362" t="n">
-        <v>99.55940522918364</v>
+        <v>50.10785876684349</v>
       </c>
       <c r="C362" t="n">
-        <v>0.007512773368546324</v>
+        <v>0.001314463505181409</v>
       </c>
       <c r="D362" t="n">
-        <v>9.895940522918362</v>
+        <v>24.75392938342175</v>
       </c>
     </row>
     <row r="363">
@@ -6093,13 +6135,13 @@
         <v>43.38189490091293</v>
       </c>
       <c r="B363" t="n">
-        <v>99.56298774965208</v>
+        <v>50.10817431947291</v>
       </c>
       <c r="C363" t="n">
-        <v>0.007118444417687917</v>
+        <v>0.00124499758676162</v>
       </c>
       <c r="D363" t="n">
-        <v>9.896298774965205</v>
+        <v>24.75408715973645</v>
       </c>
     </row>
     <row r="364">
@@ -6107,13 +6149,13 @@
         <v>43.50206635493208</v>
       </c>
       <c r="B364" t="n">
-        <v>99.56638338229382</v>
+        <v>50.10847304993334</v>
       </c>
       <c r="C364" t="n">
-        <v>0.006744686258057801</v>
+        <v>0.001179234909290263</v>
       </c>
       <c r="D364" t="n">
-        <v>9.89663833822938</v>
+        <v>24.75423652496667</v>
       </c>
     </row>
     <row r="365">
@@ -6121,13 +6163,13 @@
         <v>43.62223780895123</v>
       </c>
       <c r="B365" t="n">
-        <v>99.56960473331297</v>
+        <v>50.10875607237121</v>
       </c>
       <c r="C365" t="n">
-        <v>0.006390111321524106</v>
+        <v>0.001116930203998073</v>
       </c>
       <c r="D365" t="n">
-        <v>9.896960473331294</v>
+        <v>24.7543780361856</v>
       </c>
     </row>
     <row r="366">
@@ -6135,13 +6177,13 @@
         <v>43.74240926297038</v>
       </c>
       <c r="B366" t="n">
-        <v>99.57266410361113</v>
+        <v>50.10902447583891</v>
       </c>
       <c r="C366" t="n">
-        <v>0.006053365644677292</v>
+        <v>0.001057843726330207</v>
       </c>
       <c r="D366" t="n">
-        <v>9.897266410361111</v>
+        <v>24.75451223791945</v>
       </c>
     </row>
     <row r="367">
@@ -6149,13 +6191,13 @@
         <v>43.86258071698953</v>
       </c>
       <c r="B367" t="n">
-        <v>99.57557086363936</v>
+        <v>50.1092793242948</v>
       </c>
       <c r="C367" t="n">
-        <v>0.005733417819557519</v>
+        <v>0.001001741255946245</v>
       </c>
       <c r="D367" t="n">
-        <v>9.897557086363932</v>
+        <v>24.7546396621474</v>
       </c>
     </row>
     <row r="368">
@@ -6163,13 +6205,13 @@
         <v>43.98275217100868</v>
       </c>
       <c r="B368" t="n">
-        <v>99.57832811572042</v>
+        <v>50.10952147219918</v>
       </c>
       <c r="C368" t="n">
-        <v>0.005429926372695664</v>
+        <v>0.0009484346915177628</v>
       </c>
       <c r="D368" t="n">
-        <v>9.897832811572039</v>
+        <v>24.75476073609959</v>
       </c>
     </row>
     <row r="369">
@@ -6177,13 +6219,13 @@
         <v>44.10292362502783</v>
       </c>
       <c r="B369" t="n">
-        <v>99.58094206588905</v>
+        <v>50.109751158021</v>
       </c>
       <c r="C369" t="n">
-        <v>0.005142208204252327</v>
+        <v>0.0008978715363623383</v>
       </c>
       <c r="D369" t="n">
-        <v>9.898094206588901</v>
+        <v>24.7548755790105</v>
       </c>
     </row>
     <row r="370">
@@ -6191,13 +6233,13 @@
         <v>44.22309507904698</v>
       </c>
       <c r="B370" t="n">
-        <v>99.58341898312715</v>
+        <v>50.10996887177328</v>
       </c>
       <c r="C370" t="n">
-        <v>0.004869573285771818</v>
+        <v>0.0008499439187625905</v>
       </c>
       <c r="D370" t="n">
-        <v>9.898341898312713</v>
+        <v>24.75498443588664</v>
       </c>
     </row>
     <row r="371">
@@ -6205,13 +6247,13 @@
         <v>44.34326653306613</v>
       </c>
       <c r="B371" t="n">
-        <v>99.5857650217512</v>
+        <v>50.11017512388541</v>
       </c>
       <c r="C371" t="n">
-        <v>0.004611344210057293</v>
+        <v>0.0008045394725325237</v>
       </c>
       <c r="D371" t="n">
-        <v>9.898576502175118</v>
+        <v>24.75508756194271</v>
       </c>
     </row>
     <row r="372">
@@ -6219,13 +6261,13 @@
         <v>44.46343798708528</v>
       </c>
       <c r="B372" t="n">
-        <v>99.58798622141215</v>
+        <v>50.11037041701842</v>
       </c>
       <c r="C372" t="n">
-        <v>0.004366856191170688</v>
+        <v>0.000761547541615156</v>
       </c>
       <c r="D372" t="n">
-        <v>9.898798622141213</v>
+        <v>24.75518520850921</v>
       </c>
     </row>
     <row r="373">
@@ -6233,13 +6275,13 @@
         <v>44.58360944110443</v>
       </c>
       <c r="B373" t="n">
-        <v>99.59008850709549</v>
+        <v>50.11055524606495</v>
       </c>
       <c r="C373" t="n">
-        <v>0.004135457064432739</v>
+        <v>0.000720859180082523</v>
       </c>
       <c r="D373" t="n">
-        <v>9.899008850709546</v>
+        <v>24.75527762303247</v>
       </c>
     </row>
     <row r="374">
@@ -6247,13 +6289,13 @@
         <v>44.70378089512358</v>
       </c>
       <c r="B374" t="n">
-        <v>99.59207768912124</v>
+        <v>50.11073009814935</v>
       </c>
       <c r="C374" t="n">
-        <v>0.003916507286422975</v>
+        <v>0.0006823671521356774</v>
       </c>
       <c r="D374" t="n">
-        <v>9.89920776891212</v>
+        <v>24.75536504907467</v>
       </c>
     </row>
     <row r="375">
@@ -6261,13 +6303,13 @@
         <v>44.82395234914273</v>
       </c>
       <c r="B375" t="n">
-        <v>99.59395946314392</v>
+        <v>50.11089545262757</v>
       </c>
       <c r="C375" t="n">
-        <v>0.003709379934979724</v>
+        <v>0.0006459659321046891</v>
       </c>
       <c r="D375" t="n">
-        <v>9.899395946314389</v>
+        <v>24.75544772631379</v>
       </c>
     </row>
     <row r="376">
@@ -6275,13 +6317,13 @@
         <v>44.94412380316188</v>
       </c>
       <c r="B376" t="n">
-        <v>99.5957394101526</v>
+        <v>50.11105178108724</v>
       </c>
       <c r="C376" t="n">
-        <v>0.003513460709200113</v>
+        <v>0.0006115517044486447</v>
       </c>
       <c r="D376" t="n">
-        <v>9.899573941015257</v>
+        <v>24.75552589054362</v>
       </c>
     </row>
     <row r="377">
@@ -6289,13 +6331,13 @@
         <v>45.06429525718102</v>
       </c>
       <c r="B377" t="n">
-        <v>99.59742299647085</v>
+        <v>50.11119954734762</v>
       </c>
       <c r="C377" t="n">
-        <v>0.003328147929440073</v>
+        <v>0.0005790223637556506</v>
       </c>
       <c r="D377" t="n">
-        <v>9.899742299647082</v>
+        <v>24.75559977367381</v>
       </c>
     </row>
     <row r="378">
@@ -6303,13 +6345,13 @@
         <v>45.18446671120017</v>
       </c>
       <c r="B378" t="n">
-        <v>99.59901557375676</v>
+        <v>50.11133920745963</v>
       </c>
       <c r="C378" t="n">
-        <v>0.003152852537314301</v>
+        <v>0.0005482775147428243</v>
       </c>
       <c r="D378" t="n">
-        <v>9.899901557375673</v>
+        <v>24.75566960372981</v>
       </c>
     </row>
     <row r="379">
@@ -6317,13 +6359,13 @@
         <v>45.30463816521932</v>
       </c>
       <c r="B379" t="n">
-        <v>99.60052237900294</v>
+        <v>50.11147120970582</v>
       </c>
       <c r="C379" t="n">
-        <v>0.002986998095696327</v>
+        <v>0.0005192184722563062</v>
       </c>
       <c r="D379" t="n">
-        <v>9.900052237900292</v>
+        <v>24.75573560485291</v>
       </c>
     </row>
     <row r="380">
@@ -6331,13 +6373,13 @@
         <v>45.42480961923847</v>
       </c>
       <c r="B380" t="n">
-        <v>99.60194853453655</v>
+        <v>50.1115959946004</v>
       </c>
       <c r="C380" t="n">
-        <v>0.002830020788718462</v>
+        <v>0.0004917482612712522</v>
       </c>
       <c r="D380" t="n">
-        <v>9.900194853453652</v>
+        <v>24.7557979973002</v>
       </c>
     </row>
     <row r="381">
@@ -6345,13 +6387,13 @@
         <v>45.54498107325762</v>
       </c>
       <c r="B381" t="n">
-        <v>99.60329904801924</v>
+        <v>50.11171399488923</v>
       </c>
       <c r="C381" t="n">
-        <v>0.002681369421771819</v>
+        <v>0.0004657716168918351</v>
       </c>
       <c r="D381" t="n">
-        <v>9.900329904801922</v>
+        <v>24.75585699744461</v>
       </c>
     </row>
     <row r="382">
@@ -6359,13 +6401,13 @@
         <v>45.66515252727677</v>
       </c>
       <c r="B382" t="n">
-        <v>99.60457881244719</v>
+        <v>50.11182563554981</v>
       </c>
       <c r="C382" t="n">
-        <v>0.002540505421506304</v>
+        <v>0.0004411949843512451</v>
       </c>
       <c r="D382" t="n">
-        <v>9.900457881244716</v>
+        <v>24.75591281777491</v>
       </c>
     </row>
     <row r="383">
@@ -6373,13 +6415,13 @@
         <v>45.78532398129592</v>
       </c>
       <c r="B383" t="n">
-        <v>99.60579260615108</v>
+        <v>50.1119313337913</v>
       </c>
       <c r="C383" t="n">
-        <v>0.002406902835830622</v>
+        <v>0.0004179265190116893</v>
       </c>
       <c r="D383" t="n">
-        <v>9.900579260615107</v>
+        <v>24.75596566689565</v>
       </c>
     </row>
     <row r="384">
@@ -6387,13 +6429,13 @@
         <v>45.90549543531507</v>
       </c>
       <c r="B384" t="n">
-        <v>99.60694509279618</v>
+        <v>50.1120314990545</v>
       </c>
       <c r="C384" t="n">
-        <v>0.002280048333912276</v>
+        <v>0.0003958760863643921</v>
       </c>
       <c r="D384" t="n">
-        <v>9.900694509279615</v>
+        <v>24.75601574952725</v>
       </c>
     </row>
     <row r="385">
@@ -6401,13 +6443,13 @@
         <v>46.02566688933422</v>
       </c>
       <c r="B385" t="n">
-        <v>99.60804029871551</v>
+        <v>50.11212653301185</v>
       </c>
       <c r="C385" t="n">
-        <v>0.002159498736234634</v>
+        <v>0.0003749552620295964</v>
       </c>
       <c r="D385" t="n">
-        <v>9.900804029871548</v>
+        <v>24.75606326650592</v>
       </c>
     </row>
     <row r="386">
@@ -6415,13 +6457,13 @@
         <v>46.14583834335337</v>
       </c>
       <c r="B386" t="n">
-        <v>99.60907945987844</v>
+        <v>50.11221682956745</v>
       </c>
       <c r="C386" t="n">
-        <v>0.002045117999331024</v>
+        <v>0.0003550773317565587</v>
       </c>
       <c r="D386" t="n">
-        <v>9.900907945987841</v>
+        <v>24.75610841478372</v>
       </c>
     </row>
     <row r="387">
@@ -6429,13 +6471,13 @@
         <v>46.26600979737252</v>
       </c>
       <c r="B387" t="n">
-        <v>99.61006471193298</v>
+        <v>50.11230264475224</v>
       </c>
       <c r="C387" t="n">
-        <v>0.001936671051875547</v>
+        <v>0.0003361859327630775</v>
       </c>
       <c r="D387" t="n">
-        <v>9.901006471193295</v>
+        <v>24.75615132237612</v>
       </c>
     </row>
     <row r="388">
@@ -6443,13 +6485,13 @@
         <v>46.38618125139167</v>
       </c>
       <c r="B388" t="n">
-        <v>99.61099838041952</v>
+        <v>50.11238393317829</v>
       </c>
       <c r="C388" t="n">
-        <v>0.00183390192103855</v>
+        <v>0.0003182910567712155</v>
       </c>
       <c r="D388" t="n">
-        <v>9.901099838041949</v>
+        <v>24.75619196658915</v>
       </c>
     </row>
     <row r="389">
@@ -6457,13 +6499,13 @@
         <v>46.50635270541082</v>
       </c>
       <c r="B389" t="n">
-        <v>99.61188275086586</v>
+        <v>50.11246088666507</v>
       </c>
       <c r="C389" t="n">
-        <v>0.001736559038186613</v>
+        <v>0.0003013504765442527</v>
       </c>
       <c r="D389" t="n">
-        <v>9.901188275086582</v>
+        <v>24.75623044333253</v>
       </c>
     </row>
     <row r="390">
@@ -6471,13 +6513,13 @@
         <v>46.62652415942997</v>
       </c>
       <c r="B390" t="n">
-        <v>99.6127200687872</v>
+        <v>50.11253370821962</v>
       </c>
       <c r="C390" t="n">
-        <v>0.001644395238882548</v>
+        <v>0.0002853195020070453</v>
       </c>
       <c r="D390" t="n">
-        <v>9.901272006878715</v>
+        <v>24.75626685410981</v>
       </c>
     </row>
     <row r="391">
@@ -6485,13 +6527,13 @@
         <v>46.74669561344912</v>
       </c>
       <c r="B391" t="n">
-        <v>99.61351253968616</v>
+        <v>50.11260259606225</v>
       </c>
       <c r="C391" t="n">
-        <v>0.001557167762885403</v>
+        <v>0.0002701544968367503</v>
       </c>
       <c r="D391" t="n">
-        <v>9.901351253968611</v>
+        <v>24.75630129803112</v>
       </c>
     </row>
     <row r="392">
@@ -6499,13 +6541,13 @@
         <v>46.86686706746826</v>
       </c>
       <c r="B392" t="n">
-        <v>99.61426232905274</v>
+        <v>50.11266774362657</v>
       </c>
       <c r="C392" t="n">
-        <v>0.001474638254150462</v>
+        <v>0.0002558128784628263</v>
       </c>
       <c r="D392" t="n">
-        <v>9.901426232905271</v>
+        <v>24.75633387181328</v>
       </c>
     </row>
     <row r="393">
@@ -6513,13 +6555,13 @@
         <v>46.98703852148741</v>
       </c>
       <c r="B393" t="n">
-        <v>99.6149715623644</v>
+        <v>50.11272933955943</v>
       </c>
       <c r="C393" t="n">
-        <v>0.001396572760829228</v>
+        <v>0.0002422531180670297</v>
       </c>
       <c r="D393" t="n">
-        <v>9.901497156236436</v>
+        <v>24.75636466977971</v>
       </c>
     </row>
     <row r="394">
@@ -6527,13 +6569,13 @@
         <v>47.10720997550656</v>
       </c>
       <c r="B394" t="n">
-        <v>99.61564232508597</v>
+        <v>50.11278756772097</v>
       </c>
       <c r="C394" t="n">
-        <v>0.001322741735269455</v>
+        <v>0.0002294347405834204</v>
       </c>
       <c r="D394" t="n">
-        <v>9.901564232508594</v>
+        <v>24.75639378386049</v>
       </c>
     </row>
     <row r="395">
@@ -6541,13 +6583,13 @@
         <v>47.22738142952571</v>
       </c>
       <c r="B395" t="n">
-        <v>99.61627666266972</v>
+        <v>50.11284260718462</v>
       </c>
       <c r="C395" t="n">
-        <v>0.001252920034015121</v>
+        <v>0.0002173183246983581</v>
       </c>
       <c r="D395" t="n">
-        <v>9.901627666266968</v>
+        <v>24.75642130359231</v>
       </c>
     </row>
     <row r="396">
@@ -6555,13 +6597,13 @@
         <v>47.34755288354486</v>
       </c>
       <c r="B396" t="n">
-        <v>99.61687658055527</v>
+        <v>50.11289463223706</v>
       </c>
       <c r="C396" t="n">
-        <v>0.001186886917806442</v>
+        <v>0.0002058655028505029</v>
       </c>
       <c r="D396" t="n">
-        <v>9.901687658055524</v>
+        <v>24.75644731611853</v>
       </c>
     </row>
     <row r="397">
@@ -6569,13 +6611,13 @@
         <v>47.46772433756401</v>
       </c>
       <c r="B397" t="n">
-        <v>99.61744404416972</v>
+        <v>50.11294381237825</v>
       </c>
       <c r="C397" t="n">
-        <v>0.001124426051579863</v>
+        <v>0.0001950389612308157</v>
       </c>
       <c r="D397" t="n">
-        <v>9.901744404416968</v>
+        <v>24.75647190618912</v>
       </c>
     </row>
     <row r="398">
@@ -6583,13 +6625,13 @@
         <v>47.58789579158316</v>
       </c>
       <c r="B398" t="n">
-        <v>99.61798097892752</v>
+        <v>50.11299031232142</v>
       </c>
       <c r="C398" t="n">
-        <v>0.001065325504468066</v>
+        <v>0.0001848024397825581</v>
       </c>
       <c r="D398" t="n">
-        <v>9.901798097892748</v>
+        <v>24.75649515616071</v>
       </c>
     </row>
     <row r="399">
@@ -6597,13 +6639,13 @@
         <v>47.70806724560232</v>
       </c>
       <c r="B399" t="n">
-        <v>99.61848927023057</v>
+        <v>50.1130342919931</v>
       </c>
       <c r="C399" t="n">
-        <v>0.001009377749799966</v>
+        <v>0.0001751207322012922</v>
       </c>
       <c r="D399" t="n">
-        <v>9.901848927023053</v>
+        <v>24.75651714599655</v>
       </c>
     </row>
     <row r="400">
@@ -6611,13 +6653,13 @@
         <v>47.82823869962146</v>
       </c>
       <c r="B400" t="n">
-        <v>99.61897076346816</v>
+        <v>50.11307590653305</v>
       </c>
       <c r="C400" t="n">
-        <v>0.0009563796651007122</v>
+        <v>0.0001659596859348815</v>
       </c>
       <c r="D400" t="n">
-        <v>9.901897076346811</v>
+        <v>24.75653795326652</v>
       </c>
     </row>
     <row r="401">
@@ -6625,13 +6667,13 @@
         <v>47.94841015364061</v>
       </c>
       <c r="B401" t="n">
-        <v>99.61942726401698</v>
+        <v>50.11311530629435</v>
       </c>
       <c r="C401" t="n">
-        <v>0.0009061325320916802</v>
+        <v>0.0001572862021834883</v>
       </c>
       <c r="D401" t="n">
-        <v>9.901942726401694</v>
+        <v>24.75655765314717</v>
       </c>
     </row>
     <row r="402">
@@ -6639,13 +6681,13 @@
         <v>48.06858160765976</v>
       </c>
       <c r="B402" t="n">
-        <v>99.61986053724115</v>
+        <v>50.11315263684332</v>
       </c>
       <c r="C402" t="n">
-        <v>0.0008584420366904869</v>
+        <v>0.0001490682358995774</v>
       </c>
       <c r="D402" t="n">
-        <v>9.901986053724112</v>
+        <v>24.75657631842166</v>
       </c>
     </row>
     <row r="403">
@@ -6653,13 +6695,13 @@
         <v>48.18875306167891</v>
       </c>
       <c r="B403" t="n">
-        <v>99.62027230288967</v>
+        <v>50.11318803895956</v>
       </c>
       <c r="C403" t="n">
-        <v>0.0008131188856823338</v>
+        <v>0.0001412747957879134</v>
       </c>
       <c r="D403" t="n">
-        <v>9.902027230288965</v>
+        <v>24.75659401947978</v>
       </c>
     </row>
     <row r="404">
@@ -6667,13 +6709,13 @@
         <v>48.30892451569806</v>
       </c>
       <c r="B404" t="n">
-        <v>99.62066298080494</v>
+        <v>50.11322164863598</v>
       </c>
       <c r="C404" t="n">
-        <v>0.00077011686690623</v>
+        <v>0.0001338759443055619</v>
       </c>
       <c r="D404" t="n">
-        <v>9.902066298080491</v>
+        <v>24.75661082431799</v>
       </c>
     </row>
     <row r="405">
@@ -6681,13 +6723,13 @@
         <v>48.42909596971721</v>
       </c>
       <c r="B405" t="n">
-        <v>99.62103293276581</v>
+        <v>50.11325359707871</v>
       </c>
       <c r="C405" t="n">
-        <v>0.0007293961592680977</v>
+        <v>0.000126842797661889</v>
       </c>
       <c r="D405" t="n">
-        <v>9.902103293276578</v>
+        <v>24.75662679853935</v>
       </c>
     </row>
     <row r="406">
@@ -6695,13 +6737,13 @@
         <v>48.54926742373636</v>
       </c>
       <c r="B406" t="n">
-        <v>99.62138329295462</v>
+        <v>50.11328401070719</v>
       </c>
       <c r="C406" t="n">
-        <v>0.0006908319230295481</v>
+        <v>0.0001201475258185612</v>
       </c>
       <c r="D406" t="n">
-        <v>9.902138329295459</v>
+        <v>24.75664200535359</v>
       </c>
     </row>
     <row r="407">
@@ -6709,13 +6751,13 @@
         <v>48.66943887775551</v>
       </c>
       <c r="B407" t="n">
-        <v>99.6217151413251</v>
+        <v>50.11331307810186</v>
       </c>
       <c r="C407" t="n">
-        <v>0.0006543052874025393</v>
+        <v>0.0001137486145804523</v>
       </c>
       <c r="D407" t="n">
-        <v>9.902171514132508</v>
+        <v>24.75665653905093</v>
       </c>
     </row>
     <row r="408">
@@ -6723,13 +6765,13 @@
         <v>48.78961033177465</v>
       </c>
       <c r="B408" t="n">
-        <v>99.62202950360248</v>
+        <v>50.11334173820786</v>
       </c>
       <c r="C408" t="n">
-        <v>0.0006197033505493782</v>
+        <v>0.0001074393640787877</v>
       </c>
       <c r="D408" t="n">
-        <v>9.902202950360245</v>
+        <v>24.75667086910393</v>
       </c>
     </row>
     <row r="409">
@@ -6737,13 +6779,13 @@
         <v>48.9097817857938</v>
       </c>
       <c r="B409" t="n">
-        <v>99.62232735128337</v>
+        <v>50.11336994508235</v>
       </c>
       <c r="C409" t="n">
-        <v>0.0005869191795827128</v>
+        <v>0.0001012298881959127</v>
       </c>
       <c r="D409" t="n">
-        <v>9.902232735128337</v>
+        <v>24.75668497254117</v>
       </c>
     </row>
     <row r="410">
@@ -6751,13 +6793,13 @@
         <v>49.02995323981295</v>
       </c>
       <c r="B410" t="n">
-        <v>99.62260960163594</v>
+        <v>50.11339733037024</v>
       </c>
       <c r="C410" t="n">
-        <v>0.0005558518105655442</v>
+        <v>9.520127681024634e-05</v>
       </c>
       <c r="D410" t="n">
-        <v>9.902260960163591</v>
+        <v>24.75669866518512</v>
       </c>
     </row>
     <row r="411">
@@ -6765,13 +6807,13 @@
         <v>49.1501246938321</v>
       </c>
       <c r="B411" t="n">
-        <v>99.62287711769972</v>
+        <v>50.11342357204534</v>
       </c>
       <c r="C411" t="n">
-        <v>0.0005264062485112184</v>
+        <v>8.942442093349484e-05</v>
       </c>
       <c r="D411" t="n">
-        <v>9.902287711769969</v>
+        <v>24.75671178602267</v>
       </c>
     </row>
     <row r="412">
@@ -6779,13 +6821,13 @@
         <v>49.27029614785125</v>
       </c>
       <c r="B412" t="n">
-        <v>99.6231307082857</v>
+        <v>50.11344839441036</v>
       </c>
       <c r="C412" t="n">
-        <v>0.0004984934673834282</v>
+        <v>8.396001271065259e-05</v>
       </c>
       <c r="D412" t="n">
-        <v>9.902313070828567</v>
+        <v>24.75672419720518</v>
       </c>
     </row>
     <row r="413">
@@ -6793,13 +6835,13 @@
         <v>49.39046760187041</v>
       </c>
       <c r="B413" t="n">
-        <v>99.62337112797637</v>
+        <v>50.11347156809688</v>
       </c>
       <c r="C413" t="n">
-        <v>0.0004720304100962135</v>
+        <v>7.885854542000186e-05</v>
       </c>
       <c r="D413" t="n">
-        <v>9.902337112797635</v>
+        <v>24.75673578404844</v>
       </c>
     </row>
     <row r="414">
@@ -6807,13 +6849,13 @@
         <v>49.51063905588956</v>
       </c>
       <c r="B414" t="n">
-        <v>99.62359907712565</v>
+        <v>50.1134929100654</v>
       </c>
       <c r="C414" t="n">
-        <v>0.0004469399885139613</v>
+        <v>7.416031347311295e-05</v>
       </c>
       <c r="D414" t="n">
-        <v>9.902359907712562</v>
+        <v>24.7567464550327</v>
       </c>
     </row>
     <row r="415">
@@ -6821,13 +6863,13 @@
         <v>49.63081050990871</v>
       </c>
       <c r="B415" t="n">
-        <v>99.62381520185887</v>
+        <v>50.11351228360531</v>
       </c>
       <c r="C415" t="n">
-        <v>0.0004231510834514052</v>
+        <v>6.989541241484408e-05</v>
       </c>
       <c r="D415" t="n">
-        <v>9.902381520185886</v>
+        <v>24.75675614180265</v>
       </c>
     </row>
     <row r="416">
@@ -6835,13 +6877,13 @@
         <v>49.75098196392785</v>
       </c>
       <c r="B416" t="n">
-        <v>99.62402009407288</v>
+        <v>50.11352959833489</v>
       </c>
       <c r="C416" t="n">
-        <v>0.0004005985446736273</v>
+        <v>6.608373892334167e-05</v>
       </c>
       <c r="D416" t="n">
-        <v>9.902402009407286</v>
+        <v>24.75676479916745</v>
       </c>
     </row>
     <row r="417">
@@ -6849,13 +6891,13 @@
         <v>49.871153417947</v>
       </c>
       <c r="B417" t="n">
-        <v>99.62421429143592</v>
+        <v>50.11354481020133</v>
       </c>
       <c r="C417" t="n">
-        <v>0.0003792231908960528</v>
+        <v>6.273499081003948e-05</v>
       </c>
       <c r="D417" t="n">
-        <v>9.902421429143589</v>
+        <v>24.75677240510066</v>
       </c>
     </row>
     <row r="418">
@@ -6863,13 +6905,13 @@
         <v>49.99132487196615</v>
       </c>
       <c r="B418" t="n">
-        <v>99.62439827738771</v>
+        <v>50.11355792148067</v>
       </c>
       <c r="C418" t="n">
-        <v>0.0003589718097844578</v>
+        <v>5.984866701965987e-05</v>
       </c>
       <c r="D418" t="n">
-        <v>9.902439827738769</v>
+        <v>24.75677896074033</v>
       </c>
     </row>
     <row r="419">
@@ -6877,13 +6919,13 @@
         <v>50.1114963259853</v>
       </c>
       <c r="B419" t="n">
-        <v>99.62457248113945</v>
+        <v>50.1135689807779</v>
       </c>
       <c r="C419" t="n">
-        <v>0.0003397971579549639</v>
+        <v>5.741406763021298e-05</v>
       </c>
       <c r="D419" t="n">
-        <v>9.902457248113942</v>
+        <v>24.75678449038895</v>
       </c>
     </row>
     <row r="420">
@@ -6891,13 +6933,13 @@
         <v>50.23166778000445</v>
       </c>
       <c r="B420" t="n">
-        <v>99.62473727767372</v>
+        <v>50.11357808302687</v>
       </c>
       <c r="C420" t="n">
-        <v>0.0003216579609740398</v>
+        <v>5.541029385299686e-05</v>
       </c>
       <c r="D420" t="n">
-        <v>9.90247372776737</v>
+        <v>24.75678904151343</v>
       </c>
     </row>
     <row r="421">
@@ -6905,13 +6947,13 @@
         <v>50.3518392340236</v>
       </c>
       <c r="B421" t="n">
-        <v>99.62489298774462</v>
+        <v>50.11358536949032</v>
       </c>
       <c r="C421" t="n">
-        <v>0.0003045189133585009</v>
+        <v>5.380624803259763e-05</v>
       </c>
       <c r="D421" t="n">
-        <v>9.902489298774459</v>
+        <v>24.75679268474516</v>
       </c>
     </row>
     <row r="422">
@@ -6919,13 +6961,13 @@
         <v>50.47201068804275</v>
       </c>
       <c r="B422" t="n">
-        <v>99.62503987787764</v>
+        <v>50.11359102775993</v>
       </c>
       <c r="C422" t="n">
-        <v>0.0002883506785755101</v>
+        <v>5.256063364688924e-05</v>
       </c>
       <c r="D422" t="n">
-        <v>9.902503987787762</v>
+        <v>24.75679551387996</v>
       </c>
     </row>
     <row r="423">
@@ -6933,13 +6975,13 @@
         <v>50.5921821420619</v>
       </c>
       <c r="B423" t="n">
-        <v>99.62518007607399</v>
+        <v>50.11359529175622</v>
       </c>
       <c r="C423" t="n">
-        <v>0.0002729190269876322</v>
+        <v>5.162195530703375e-05</v>
       </c>
       <c r="D423" t="n">
-        <v>9.902518007607396</v>
+        <v>24.75679764587811</v>
       </c>
     </row>
     <row r="424">
@@ -6947,13 +6989,13 @@
         <v>50.71235359608104</v>
       </c>
       <c r="B424" t="n">
-        <v>99.62531691222989</v>
+        <v>50.11359844172863</v>
       </c>
       <c r="C424" t="n">
-        <v>0.0002578574360560895</v>
+        <v>5.092851875748112e-05</v>
       </c>
       <c r="D424" t="n">
-        <v>9.902531691222988</v>
+        <v>24.75679922086431</v>
       </c>
     </row>
     <row r="425">
@@ -6961,13 +7003,13 @@
         <v>50.83252505010019</v>
       </c>
       <c r="B425" t="n">
-        <v>99.62544925775504</v>
+        <v>50.1136008042555</v>
       </c>
       <c r="C425" t="n">
-        <v>0.000243290130010367</v>
+        <v>5.040843087596922e-05</v>
       </c>
       <c r="D425" t="n">
-        <v>9.902544925775501</v>
+        <v>24.75680040212775</v>
       </c>
     </row>
     <row r="426">
@@ -6975,13 +7017,13 @@
         <v>50.95269650411934</v>
       </c>
       <c r="B426" t="n">
-        <v>99.62557601802853</v>
+        <v>50.11360275224404</v>
       </c>
       <c r="C426" t="n">
-        <v>0.0002293375940515474</v>
+        <v>4.9979599673524e-05</v>
       </c>
       <c r="D426" t="n">
-        <v>9.902557601802851</v>
+        <v>24.75680137612202</v>
       </c>
     </row>
     <row r="427">
@@ -6989,13 +7031,13 @@
         <v>51.0728679581385</v>
       </c>
       <c r="B427" t="n">
-        <v>99.6256962671156</v>
+        <v>50.11360470493039</v>
       </c>
       <c r="C427" t="n">
-        <v>0.0002161017460606086</v>
+        <v>4.954973429445935e-05</v>
       </c>
       <c r="D427" t="n">
-        <v>9.902569626711557</v>
+        <v>24.75680235246519</v>
       </c>
     </row>
     <row r="428">
@@ -7003,13 +7045,13 @@
         <v>51.19303941215765</v>
       </c>
       <c r="B428" t="n">
-        <v>99.62580924776752</v>
+        <v>50.11360712787956</v>
       </c>
       <c r="C428" t="n">
-        <v>0.0002036659365984241</v>
+        <v>4.901634501637705e-05</v>
       </c>
       <c r="D428" t="n">
-        <v>9.90258092477675</v>
+        <v>24.75680356393978</v>
       </c>
     </row>
     <row r="429">
@@ -7017,13 +7059,13 @@
         <v>51.3132108661768</v>
       </c>
       <c r="B429" t="n">
-        <v>99.62591437142166</v>
+        <v>50.11361053298545</v>
       </c>
       <c r="C429" t="n">
-        <v>0.0001920949489057635</v>
+        <v>4.826674325016701e-05</v>
       </c>
       <c r="D429" t="n">
-        <v>9.902591437142163</v>
+        <v>24.75680526649273</v>
       </c>
     </row>
     <row r="430">
@@ -7031,13 +7073,13 @@
         <v>51.43338232019595</v>
       </c>
       <c r="B430" t="n">
-        <v>99.62601121820147</v>
+        <v>50.11361547847088</v>
       </c>
       <c r="C430" t="n">
-        <v>0.0001814349989032925</v>
+        <v>4.717804154000692e-05</v>
       </c>
       <c r="D430" t="n">
-        <v>9.902601121820146</v>
+        <v>24.75680773923544</v>
       </c>
     </row>
     <row r="431">
@@ -7045,13 +7087,13 @@
         <v>51.5535537742151</v>
       </c>
       <c r="B431" t="n">
-        <v>99.62609953691647</v>
+        <v>50.11362256888754</v>
       </c>
       <c r="C431" t="n">
-        <v>0.0001717137351915725</v>
+        <v>4.561715356336255e-05</v>
       </c>
       <c r="D431" t="n">
-        <v>9.902609953691645</v>
+        <v>24.75681128444377</v>
       </c>
     </row>
     <row r="432">
@@ -7059,13 +7101,13 @@
         <v>51.67372522823424</v>
       </c>
       <c r="B432" t="n">
-        <v>99.62617924506226</v>
+        <v>50.11363240011249</v>
       </c>
       <c r="C432" t="n">
-        <v>0.0001629402390510614</v>
+        <v>4.34529026376596e-05</v>
       </c>
       <c r="D432" t="n">
-        <v>9.902617924506224</v>
+        <v>24.75681620005625</v>
       </c>
     </row>
     <row r="433">
@@ -7073,13 +7115,13 @@
         <v>51.79389668225339</v>
       </c>
       <c r="B433" t="n">
-        <v>99.62625042882051</v>
+        <v>50.11364324512224</v>
       </c>
       <c r="C433" t="n">
-        <v>0.0001551050244421117</v>
+        <v>4.106547660403736e-05</v>
       </c>
       <c r="D433" t="n">
-        <v>9.902625042882049</v>
+        <v>24.75682162256112</v>
       </c>
     </row>
     <row r="434">
@@ -7087,13 +7129,13 @@
         <v>51.91406813627254</v>
       </c>
       <c r="B434" t="n">
-        <v>99.626313343059</v>
+        <v>50.11365389878175</v>
       </c>
       <c r="C434" t="n">
-        <v>0.0001481800380049731</v>
+        <v>3.872017451005389e-05</v>
       </c>
       <c r="D434" t="n">
-        <v>9.902631334305898</v>
+        <v>24.75682694939087</v>
       </c>
     </row>
     <row r="435">
@@ -7101,13 +7143,13 @@
         <v>52.03423959029169</v>
       </c>
       <c r="B435" t="n">
-        <v>99.62636841133154</v>
+        <v>50.11366423205242</v>
       </c>
       <c r="C435" t="n">
-        <v>0.000142118659059791</v>
+        <v>3.644540298063043e-05</v>
       </c>
       <c r="D435" t="n">
-        <v>9.902636841133152</v>
+        <v>24.75683211602621</v>
       </c>
     </row>
     <row r="436">
@@ -7115,13 +7157,13 @@
         <v>52.15441104431084</v>
       </c>
       <c r="B436" t="n">
-        <v>99.62641622587806</v>
+        <v>50.11367413237955</v>
       </c>
       <c r="C436" t="n">
-        <v>0.0001368556996066066</v>
+        <v>3.426593986531382e-05</v>
       </c>
       <c r="D436" t="n">
-        <v>9.902641622587804</v>
+        <v>24.75683706618977</v>
       </c>
     </row>
     <row r="437">
@@ -7129,13 +7171,13 @@
         <v>52.27458249832999</v>
       </c>
       <c r="B437" t="n">
-        <v>99.62645754762455</v>
+        <v>50.11368350369235</v>
       </c>
       <c r="C437" t="n">
-        <v>0.0001323074043253571</v>
+        <v>3.220293423827647e-05</v>
       </c>
       <c r="D437" t="n">
-        <v>9.902645754762453</v>
+        <v>24.75684175184617</v>
       </c>
     </row>
     <row r="438">
@@ -7143,13 +7185,13 @@
         <v>52.39475395234914</v>
       </c>
       <c r="B438" t="n">
-        <v>99.62649330618309</v>
+        <v>50.11369226640392</v>
       </c>
       <c r="C438" t="n">
-        <v>0.0001283714505758756</v>
+        <v>3.027390639831635e-05</v>
       </c>
       <c r="D438" t="n">
-        <v>9.902649330618306</v>
+        <v>24.75684613320196</v>
       </c>
     </row>
     <row r="439">
@@ -7157,13 +7199,13 @@
         <v>52.51492540636829</v>
       </c>
       <c r="B439" t="n">
-        <v>99.62652459985181</v>
+        <v>50.11370035741128</v>
       </c>
       <c r="C439" t="n">
-        <v>0.0001249269483978912</v>
+        <v>2.849274786885702e-05</v>
       </c>
       <c r="D439" t="n">
-        <v>9.902652459985179</v>
+        <v>24.75685017870564</v>
       </c>
     </row>
     <row r="440">
@@ -7171,13 +7213,13 @@
         <v>52.63509686038743</v>
       </c>
       <c r="B440" t="n">
-        <v>99.62655269561495</v>
+        <v>50.11370773009536</v>
       </c>
       <c r="C440" t="n">
-        <v>0.000121834440511029</v>
+        <v>2.686972139794769e-05</v>
       </c>
       <c r="D440" t="n">
-        <v>9.902655269561492</v>
+        <v>24.75685386504768</v>
       </c>
     </row>
     <row r="441">
@@ -7185,13 +7227,13 @@
         <v>52.75526831440659</v>
       </c>
       <c r="B441" t="n">
-        <v>99.62657902914282</v>
+        <v>50.11371435432097</v>
       </c>
       <c r="C441" t="n">
-        <v>0.0001189359023148097</v>
+        <v>2.541146095826286e-05</v>
       </c>
       <c r="D441" t="n">
-        <v>9.90265790291428</v>
+        <v>24.75685717716048</v>
       </c>
     </row>
     <row r="442">
@@ -7199,13 +7241,13 @@
         <v>52.87543976842574</v>
       </c>
       <c r="B442" t="n">
-        <v>99.6266052047918</v>
+        <v>50.11372021643685</v>
       </c>
       <c r="C442" t="n">
-        <v>0.0001160547418886503</v>
+        <v>2.412097174710293e-05</v>
       </c>
       <c r="D442" t="n">
-        <v>9.902660520479177</v>
+        <v>24.75686010821843</v>
       </c>
     </row>
     <row r="443">
@@ -7213,13 +7255,13 @@
         <v>52.99561122244489</v>
       </c>
       <c r="B443" t="n">
-        <v>99.62663299560435</v>
+        <v>50.11372531927564</v>
       </c>
       <c r="C443" t="n">
-        <v>0.0001129957999918636</v>
+        <v>2.299763018639373e-05</v>
       </c>
       <c r="D443" t="n">
-        <v>9.902663299560432</v>
+        <v>24.75686265963782</v>
       </c>
     </row>
     <row r="444">
@@ -7227,13 +7269,13 @@
         <v>53.11578267646404</v>
       </c>
       <c r="B444" t="n">
-        <v>99.62666434330902</v>
+        <v>50.11372968215389</v>
       </c>
       <c r="C444" t="n">
-        <v>0.0001095453500636587</v>
+        <v>2.203718392268668e-05</v>
       </c>
       <c r="D444" t="n">
-        <v>9.9026664343309</v>
+        <v>24.75686484107694</v>
       </c>
     </row>
     <row r="445">
@@ -7241,13 +7283,13 @@
         <v>53.23595413048319</v>
       </c>
       <c r="B445" t="n">
-        <v>99.62670135832042</v>
+        <v>50.11373334087202</v>
       </c>
       <c r="C445" t="n">
-        <v>0.00010547109822314</v>
+        <v>2.123175182715879e-05</v>
       </c>
       <c r="D445" t="n">
-        <v>9.902670135832039</v>
+        <v>24.75686667043601</v>
       </c>
     </row>
     <row r="446">
@@ -7255,13 +7297,13 @@
         <v>53.35612558450234</v>
       </c>
       <c r="B446" t="n">
-        <v>99.62674631938653</v>
+        <v>50.11373634771441</v>
       </c>
       <c r="C446" t="n">
-        <v>0.0001005222220941836</v>
+        <v>2.056982399561263e-05</v>
       </c>
       <c r="D446" t="n">
-        <v>9.90267463193865</v>
+        <v>24.7568681738572</v>
       </c>
     </row>
     <row r="447">
@@ -7269,13 +7311,13 @@
         <v>53.47629703852149</v>
       </c>
       <c r="B447" t="n">
-        <v>99.62679514235988</v>
+        <v>50.1137387714493</v>
       </c>
       <c r="C447" t="n">
-        <v>9.514826483945617e-05</v>
+        <v>2.003626174847632e-05</v>
       </c>
       <c r="D447" t="n">
-        <v>9.902679514235986</v>
+        <v>24.75686938572465</v>
       </c>
     </row>
     <row r="448">
@@ -7283,13 +7325,13 @@
         <v>53.59646849254063</v>
       </c>
       <c r="B448" t="n">
-        <v>99.62684215768394</v>
+        <v>50.11374069732885</v>
       </c>
       <c r="C448" t="n">
-        <v>8.997327600978754e-05</v>
+        <v>1.961229763080362e-05</v>
       </c>
       <c r="D448" t="n">
-        <v>9.902684215768391</v>
+        <v>24.75687034866442</v>
       </c>
     </row>
     <row r="449">
@@ -7297,13 +7339,13 @@
         <v>53.71663994655978</v>
       </c>
       <c r="B449" t="n">
-        <v>99.62688714759003</v>
+        <v>50.11374222708914</v>
       </c>
       <c r="C449" t="n">
-        <v>8.502122545702524e-05</v>
+        <v>1.927553541227377e-05</v>
       </c>
       <c r="D449" t="n">
-        <v>9.902688714759</v>
+        <v>24.75687111354457</v>
       </c>
     </row>
     <row r="450">
@@ -7311,13 +7353,13 @@
         <v>53.83681140057893</v>
       </c>
       <c r="B450" t="n">
-        <v>99.62692993209527</v>
+        <v>50.11374347895014</v>
       </c>
       <c r="C450" t="n">
-        <v>8.031192394265254e-05</v>
+        <v>1.899995008719167e-05</v>
       </c>
       <c r="D450" t="n">
-        <v>9.902692993209524</v>
+        <v>24.75687173947507</v>
       </c>
     </row>
     <row r="451">
@@ -7325,13 +7367,13 @@
         <v>53.95698285459808</v>
       </c>
       <c r="B451" t="n">
-        <v>99.62697036900258</v>
+        <v>50.11374458761572</v>
       </c>
       <c r="C451" t="n">
-        <v>7.586102313778724e-05</v>
+        <v>1.875588787448774e-05</v>
       </c>
       <c r="D451" t="n">
-        <v>9.902697036900255</v>
+        <v>24.75687229380786</v>
       </c>
     </row>
     <row r="452">
@@ -7339,13 +7381,13 @@
         <v>54.07715430861723</v>
       </c>
       <c r="B452" t="n">
-        <v>99.62700835390064</v>
+        <v>50.11374570427368</v>
       </c>
       <c r="C452" t="n">
-        <v>7.168001562318199e-05</v>
+        <v>1.851006621771802e-05</v>
       </c>
       <c r="D452" t="n">
-        <v>9.902700835390061</v>
+        <v>24.75687285213684</v>
       </c>
     </row>
     <row r="453">
@@ -7353,13 +7395,13 @@
         <v>54.19732576263638</v>
       </c>
       <c r="B453" t="n">
-        <v>99.62704382016391</v>
+        <v>50.11374699659568</v>
       </c>
       <c r="C453" t="n">
-        <v>6.777623488922426e-05</v>
+        <v>1.822557378506406e-05</v>
       </c>
       <c r="D453" t="n">
-        <v>9.902704382016388</v>
+        <v>24.75687349829784</v>
       </c>
     </row>
     <row r="454">
@@ -7367,13 +7409,13 @@
         <v>54.31749721665553</v>
       </c>
       <c r="B454" t="n">
-        <v>99.62707673895261</v>
+        <v>50.11374864873734</v>
       </c>
       <c r="C454" t="n">
-        <v>6.415285533593636e-05</v>
+        <v>1.786187046933305e-05</v>
       </c>
       <c r="D454" t="n">
-        <v>9.902707673895259</v>
+        <v>24.75687432436867</v>
       </c>
     </row>
     <row r="455">
@@ -7381,13 +7423,13 @@
         <v>54.43766867067468</v>
       </c>
       <c r="B455" t="n">
-        <v>99.62710711921278</v>
+        <v>50.11375086133815</v>
       </c>
       <c r="C455" t="n">
-        <v>6.080889227297563e-05</v>
+        <v>1.737478738795776e-05</v>
       </c>
       <c r="D455" t="n">
-        <v>9.902710711921275</v>
+        <v>24.75687543066907</v>
       </c>
     </row>
     <row r="456">
@@ -7395,13 +7437,13 @@
         <v>54.55784012469383</v>
       </c>
       <c r="B456" t="n">
-        <v>99.6271350076762</v>
+        <v>50.1137538515215</v>
       </c>
       <c r="C456" t="n">
-        <v>5.773920191963365e-05</v>
+        <v>1.671652688299643e-05</v>
       </c>
       <c r="D456" t="n">
-        <v>9.902713500767618</v>
+        <v>24.75687692576075</v>
       </c>
     </row>
     <row r="457">
@@ -7409,13 +7451,13 @@
         <v>54.67801157871298</v>
       </c>
       <c r="B457" t="n">
-        <v>99.62716048886045</v>
+        <v>50.11375773494537</v>
       </c>
       <c r="C457" t="n">
-        <v>5.493448140483746e-05</v>
+        <v>1.586162795087046e-05</v>
       </c>
       <c r="D457" t="n">
-        <v>9.902716048886042</v>
+        <v>24.75687886747269</v>
       </c>
     </row>
     <row r="458">
@@ -7423,13 +7465,13 @@
         <v>54.79818303273213</v>
       </c>
       <c r="B458" t="n">
-        <v>99.62718368506889</v>
+        <v>50.11376180101168</v>
       </c>
       <c r="C458" t="n">
-        <v>5.238126876714872e-05</v>
+        <v>1.496652202024615e-05</v>
       </c>
       <c r="D458" t="n">
-        <v>9.902718368506886</v>
+        <v>24.75688090050584</v>
       </c>
     </row>
     <row r="459">
@@ -7437,13 +7479,13 @@
         <v>54.91835448675128</v>
       </c>
       <c r="B459" t="n">
-        <v>99.62720475639063</v>
+        <v>50.11376583983316</v>
       </c>
       <c r="C459" t="n">
-        <v>5.006194295476395e-05</v>
+        <v>1.407741377723276e-05</v>
       </c>
       <c r="D459" t="n">
-        <v>9.902720475639059</v>
+        <v>24.75688291991658</v>
       </c>
     </row>
     <row r="460">
@@ -7451,13 +7493,13 @@
         <v>55.03852594077043</v>
       </c>
       <c r="B460" t="n">
-        <v>99.62722390070059</v>
+        <v>50.11376979903318</v>
       </c>
       <c r="C460" t="n">
-        <v>4.795472382551442e-05</v>
+        <v>1.320583344592283e-05</v>
       </c>
       <c r="D460" t="n">
-        <v>9.902722390070055</v>
+        <v>24.75688489951659</v>
       </c>
     </row>
     <row r="461">
@@ -7465,13 +7507,13 @@
         <v>55.15869739478958</v>
       </c>
       <c r="B461" t="n">
-        <v>99.62724135365946</v>
+        <v>50.11377363159185</v>
       </c>
       <c r="C461" t="n">
-        <v>4.603367214686637e-05</v>
+        <v>1.236213200617164e-05</v>
       </c>
       <c r="D461" t="n">
-        <v>9.902724135365943</v>
+        <v>24.75688681579592</v>
       </c>
     </row>
     <row r="462">
@@ -7479,13 +7521,13 @@
         <v>55.27886884880873</v>
       </c>
       <c r="B462" t="n">
-        <v>99.62725738871369</v>
+        <v>50.11377729584607</v>
       </c>
       <c r="C462" t="n">
-        <v>4.426868959592079e-05</v>
+        <v>1.155548119359724e-05</v>
       </c>
       <c r="D462" t="n">
-        <v>9.902725738871366</v>
+        <v>24.75688864792303</v>
       </c>
     </row>
     <row r="463">
@@ -7493,13 +7535,13 @@
         <v>55.39904030282787</v>
       </c>
       <c r="B463" t="n">
-        <v>99.62727231709555</v>
+        <v>50.11378075548953</v>
       </c>
       <c r="C463" t="n">
-        <v>4.262551875941363e-05</v>
+        <v>1.079387349958044e-05</v>
       </c>
       <c r="D463" t="n">
-        <v>9.902727231709552</v>
+        <v>24.75689037774476</v>
       </c>
     </row>
     <row r="464">
@@ -7507,13 +7549,13 @@
         <v>55.51921175684702</v>
       </c>
       <c r="B464" t="n">
-        <v>99.62728648782304</v>
+        <v>50.11378397957269</v>
       </c>
       <c r="C464" t="n">
-        <v>4.106574313371534e-05</v>
+        <v>1.008412217126468e-05</v>
       </c>
       <c r="D464" t="n">
-        <v>9.902728648782302</v>
+        <v>24.75689198978635</v>
       </c>
     </row>
     <row r="465">
@@ -7521,13 +7563,13 @@
         <v>55.63938321086617</v>
       </c>
       <c r="B465" t="n">
-        <v>99.62730028769997</v>
+        <v>50.1137869425028</v>
       </c>
       <c r="C465" t="n">
-        <v>3.954678712483161e-05</v>
+        <v>9.431861211556286e-06</v>
       </c>
       <c r="D465" t="n">
-        <v>9.902730028769994</v>
+        <v>24.7568934712514</v>
       </c>
     </row>
     <row r="466">
@@ -7535,13 +7577,13 @@
         <v>55.75955466488532</v>
       </c>
       <c r="B466" t="n">
-        <v>99.62731414131592</v>
+        <v>50.11378962404387</v>
       </c>
       <c r="C466" t="n">
-        <v>3.802191604840276e-05</v>
+        <v>8.841545379124264e-06</v>
       </c>
       <c r="D466" t="n">
-        <v>9.902731414131591</v>
+        <v>24.75689481202193</v>
       </c>
     </row>
     <row r="467">
@@ -7549,13 +7591,13 @@
         <v>55.87972611890447</v>
       </c>
       <c r="B467" t="n">
-        <v>99.62732851104624</v>
+        <v>50.1137920093167</v>
       </c>
       <c r="C467" t="n">
-        <v>3.644023612970398e-05</v>
+        <v>8.316450188400393e-06</v>
       </c>
       <c r="D467" t="n">
-        <v>9.902732851104622</v>
+        <v>24.75689600465835</v>
       </c>
     </row>
     <row r="468">
@@ -7563,13 +7605,13 @@
         <v>55.99989757292362</v>
       </c>
       <c r="B468" t="n">
-        <v>99.62734389705209</v>
+        <v>50.11379408879888</v>
       </c>
       <c r="C468" t="n">
-        <v>3.474669450364532e-05</v>
+        <v>7.85867190957918e-06</v>
       </c>
       <c r="D468" t="n">
-        <v>9.902734389705206</v>
+        <v>24.75689704439944</v>
       </c>
     </row>
     <row r="469">
@@ -7577,13 +7619,13 @@
         <v>56.12006902694277</v>
       </c>
       <c r="B469" t="n">
-        <v>99.62736056247827</v>
+        <v>50.11379585832477</v>
       </c>
       <c r="C469" t="n">
-        <v>3.291232674951992e-05</v>
+        <v>7.469127568617895e-06</v>
       </c>
       <c r="D469" t="n">
-        <v>9.902736056247825</v>
+        <v>24.75689792916238</v>
       </c>
     </row>
     <row r="470">
@@ -7591,13 +7633,13 @@
         <v>56.24024048096192</v>
       </c>
       <c r="B470" t="n">
-        <v>99.62737749196721</v>
+        <v>50.11379731908551</v>
       </c>
       <c r="C470" t="n">
-        <v>3.104889354232606e-05</v>
+        <v>7.147554947236533e-06</v>
       </c>
       <c r="D470" t="n">
-        <v>9.902737749196717</v>
+        <v>24.75689865954275</v>
       </c>
     </row>
     <row r="471">
@@ -7605,13 +7647,13 @@
         <v>56.36041193498107</v>
       </c>
       <c r="B471" t="n">
-        <v>99.62739430550494</v>
+        <v>50.11379847762901</v>
       </c>
       <c r="C471" t="n">
-        <v>2.919822311259306e-05</v>
+        <v>6.892512582917874e-06</v>
       </c>
       <c r="D471" t="n">
-        <v>9.90273943055049</v>
+        <v>24.7568992388145</v>
       </c>
     </row>
     <row r="472">
@@ -7619,13 +7661,13 @@
         <v>56.48058338900022</v>
       </c>
       <c r="B472" t="n">
-        <v>99.62741077109531</v>
+        <v>50.11379934585999</v>
       </c>
       <c r="C472" t="n">
-        <v>2.738585133769908e-05</v>
+        <v>6.701379768907386e-06</v>
       </c>
       <c r="D472" t="n">
-        <v>9.902741077109528</v>
+        <v>24.75689967292999</v>
       </c>
     </row>
     <row r="473">
@@ -7633,13 +7675,13 @@
         <v>56.60075484301937</v>
       </c>
       <c r="B473" t="n">
-        <v>99.62742668122367</v>
+        <v>50.11379994103991</v>
       </c>
       <c r="C473" t="n">
-        <v>2.563461941198638e-05</v>
+        <v>6.570356554213329e-06</v>
       </c>
       <c r="D473" t="n">
-        <v>9.902742668122363</v>
+        <v>24.75689997051995</v>
       </c>
     </row>
     <row r="474">
@@ -7647,13 +7689,13 @@
         <v>56.72092629703852</v>
       </c>
       <c r="B474" t="n">
-        <v>99.62744185285678</v>
+        <v>50.11380028578704</v>
       </c>
       <c r="C474" t="n">
-        <v>2.396467384676078e-05</v>
+        <v>6.494463743606705e-06</v>
       </c>
       <c r="D474" t="n">
-        <v>9.902744185285675</v>
+        <v>24.75690014289352</v>
       </c>
     </row>
     <row r="475">
@@ -7661,13 +7703,13 @@
         <v>56.84109775105767</v>
       </c>
       <c r="B475" t="n">
-        <v>99.62745612744294</v>
+        <v>50.11380040807641</v>
       </c>
       <c r="C475" t="n">
-        <v>2.239346647029186e-05</v>
+        <v>6.46754289762125e-06</v>
       </c>
       <c r="D475" t="n">
-        <v>9.90274561274429</v>
+        <v>24.75690020403821</v>
       </c>
     </row>
     <row r="476">
@@ -7675,13 +7717,13 @@
         <v>56.96126920507682</v>
       </c>
       <c r="B476" t="n">
-        <v>99.62746937091192</v>
+        <v>50.11380034123985</v>
       </c>
       <c r="C476" t="n">
-        <v>2.093575442781294e-05</v>
+        <v>6.482256332553462e-06</v>
       </c>
       <c r="D476" t="n">
-        <v>9.902746937091189</v>
+        <v>24.75690017061993</v>
       </c>
     </row>
     <row r="477">
@@ -7689,13 +7731,13 @@
         <v>57.08144065909597</v>
       </c>
       <c r="B477" t="n">
-        <v>99.62748147367498</v>
+        <v>50.11380012396595</v>
       </c>
       <c r="C477" t="n">
-        <v>1.960360018152103e-05</v>
+        <v>6.530087120462569e-06</v>
       </c>
       <c r="D477" t="n">
-        <v>9.902748147367493</v>
+        <v>24.75690006198298</v>
       </c>
     </row>
     <row r="478">
@@ -7703,13 +7745,13 @@
         <v>57.20161211311512</v>
       </c>
       <c r="B478" t="n">
-        <v>99.62749235062481</v>
+        <v>50.11379980030009</v>
       </c>
       <c r="C478" t="n">
-        <v>1.84063715105769e-05</v>
+        <v>6.601339089170556e-06</v>
       </c>
       <c r="D478" t="n">
-        <v>9.902749235062478</v>
+        <v>24.75689990015005</v>
       </c>
     </row>
     <row r="479">
@@ -7717,13 +7759,13 @@
         <v>57.32178356713426</v>
       </c>
       <c r="B479" t="n">
-        <v>99.62750194113566</v>
+        <v>50.11379941964444</v>
       </c>
       <c r="C479" t="n">
-        <v>1.735074151110509e-05</v>
+        <v>6.685136822262151e-06</v>
       </c>
       <c r="D479" t="n">
-        <v>9.902750194113562</v>
+        <v>24.75689970982222</v>
       </c>
     </row>
     <row r="480">
@@ -7731,13 +7773,13 @@
         <v>57.44195502115341</v>
       </c>
       <c r="B480" t="n">
-        <v>99.6275102090632</v>
+        <v>50.11379903675791</v>
       </c>
       <c r="C480" t="n">
-        <v>1.644068859619367e-05</v>
+        <v>6.769425659084839e-06</v>
       </c>
       <c r="D480" t="n">
-        <v>9.902751020906317</v>
+        <v>24.75689951837895</v>
       </c>
     </row>
     <row r="481">
@@ -7745,13 +7787,13 @@
         <v>57.56212647517256</v>
       </c>
       <c r="B481" t="n">
-        <v>99.62751714274462</v>
+        <v>50.11379871175624</v>
       </c>
       <c r="C481" t="n">
-        <v>1.567749649589466e-05</v>
+        <v>6.840971694748838e-06</v>
       </c>
       <c r="D481" t="n">
-        <v>9.902751714274459</v>
+        <v>24.75689935587812</v>
       </c>
     </row>
     <row r="482">
@@ -7759,13 +7801,13 @@
         <v>57.68229792919171</v>
       </c>
       <c r="B482" t="n">
-        <v>99.62752275499858</v>
+        <v>50.11379851011191</v>
       </c>
       <c r="C482" t="n">
-        <v>1.505975425722373e-05</v>
+        <v>6.885361780127118e-06</v>
       </c>
       <c r="D482" t="n">
-        <v>9.902752275499854</v>
+        <v>24.75689925505596</v>
       </c>
     </row>
     <row r="483">
@@ -7773,13 +7815,13 @@
         <v>57.80246938321086</v>
       </c>
       <c r="B483" t="n">
-        <v>99.62752708312522</v>
+        <v>50.11379850265421</v>
       </c>
       <c r="C483" t="n">
-        <v>1.458335624416026e-05</v>
+        <v>6.887003521855398e-06</v>
       </c>
       <c r="D483" t="n">
-        <v>9.902752708312518</v>
+        <v>24.75689925132711</v>
       </c>
     </row>
     <row r="484">
@@ -7787,13 +7829,13 @@
         <v>57.92264083723001</v>
       </c>
       <c r="B484" t="n">
-        <v>99.62753018890614</v>
+        <v>50.1137987655692</v>
       </c>
       <c r="C484" t="n">
-        <v>1.424150213764737e-05</v>
+        <v>6.829125282332145e-06</v>
       </c>
       <c r="D484" t="n">
-        <v>9.902753018890611</v>
+        <v>24.7568993827846</v>
       </c>
     </row>
     <row r="485">
@@ -7801,13 +7843,13 @@
         <v>58.04281229124916</v>
       </c>
       <c r="B485" t="n">
-        <v>99.62753215860447</v>
+        <v>50.1137993803997</v>
       </c>
       <c r="C485" t="n">
-        <v>1.402469693559191e-05</v>
+        <v>6.693776179718566e-06</v>
       </c>
       <c r="D485" t="n">
-        <v>9.902753215860443</v>
+        <v>24.75689969019985</v>
       </c>
     </row>
     <row r="486">
@@ -7815,13 +7857,13 @@
         <v>58.16298374526831</v>
       </c>
       <c r="B486" t="n">
-        <v>99.62753310296478</v>
+        <v>50.11380043404532</v>
       </c>
       <c r="C486" t="n">
-        <v>1.392075095286446e-05</v>
+        <v>6.461826087938616e-06</v>
       </c>
       <c r="D486" t="n">
-        <v>9.902753310296474</v>
+        <v>24.75690021702266</v>
       </c>
     </row>
     <row r="487">
@@ -7829,13 +7871,13 @@
         <v>58.28315519928746</v>
       </c>
       <c r="B487" t="n">
-        <v>99.62753315721314</v>
+        <v>50.11380192625246</v>
       </c>
       <c r="C487" t="n">
-        <v>1.39147798212993e-05</v>
+        <v>6.133330839839968e-06</v>
       </c>
       <c r="D487" t="n">
-        <v>9.902753315721309</v>
+        <v>24.75690096312623</v>
       </c>
     </row>
     <row r="488">
@@ -7843,13 +7885,13 @@
         <v>58.40332665330661</v>
       </c>
       <c r="B488" t="n">
-        <v>99.6275324810571</v>
+        <v>50.11380340973249</v>
       </c>
       <c r="C488" t="n">
-        <v>1.398920448969448e-05</v>
+        <v>5.80675678256534e-06</v>
       </c>
       <c r="D488" t="n">
-        <v>9.902753248105707</v>
+        <v>24.75690170486624</v>
       </c>
     </row>
     <row r="489">
@@ -7857,13 +7899,13 @@
         <v>58.52349810732576</v>
       </c>
       <c r="B489" t="n">
-        <v>99.62753125868572</v>
+        <v>50.11380481475488</v>
       </c>
       <c r="C489" t="n">
-        <v>1.412375122381174e-05</v>
+        <v>5.497454430911991e-06</v>
       </c>
       <c r="D489" t="n">
-        <v>9.902753125868568</v>
+        <v>24.75690240737744</v>
       </c>
     </row>
     <row r="490">
@@ -7871,13 +7913,13 @@
         <v>58.64366956134491</v>
       </c>
       <c r="B490" t="n">
-        <v>99.62752969876948</v>
+        <v>50.11380614511287</v>
       </c>
       <c r="C490" t="n">
-        <v>1.429545160637657e-05</v>
+        <v>5.204588736334062e-06</v>
       </c>
       <c r="D490" t="n">
-        <v>9.902752969876943</v>
+        <v>24.75690307255644</v>
       </c>
     </row>
     <row r="491">
@@ -7885,13 +7927,13 @@
         <v>58.76384101536406</v>
       </c>
       <c r="B491" t="n">
-        <v>99.62752803446038</v>
+        <v>50.11380740448981</v>
       </c>
       <c r="C491" t="n">
-        <v>1.447864253707818e-05</v>
+        <v>4.927348847111666e-06</v>
       </c>
       <c r="D491" t="n">
-        <v>9.902752803446035</v>
+        <v>24.75690370224491</v>
       </c>
     </row>
     <row r="492">
@@ -7899,13 +7941,13 @@
         <v>58.88401246938321</v>
       </c>
       <c r="B492" t="n">
-        <v>99.62752652339191</v>
+        <v>50.11380859645913</v>
       </c>
       <c r="C492" t="n">
-        <v>1.464496623256951e-05</v>
+        <v>4.664948108350884e-06</v>
       </c>
       <c r="D492" t="n">
-        <v>9.902752652339187</v>
+        <v>24.75690429822956</v>
       </c>
     </row>
     <row r="493">
@@ -7913,13 +7955,13 @@
         <v>59.00418392340236</v>
       </c>
       <c r="B493" t="n">
-        <v>99.62752544767903</v>
+        <v>50.11380972448432</v>
       </c>
       <c r="C493" t="n">
-        <v>1.476337022646721e-05</v>
+        <v>4.416624061983764e-06</v>
       </c>
       <c r="D493" t="n">
-        <v>9.9027525447679</v>
+        <v>24.75690486224216</v>
       </c>
     </row>
     <row r="494">
@@ -7927,13 +7969,13 @@
         <v>59.12435537742151</v>
       </c>
       <c r="B494" t="n">
-        <v>99.62752511391818</v>
+        <v>50.11381079191897</v>
       </c>
       <c r="C494" t="n">
-        <v>1.480010736935168e-05</v>
+        <v>4.181638446768321e-06</v>
       </c>
       <c r="D494" t="n">
-        <v>9.902752511391814</v>
+        <v>24.75690539595949</v>
       </c>
     </row>
     <row r="495">
@@ -7941,13 +7983,13 @@
         <v>59.24452683144065</v>
       </c>
       <c r="B495" t="n">
-        <v>99.62752585318728</v>
+        <v>50.11381180200677</v>
       </c>
       <c r="C495" t="n">
-        <v>1.471873582876706e-05</v>
+        <v>3.959277198288558e-06</v>
       </c>
       <c r="D495" t="n">
-        <v>9.902752585318725</v>
+        <v>24.75690590100339</v>
       </c>
     </row>
     <row r="496">
@@ -7955,13 +7997,13 @@
         <v>59.3646982854598</v>
       </c>
       <c r="B496" t="n">
-        <v>99.62752802104575</v>
+        <v>50.11381275788148</v>
       </c>
       <c r="C496" t="n">
-        <v>1.448011908922114e-05</v>
+        <v>3.748850448954399e-06</v>
       </c>
       <c r="D496" t="n">
-        <v>9.902752802104571</v>
+        <v>24.75690637894074</v>
       </c>
     </row>
     <row r="497">
@@ -7969,13 +8011,13 @@
         <v>59.48486973947895</v>
       </c>
       <c r="B497" t="n">
-        <v>99.62753199753446</v>
+        <v>50.11381366256693</v>
       </c>
       <c r="C497" t="n">
-        <v>1.404242595218555e-05</v>
+        <v>3.549692528001782e-06</v>
       </c>
       <c r="D497" t="n">
-        <v>9.902753199753443</v>
+        <v>24.75690683128346</v>
       </c>
     </row>
     <row r="498">
@@ -7983,13 +8025,13 @@
         <v>59.6050411934981</v>
       </c>
       <c r="B498" t="n">
-        <v>99.62753806988874</v>
+        <v>50.11381451897705</v>
       </c>
       <c r="C498" t="n">
-        <v>1.337404035295697e-05</v>
+        <v>3.361161961492599e-06</v>
       </c>
       <c r="D498" t="n">
-        <v>9.902753806988871</v>
+        <v>24.75690725948852</v>
       </c>
     </row>
     <row r="499">
@@ -7997,13 +8039,13 @@
         <v>59.72521264751725</v>
       </c>
       <c r="B499" t="n">
-        <v>99.62754449760855</v>
+        <v>50.11381532991587</v>
       </c>
       <c r="C499" t="n">
-        <v>1.266653957620081e-05</v>
+        <v>3.182641472314707e-06</v>
       </c>
       <c r="D499" t="n">
-        <v>9.902754449760852</v>
+        <v>24.75690766495793</v>
       </c>
     </row>
     <row r="500">
@@ -8011,13 +8053,13 @@
         <v>59.8453841015364</v>
       </c>
       <c r="B500" t="n">
-        <v>99.62755058528506</v>
+        <v>50.11381609807748</v>
       </c>
       <c r="C500" t="n">
-        <v>1.199646745585531e-05</v>
+        <v>3.013537980181934e-06</v>
       </c>
       <c r="D500" t="n">
-        <v>9.902755058528502</v>
+        <v>24.75690804903874</v>
       </c>
     </row>
     <row r="501">
@@ -8025,13 +8067,13 @@
         <v>59.96555555555555</v>
       </c>
       <c r="B501" t="n">
-        <v>99.62755635091774</v>
+        <v>50.11381682604605</v>
       </c>
       <c r="C501" t="n">
-        <v>1.136184278018755e-05</v>
+        <v>2.853282601634079e-06</v>
       </c>
       <c r="D501" t="n">
-        <v>9.902755635091772</v>
+        <v>24.75690841302303</v>
       </c>
     </row>
   </sheetData>
